--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -33,9 +33,11 @@
     <sheet name="CurioDomainGrants" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="EquationExpansionRewards" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="DomainLayout" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="DomainDecks" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="DomainCards" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -62,6 +64,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'CurioDomainGrants'!$A$3:$L$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'EquationExpansionRewards'!$A$3:$Q$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'DomainLayout'!$A$3:$L$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'DomainDecks'!$A$3:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'DomainCards'!$A$3:$J$132</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -569,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4302,8 +4306,161 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="9" t="n"/>
+      <c r="B74" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>du.source.domain-deck.roguepersonastyle</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/RoguePersonaStyle.json; exact keys retained per deck/card row</t>
+        </is>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>49b1c63d1f9dcad5201ae6f6446c01b9f401506b5625c39fc4da4b62378c6834</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K74" s="9" t="inlineStr">
+        <is>
+          <t>Exact source values only; field roles and runtime admission remain explicit policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="n"/>
+      <c r="B75" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>du.source.domain-deck.roguepersonaroompreset</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/RoguePersonaRoomPreset.json; exact keys retained per deck/card row</t>
+        </is>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>a4cc8bbd6e3a4db5fecb62b83a0c5de7ad2f4a9820ad5ae9180b30ae33c346b5</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K75" s="9" t="inlineStr">
+        <is>
+          <t>Exact source values only; field roles and runtime admission remain explicit policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="n"/>
+      <c r="B76" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>du.source.domain-deck.roguepersonaroomcomptype</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/RoguePersonaRoomCompType.json; exact keys retained per deck/card row</t>
+        </is>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>c0223603c6e5252278dac5224d766f1c4ed60ebe5845b9839b9e3533a8ad76a5</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K76" s="9" t="inlineStr">
+        <is>
+          <t>Exact source values only; field roles and runtime admission remain explicit policy.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K73"/>
+  <autoFilter ref="A3:K76"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -18620,6 +18777,6130 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="9"/>
+    <col width="28" customWidth="1" style="5" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuDomainDecks</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>dffd7b16ec599e1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>style_source</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>card_count</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>source_locator</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>style_source</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>card_count</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>source_locator</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuDomainDeckPolicy&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..256</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.gladiator</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>ExplicitSourceDeck</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicyExplicitSourceDeck: caller selects this reviewed source record; interpret JEHDKAKMCGC as an ordered initial deck and repeated presets as distinct card instances. Interpret preset AAGKEBFHLMC as level. Exact numeric joins do not prove playable mask eligibility, unlock conditions, initial offer weights, draw width, pass costs or room behavior. No automatic profile membership or terminal runtime coverage is granted.</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Replace field-role inference and caller-selected admission when released named selectors or reproducible observations establish initial decks and eligibility. Retain duplicate instances and exact source order. Style 901 and all other unselected records remain pending, not excluded.</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=101;JEHDKAKMCGC</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.camera</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>ExplicitSourceDeck</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicyExplicitSourceDeck: caller selects this reviewed source record; interpret JEHDKAKMCGC as an ordered initial deck and repeated presets as distinct card instances. Interpret preset AAGKEBFHLMC as level. Exact numeric joins do not prove playable mask eligibility, unlock conditions, initial offer weights, draw width, pass costs or room behavior. No automatic profile membership or terminal runtime coverage is granted.</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Replace field-role inference and caller-selected admission when released named selectors or reproducible observations establish initial decks and eligibility. Retain duplicate instances and exact source order. Style 901 and all other unselected records remain pending, not excluded.</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=102;JEHDKAKMCGC</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.mechatron</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>ExplicitSourceDeck</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicyExplicitSourceDeck: caller selects this reviewed source record; interpret JEHDKAKMCGC as an ordered initial deck and repeated presets as distinct card instances. Interpret preset AAGKEBFHLMC as level. Exact numeric joins do not prove playable mask eligibility, unlock conditions, initial offer weights, draw width, pass costs or room behavior. No automatic profile membership or terminal runtime coverage is granted.</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>Replace field-role inference and caller-selected admission when released named selectors or reproducible observations establish initial decks and eligibility. Retain duplicate instances and exact source order. Style 901 and all other unselected records remain pending, not excluded.</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=103;JEHDKAKMCGC</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.horse</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>ExplicitSourceDeck</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicyExplicitSourceDeck: caller selects this reviewed source record; interpret JEHDKAKMCGC as an ordered initial deck and repeated presets as distinct card instances. Interpret preset AAGKEBFHLMC as level. Exact numeric joins do not prove playable mask eligibility, unlock conditions, initial offer weights, draw width, pass costs or room behavior. No automatic profile membership or terminal runtime coverage is granted.</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>Replace field-role inference and caller-selected admission when released named selectors or reproducible observations establish initial decks and eligibility. Retain duplicate instances and exact source order. Style 901 and all other unselected records remain pending, not excluded.</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=104;JEHDKAKMCGC</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.fortune-cat</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>ExplicitSourceDeck</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicyExplicitSourceDeck: caller selects this reviewed source record; interpret JEHDKAKMCGC as an ordered initial deck and repeated presets as distinct card instances. Interpret preset AAGKEBFHLMC as level. Exact numeric joins do not prove playable mask eligibility, unlock conditions, initial offer weights, draw width, pass costs or room behavior. No automatic profile membership or terminal runtime coverage is granted.</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>Replace field-role inference and caller-selected admission when released named selectors or reproducible observations establish initial decks and eligibility. Retain duplicate instances and exact source order. Style 901 and all other unselected records remain pending, not excluded.</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=105;JEHDKAKMCGC</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.cringe</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>ExplicitSourceDeck</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicyExplicitSourceDeck: caller selects this reviewed source record; interpret JEHDKAKMCGC as an ordered initial deck and repeated presets as distinct card instances. Interpret preset AAGKEBFHLMC as level. Exact numeric joins do not prove playable mask eligibility, unlock conditions, initial offer weights, draw width, pass costs or room behavior. No automatic profile membership or terminal runtime coverage is granted.</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>Replace field-role inference and caller-selected admission when released named selectors or reproducible observations establish initial decks and eligibility. Retain duplicate instances and exact source order. Style 901 and all other unselected records remain pending, not excluded.</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=106;JEHDKAKMCGC</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.slipshod</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>ExplicitSourceDeck</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicyExplicitSourceDeck: caller selects this reviewed source record; interpret JEHDKAKMCGC as an ordered initial deck and repeated presets as distinct card instances. Interpret preset AAGKEBFHLMC as level. Exact numeric joins do not prove playable mask eligibility, unlock conditions, initial offer weights, draw width, pass costs or room behavior. No automatic profile membership or terminal runtime coverage is granted.</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>Replace field-role inference and caller-selected admission when released named selectors or reproducible observations establish initial decks and eligibility. Retain duplicate instances and exact source order. Style 901 and all other unselected records remain pending, not excluded.</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=107;JEHDKAKMCGC</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.chariot</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>ExplicitSourceDeck</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicyExplicitSourceDeck: caller selects this reviewed source record; interpret JEHDKAKMCGC as an ordered initial deck and repeated presets as distinct card instances. Interpret preset AAGKEBFHLMC as level. Exact numeric joins do not prove playable mask eligibility, unlock conditions, initial offer weights, draw width, pass costs or room behavior. No automatic profile membership or terminal runtime coverage is granted.</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>Replace field-role inference and caller-selected admission when released named selectors or reproducible observations establish initial decks and eligibility. Retain duplicate instances and exact source order. Style 901 and all other unselected records remain pending, not excluded.</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=108;JEHDKAKMCGC</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.two</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>ExplicitSourceDeck</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicyExplicitSourceDeck: caller selects this reviewed source record; interpret JEHDKAKMCGC as an ordered initial deck and repeated presets as distinct card instances. Interpret preset AAGKEBFHLMC as level. Exact numeric joins do not prove playable mask eligibility, unlock conditions, initial offer weights, draw width, pass costs or room behavior. No automatic profile membership or terminal runtime coverage is granted.</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Replace field-role inference and caller-selected admission when released named selectors or reproducible observations establish initial decks and eligibility. Retain duplicate instances and exact source order. Style 901 and all other unselected records remain pending, not excluded.</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=110;JEHDKAKMCGC</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J16"/>
+  <dataValidations count="3">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="E8:E1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExplicitSourceDeck" promptTitle="DuDomainDeckPolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"ExplicitSourceDeck"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F8:F1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 256." promptTitle="Integer range" prompt="Enter an integer from 1 to 256." type="whole">
+      <formula1>1</formula1>
+      <formula2>256</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J132"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="9"/>
+    <col width="28" customWidth="1" style="5" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuDomainCards</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>5022e055fa084725</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>deck_id</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>ordinal</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>preset_source</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>source_locator</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>deck_id</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>ordinal</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>preset_source</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>source_locator</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>ref&lt;DuDomainDecks.id&gt;</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuDomainCardKind&gt;</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..256</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..5</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.gladiator.card-1</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=101;JEHDKAKMCGC[0];RoguePersonaRoomPreset:LIIPLGLNPGB=1005</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.gladiator.card-2</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=101;JEHDKAKMCGC[1];RoguePersonaRoomPreset:LIIPLGLNPGB=1005</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.gladiator.card-3</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=101;JEHDKAKMCGC[2];RoguePersonaRoomPreset:LIIPLGLNPGB=1006</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.gladiator.card-4</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=101;JEHDKAKMCGC[3];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.gladiator.card-5</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=101;JEHDKAKMCGC[4];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.gladiator.card-6</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=101;JEHDKAKMCGC[5];RoguePersonaRoomPreset:LIIPLGLNPGB=1008</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.gladiator.card-7</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=101;JEHDKAKMCGC[6];RoguePersonaRoomPreset:LIIPLGLNPGB=1009</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.gladiator.card-8</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=101;JEHDKAKMCGC[7];RoguePersonaRoomPreset:LIIPLGLNPGB=1009</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.gladiator.card-9</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=101;JEHDKAKMCGC[8];RoguePersonaRoomPreset:LIIPLGLNPGB=1010</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.gladiator.card-10</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>Adventure</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=101;JEHDKAKMCGC[9];RoguePersonaRoomPreset:LIIPLGLNPGB=1011</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.gladiator.card-11</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>Reforge</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=101;JEHDKAKMCGC[10];RoguePersonaRoomPreset:LIIPLGLNPGB=1017</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.gladiator.card-12</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=101;JEHDKAKMCGC[11];RoguePersonaRoomPreset:LIIPLGLNPGB=1020</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.gladiator.card-13</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=101;JEHDKAKMCGC[12];RoguePersonaRoomPreset:LIIPLGLNPGB=1025</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.gladiator.card-14</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=101;JEHDKAKMCGC[13];RoguePersonaRoomPreset:LIIPLGLNPGB=1023</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.camera.card-1</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=102;JEHDKAKMCGC[0];RoguePersonaRoomPreset:LIIPLGLNPGB=1005</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.camera.card-2</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=102;JEHDKAKMCGC[1];RoguePersonaRoomPreset:LIIPLGLNPGB=1005</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.camera.card-3</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=102;JEHDKAKMCGC[2];RoguePersonaRoomPreset:LIIPLGLNPGB=1006</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.camera.card-4</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=102;JEHDKAKMCGC[3];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.camera.card-5</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=102;JEHDKAKMCGC[4];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n"/>
+      <c r="B27" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.camera.card-6</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=102;JEHDKAKMCGC[5];RoguePersonaRoomPreset:LIIPLGLNPGB=1008</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.camera.card-7</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=102;JEHDKAKMCGC[6];RoguePersonaRoomPreset:LIIPLGLNPGB=1009</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.camera.card-8</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=102;JEHDKAKMCGC[7];RoguePersonaRoomPreset:LIIPLGLNPGB=1010</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.camera.card-9</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>Adventure</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=102;JEHDKAKMCGC[8];RoguePersonaRoomPreset:LIIPLGLNPGB=1011</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n"/>
+      <c r="B31" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.camera.card-10</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>Reforge</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=102;JEHDKAKMCGC[9];RoguePersonaRoomPreset:LIIPLGLNPGB=1017</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n"/>
+      <c r="B32" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.camera.card-11</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=102;JEHDKAKMCGC[10];RoguePersonaRoomPreset:LIIPLGLNPGB=1020</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n"/>
+      <c r="B33" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.camera.card-12</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=102;JEHDKAKMCGC[11];RoguePersonaRoomPreset:LIIPLGLNPGB=1021</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n"/>
+      <c r="B34" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.camera.card-13</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=102;JEHDKAKMCGC[12];RoguePersonaRoomPreset:LIIPLGLNPGB=1022</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="n"/>
+      <c r="B35" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.mechatron.card-1</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=103;JEHDKAKMCGC[0];RoguePersonaRoomPreset:LIIPLGLNPGB=1005</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n"/>
+      <c r="B36" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.mechatron.card-2</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=103;JEHDKAKMCGC[1];RoguePersonaRoomPreset:LIIPLGLNPGB=1005</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n"/>
+      <c r="B37" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.mechatron.card-3</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=103;JEHDKAKMCGC[2];RoguePersonaRoomPreset:LIIPLGLNPGB=1005</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n"/>
+      <c r="B38" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.mechatron.card-4</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=103;JEHDKAKMCGC[3];RoguePersonaRoomPreset:LIIPLGLNPGB=1023</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="n"/>
+      <c r="B39" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.mechatron.card-5</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=103;JEHDKAKMCGC[4];RoguePersonaRoomPreset:LIIPLGLNPGB=1006</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n"/>
+      <c r="B40" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.mechatron.card-6</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=103;JEHDKAKMCGC[5];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="n"/>
+      <c r="B41" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.mechatron.card-7</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=103;JEHDKAKMCGC[6];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n"/>
+      <c r="B42" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.mechatron.card-8</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=103;JEHDKAKMCGC[7];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="n"/>
+      <c r="B43" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.mechatron.card-9</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=103;JEHDKAKMCGC[8];RoguePersonaRoomPreset:LIIPLGLNPGB=1021</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="n"/>
+      <c r="B44" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.mechatron.card-10</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=103;JEHDKAKMCGC[9];RoguePersonaRoomPreset:LIIPLGLNPGB=1008</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="n"/>
+      <c r="B45" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.mechatron.card-11</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=103;JEHDKAKMCGC[10];RoguePersonaRoomPreset:LIIPLGLNPGB=1008</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="n"/>
+      <c r="B46" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.mechatron.card-12</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=103;JEHDKAKMCGC[11];RoguePersonaRoomPreset:LIIPLGLNPGB=1008</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="n"/>
+      <c r="B47" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.mechatron.card-13</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=103;JEHDKAKMCGC[12];RoguePersonaRoomPreset:LIIPLGLNPGB=1024</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="n"/>
+      <c r="B48" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.mechatron.card-14</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=103;JEHDKAKMCGC[13];RoguePersonaRoomPreset:LIIPLGLNPGB=1009</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="n"/>
+      <c r="B49" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.mechatron.card-15</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=103;JEHDKAKMCGC[14];RoguePersonaRoomPreset:LIIPLGLNPGB=1010</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="n"/>
+      <c r="B50" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.mechatron.card-16</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>Adventure</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=103;JEHDKAKMCGC[15];RoguePersonaRoomPreset:LIIPLGLNPGB=1011</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="n"/>
+      <c r="B51" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.mechatron.card-17</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>Reforge</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=103;JEHDKAKMCGC[16];RoguePersonaRoomPreset:LIIPLGLNPGB=1017</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="n"/>
+      <c r="B52" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.mechatron.card-18</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=103;JEHDKAKMCGC[17];RoguePersonaRoomPreset:LIIPLGLNPGB=1020</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="n"/>
+      <c r="B53" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.horse.card-1</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=104;JEHDKAKMCGC[0];RoguePersonaRoomPreset:LIIPLGLNPGB=1005</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="n"/>
+      <c r="B54" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.horse.card-2</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E54" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=104;JEHDKAKMCGC[1];RoguePersonaRoomPreset:LIIPLGLNPGB=1005</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="n"/>
+      <c r="B55" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.horse.card-3</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=104;JEHDKAKMCGC[2];RoguePersonaRoomPreset:LIIPLGLNPGB=1023</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="n"/>
+      <c r="B56" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.horse.card-4</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E56" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=104;JEHDKAKMCGC[3];RoguePersonaRoomPreset:LIIPLGLNPGB=1006</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="n"/>
+      <c r="B57" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.horse.card-5</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=104;JEHDKAKMCGC[4];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="n"/>
+      <c r="B58" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.horse.card-6</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H58" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=104;JEHDKAKMCGC[5];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="n"/>
+      <c r="B59" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.horse.card-7</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=104;JEHDKAKMCGC[6];RoguePersonaRoomPreset:LIIPLGLNPGB=1021</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="n"/>
+      <c r="B60" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.horse.card-8</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E60" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=104;JEHDKAKMCGC[7];RoguePersonaRoomPreset:LIIPLGLNPGB=1008</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.horse.card-9</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="H61" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=104;JEHDKAKMCGC[8];RoguePersonaRoomPreset:LIIPLGLNPGB=1009</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="n"/>
+      <c r="B62" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.horse.card-10</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="H62" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=104;JEHDKAKMCGC[9];RoguePersonaRoomPreset:LIIPLGLNPGB=1010</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="n"/>
+      <c r="B63" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.horse.card-11</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>Adventure</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=104;JEHDKAKMCGC[10];RoguePersonaRoomPreset:LIIPLGLNPGB=1011</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="n"/>
+      <c r="B64" s="9" t="n">
+        <v>57</v>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.horse.card-12</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E64" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>Reforge</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=104;JEHDKAKMCGC[11];RoguePersonaRoomPreset:LIIPLGLNPGB=1017</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="n"/>
+      <c r="B65" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.horse.card-13</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=104;JEHDKAKMCGC[12];RoguePersonaRoomPreset:LIIPLGLNPGB=1020</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="n"/>
+      <c r="B66" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.fortune-cat.card-1</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=105;JEHDKAKMCGC[0];RoguePersonaRoomPreset:LIIPLGLNPGB=1005</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="n"/>
+      <c r="B67" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.fortune-cat.card-2</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E67" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=105;JEHDKAKMCGC[1];RoguePersonaRoomPreset:LIIPLGLNPGB=1005</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="n"/>
+      <c r="B68" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.fortune-cat.card-3</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E68" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=105;JEHDKAKMCGC[2];RoguePersonaRoomPreset:LIIPLGLNPGB=1006</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="n"/>
+      <c r="B69" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.fortune-cat.card-4</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=105;JEHDKAKMCGC[3];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="n"/>
+      <c r="B70" s="9" t="n">
+        <v>63</v>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.fortune-cat.card-5</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E70" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=105;JEHDKAKMCGC[4];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="n"/>
+      <c r="B71" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.fortune-cat.card-6</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E71" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=105;JEHDKAKMCGC[5];RoguePersonaRoomPreset:LIIPLGLNPGB=1008</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="n"/>
+      <c r="B72" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.fortune-cat.card-7</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E72" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=105;JEHDKAKMCGC[6];RoguePersonaRoomPreset:LIIPLGLNPGB=1008</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="n"/>
+      <c r="B73" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.fortune-cat.card-8</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E73" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=105;JEHDKAKMCGC[7];RoguePersonaRoomPreset:LIIPLGLNPGB=1009</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="n"/>
+      <c r="B74" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.fortune-cat.card-9</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E74" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=105;JEHDKAKMCGC[8];RoguePersonaRoomPreset:LIIPLGLNPGB=1026</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="n"/>
+      <c r="B75" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.fortune-cat.card-10</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E75" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=105;JEHDKAKMCGC[9];RoguePersonaRoomPreset:LIIPLGLNPGB=1010</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="n"/>
+      <c r="B76" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.fortune-cat.card-11</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E76" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>Adventure</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=105;JEHDKAKMCGC[10];RoguePersonaRoomPreset:LIIPLGLNPGB=1011</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="n"/>
+      <c r="B77" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.fortune-cat.card-12</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E77" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>Reforge</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=105;JEHDKAKMCGC[11];RoguePersonaRoomPreset:LIIPLGLNPGB=1017</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="n"/>
+      <c r="B78" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.fortune-cat.card-13</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E78" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=105;JEHDKAKMCGC[12];RoguePersonaRoomPreset:LIIPLGLNPGB=1020</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="n"/>
+      <c r="B79" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.fortune-cat.card-14</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=105;JEHDKAKMCGC[13];RoguePersonaRoomPreset:LIIPLGLNPGB=1024</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="n"/>
+      <c r="B80" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.cringe.card-1</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E80" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=106;JEHDKAKMCGC[0];RoguePersonaRoomPreset:LIIPLGLNPGB=1005</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n"/>
+      <c r="B81" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.cringe.card-2</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E81" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=106;JEHDKAKMCGC[1];RoguePersonaRoomPreset:LIIPLGLNPGB=1005</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="n"/>
+      <c r="B82" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.cringe.card-3</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E82" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H82" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=106;JEHDKAKMCGC[2];RoguePersonaRoomPreset:LIIPLGLNPGB=1023</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="n"/>
+      <c r="B83" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.cringe.card-4</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E83" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="H83" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=106;JEHDKAKMCGC[3];RoguePersonaRoomPreset:LIIPLGLNPGB=1006</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="n"/>
+      <c r="B84" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.cringe.card-5</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E84" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=106;JEHDKAKMCGC[4];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="n"/>
+      <c r="B85" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.cringe.card-6</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E85" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=106;JEHDKAKMCGC[5];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="n"/>
+      <c r="B86" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.cringe.card-7</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E86" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H86" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=106;JEHDKAKMCGC[6];RoguePersonaRoomPreset:LIIPLGLNPGB=1021</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="n"/>
+      <c r="B87" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.cringe.card-8</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E87" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=106;JEHDKAKMCGC[7];RoguePersonaRoomPreset:LIIPLGLNPGB=1008</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="n"/>
+      <c r="B88" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.cringe.card-9</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E88" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="G88" s="9" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="H88" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=106;JEHDKAKMCGC[8];RoguePersonaRoomPreset:LIIPLGLNPGB=1009</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="n"/>
+      <c r="B89" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.cringe.card-10</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E89" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="H89" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=106;JEHDKAKMCGC[9];RoguePersonaRoomPreset:LIIPLGLNPGB=1009</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="n"/>
+      <c r="B90" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.cringe.card-11</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E90" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=106;JEHDKAKMCGC[10];RoguePersonaRoomPreset:LIIPLGLNPGB=1010</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="n"/>
+      <c r="B91" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.cringe.card-12</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E91" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="G91" s="9" t="inlineStr">
+        <is>
+          <t>Adventure</t>
+        </is>
+      </c>
+      <c r="H91" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=106;JEHDKAKMCGC[11];RoguePersonaRoomPreset:LIIPLGLNPGB=1011</t>
+        </is>
+      </c>
+      <c r="J91" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="n"/>
+      <c r="B92" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.cringe.card-13</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E92" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="G92" s="9" t="inlineStr">
+        <is>
+          <t>Reforge</t>
+        </is>
+      </c>
+      <c r="H92" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=106;JEHDKAKMCGC[12];RoguePersonaRoomPreset:LIIPLGLNPGB=1017</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="n"/>
+      <c r="B93" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.cringe.card-14</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E93" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="G93" s="9" t="inlineStr">
+        <is>
+          <t>Reforge</t>
+        </is>
+      </c>
+      <c r="H93" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=106;JEHDKAKMCGC[13];RoguePersonaRoomPreset:LIIPLGLNPGB=1017</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="n"/>
+      <c r="B94" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.cringe.card-15</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E94" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=106;JEHDKAKMCGC[14];RoguePersonaRoomPreset:LIIPLGLNPGB=1020</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="n"/>
+      <c r="B95" s="9" t="n">
+        <v>88</v>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.slipshod.card-1</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E95" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=107;JEHDKAKMCGC[0];RoguePersonaRoomPreset:LIIPLGLNPGB=1005</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="n"/>
+      <c r="B96" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.slipshod.card-2</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E96" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="G96" s="9" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="H96" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=107;JEHDKAKMCGC[1];RoguePersonaRoomPreset:LIIPLGLNPGB=1006</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="n"/>
+      <c r="B97" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.slipshod.card-3</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E97" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G97" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H97" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=107;JEHDKAKMCGC[2];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="n"/>
+      <c r="B98" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.slipshod.card-4</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E98" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G98" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H98" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=107;JEHDKAKMCGC[3];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="n"/>
+      <c r="B99" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.slipshod.card-5</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E99" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="G99" s="9" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="H99" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=107;JEHDKAKMCGC[4];RoguePersonaRoomPreset:LIIPLGLNPGB=1008</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="n"/>
+      <c r="B100" s="9" t="n">
+        <v>93</v>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.slipshod.card-6</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E100" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=107;JEHDKAKMCGC[5];RoguePersonaRoomPreset:LIIPLGLNPGB=1009</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="n"/>
+      <c r="B101" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.slipshod.card-7</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E101" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="G101" s="9" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="H101" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=107;JEHDKAKMCGC[6];RoguePersonaRoomPreset:LIIPLGLNPGB=1010</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="n"/>
+      <c r="B102" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.slipshod.card-8</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E102" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="G102" s="9" t="inlineStr">
+        <is>
+          <t>Adventure</t>
+        </is>
+      </c>
+      <c r="H102" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=107;JEHDKAKMCGC[7];RoguePersonaRoomPreset:LIIPLGLNPGB=1011</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="n"/>
+      <c r="B103" s="9" t="n">
+        <v>96</v>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.slipshod.card-9</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E103" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="G103" s="9" t="inlineStr">
+        <is>
+          <t>Reforge</t>
+        </is>
+      </c>
+      <c r="H103" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=107;JEHDKAKMCGC[8];RoguePersonaRoomPreset:LIIPLGLNPGB=1017</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="n"/>
+      <c r="B104" s="9" t="n">
+        <v>97</v>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.slipshod.card-10</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E104" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="G104" s="9" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="H104" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=107;JEHDKAKMCGC[9];RoguePersonaRoomPreset:LIIPLGLNPGB=1020</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="n"/>
+      <c r="B105" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.slipshod.card-11</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E105" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=107;JEHDKAKMCGC[10];RoguePersonaRoomPreset:LIIPLGLNPGB=1021</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="n"/>
+      <c r="B106" s="9" t="n">
+        <v>99</v>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.slipshod.card-12</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E106" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H106" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=107;JEHDKAKMCGC[11];RoguePersonaRoomPreset:LIIPLGLNPGB=1023</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="n"/>
+      <c r="B107" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.chariot.card-1</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E107" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G107" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=108;JEHDKAKMCGC[0];RoguePersonaRoomPreset:LIIPLGLNPGB=1005</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="n"/>
+      <c r="B108" s="9" t="n">
+        <v>101</v>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.chariot.card-2</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E108" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H108" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=108;JEHDKAKMCGC[1];RoguePersonaRoomPreset:LIIPLGLNPGB=1005</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="n"/>
+      <c r="B109" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.chariot.card-3</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E109" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H109" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=108;JEHDKAKMCGC[2];RoguePersonaRoomPreset:LIIPLGLNPGB=1023</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="n"/>
+      <c r="B110" s="9" t="n">
+        <v>103</v>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.chariot.card-4</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E110" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="G110" s="9" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="H110" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=108;JEHDKAKMCGC[3];RoguePersonaRoomPreset:LIIPLGLNPGB=1006</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="n"/>
+      <c r="B111" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.chariot.card-5</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E111" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G111" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H111" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=108;JEHDKAKMCGC[4];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="n"/>
+      <c r="B112" s="9" t="n">
+        <v>105</v>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.chariot.card-6</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E112" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G112" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H112" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=108;JEHDKAKMCGC[5];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="n"/>
+      <c r="B113" s="9" t="n">
+        <v>106</v>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.chariot.card-7</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E113" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="G113" s="9" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="H113" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=108;JEHDKAKMCGC[6];RoguePersonaRoomPreset:LIIPLGLNPGB=1008</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="n"/>
+      <c r="B114" s="9" t="n">
+        <v>107</v>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.chariot.card-8</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E114" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="G114" s="9" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="H114" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=108;JEHDKAKMCGC[7];RoguePersonaRoomPreset:LIIPLGLNPGB=1009</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="n"/>
+      <c r="B115" s="9" t="n">
+        <v>108</v>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.chariot.card-9</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E115" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="G115" s="9" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="H115" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I115" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=108;JEHDKAKMCGC[8];RoguePersonaRoomPreset:LIIPLGLNPGB=1010</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="n"/>
+      <c r="B116" s="9" t="n">
+        <v>109</v>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.chariot.card-10</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E116" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F116" s="9" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="G116" s="9" t="inlineStr">
+        <is>
+          <t>Adventure</t>
+        </is>
+      </c>
+      <c r="H116" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=108;JEHDKAKMCGC[9];RoguePersonaRoomPreset:LIIPLGLNPGB=1011</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="n"/>
+      <c r="B117" s="9" t="n">
+        <v>110</v>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.chariot.card-11</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E117" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F117" s="9" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="G117" s="9" t="inlineStr">
+        <is>
+          <t>Reforge</t>
+        </is>
+      </c>
+      <c r="H117" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=108;JEHDKAKMCGC[10];RoguePersonaRoomPreset:LIIPLGLNPGB=1017</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="n"/>
+      <c r="B118" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.chariot.card-12</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E118" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F118" s="9" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="G118" s="9" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="H118" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=108;JEHDKAKMCGC[11];RoguePersonaRoomPreset:LIIPLGLNPGB=1020</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="n"/>
+      <c r="B119" s="9" t="n">
+        <v>112</v>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.chariot.card-13</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E119" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F119" s="9" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="G119" s="9" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="H119" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=108;JEHDKAKMCGC[12];RoguePersonaRoomPreset:LIIPLGLNPGB=1025</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="n"/>
+      <c r="B120" s="9" t="n">
+        <v>113</v>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.two.card-1</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E120" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G120" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H120" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=110;JEHDKAKMCGC[0];RoguePersonaRoomPreset:LIIPLGLNPGB=1005</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="n"/>
+      <c r="B121" s="9" t="n">
+        <v>114</v>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.two.card-2</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E121" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F121" s="9" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G121" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H121" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=110;JEHDKAKMCGC[1];RoguePersonaRoomPreset:LIIPLGLNPGB=1005</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="n"/>
+      <c r="B122" s="9" t="n">
+        <v>115</v>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.two.card-3</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E122" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F122" s="9" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="G122" s="9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="H122" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I122" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=110;JEHDKAKMCGC[2];RoguePersonaRoomPreset:LIIPLGLNPGB=1005</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="n"/>
+      <c r="B123" s="9" t="n">
+        <v>116</v>
+      </c>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.two.card-4</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E123" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F123" s="9" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="G123" s="9" t="inlineStr">
+        <is>
+          <t>Encounter</t>
+        </is>
+      </c>
+      <c r="H123" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=110;JEHDKAKMCGC[3];RoguePersonaRoomPreset:LIIPLGLNPGB=1006</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="n"/>
+      <c r="B124" s="9" t="n">
+        <v>117</v>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.two.card-5</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E124" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F124" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G124" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H124" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I124" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=110;JEHDKAKMCGC[4];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="n"/>
+      <c r="B125" s="9" t="n">
+        <v>118</v>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.two.card-6</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E125" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G125" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H125" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=110;JEHDKAKMCGC[5];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="n"/>
+      <c r="B126" s="9" t="n">
+        <v>119</v>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.two.card-7</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E126" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F126" s="9" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="H126" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=110;JEHDKAKMCGC[6];RoguePersonaRoomPreset:LIIPLGLNPGB=1007</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="n"/>
+      <c r="B127" s="9" t="n">
+        <v>120</v>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.two.card-8</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E127" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F127" s="9" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="G127" s="9" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="H127" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=110;JEHDKAKMCGC[7];RoguePersonaRoomPreset:LIIPLGLNPGB=1008</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="n"/>
+      <c r="B128" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.two.card-9</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E128" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F128" s="9" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="G128" s="9" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="H128" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=110;JEHDKAKMCGC[8];RoguePersonaRoomPreset:LIIPLGLNPGB=1009</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="n"/>
+      <c r="B129" s="9" t="n">
+        <v>122</v>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.two.card-10</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E129" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F129" s="9" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="G129" s="9" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="H129" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=110;JEHDKAKMCGC[9];RoguePersonaRoomPreset:LIIPLGLNPGB=1010</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="n"/>
+      <c r="B130" s="9" t="n">
+        <v>123</v>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.two.card-11</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E130" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F130" s="9" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="G130" s="9" t="inlineStr">
+        <is>
+          <t>Adventure</t>
+        </is>
+      </c>
+      <c r="H130" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=110;JEHDKAKMCGC[10];RoguePersonaRoomPreset:LIIPLGLNPGB=1011</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="n"/>
+      <c r="B131" s="9" t="n">
+        <v>124</v>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.two.card-12</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E131" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F131" s="9" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="G131" s="9" t="inlineStr">
+        <is>
+          <t>Reforge</t>
+        </is>
+      </c>
+      <c r="H131" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=110;JEHDKAKMCGC[11];RoguePersonaRoomPreset:LIIPLGLNPGB=1017</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="n"/>
+      <c r="B132" s="9" t="n">
+        <v>125</v>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>du.domain-deck.two.card-13</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E132" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F132" s="9" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="G132" s="9" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="H132" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" s="9" t="inlineStr">
+        <is>
+          <t>RoguePersonaStyle:KLOEJIMMPJM=110;JEHDKAKMCGC[12];RoguePersonaRoomPreset:LIIPLGLNPGB=1020</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="inlineStr">
+        <is>
+          <t>67|68|69</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J132"/>
+  <dataValidations count="4">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="E8:E1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 256." promptTitle="Integer range" prompt="Enter an integer from 1 to 256." type="whole">
+      <formula1>1</formula1>
+      <formula2>256</formula2>
+    </dataValidation>
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Battle, Encounter, Event, Coin, Shop, Reward, Adventure, Reforge, Elite" promptTitle="DuDomainCardKind enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"Battle,Encounter,Event,Coin,Shop,Reward,Adventure,Reforge,Elite"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H8:H1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 5." promptTitle="Integer range" prompt="Enter an integer from 1 to 5." type="whole">
+      <formula1>1</formula1>
+      <formula2>5</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -56,7 +56,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'EvolutionOptions'!$A$3:$P$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'CurioVictoryBlessings'!$A$3:$P$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'DomainChoices'!$A$3:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'BattleFragments'!$A$3:$J$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'BattleFragments'!$A$3:$J$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'CurioDomainExpiries'!$A$3:$M$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'CurioBattleStats'!$A$3:$P$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'CurioBattleReactions'!$A$3:$O$8</definedName>
@@ -11151,7 +11151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>VersionedProjectPolicy: after each verified won battle, credit the authored fixed base amount for the authenticated domain before separate Curio victory grants and Blessing generation. Combat and Aberration proxies grant 40; Elite proxies grant 100. These amounts are engineering choices, not observed game values: they provide a nonzero repeatable combat income with an explicit higher Elite reward while original drop distributions remain unavailable. Apply the existing global fragment-gain pipeline to this credit independently of each Curio credit. Loss/fault grants nothing, Blessing suppression does not suppress fragments, and no reward RNG is drawn. Result verification, carry, all reward stages and automatic advance roll back together. Do not infer domain from source elite flags, enemy count or account reward displays. No boss policy is declared until that route exists.</t>
+          <t>VersionedProjectPolicy: after each verified won battle, credit the authored fixed base amount for the authenticated domain before separate Curio victory grants and Blessing generation. Combat and Aberration proxies grant 40; Elite proxies grant 100. These amounts are engineering choices, not observed game values: they provide a nonzero repeatable combat income with an explicit higher Elite reward while original drop distributions remain unavailable. Apply the existing global fragment-gain pipeline to this credit independently of each Curio credit. Loss/fault grants nothing, Blessing suppression does not suppress fragments, and no reward RNG is drawn. Result verification, carry, all reward stages and automatic advance roll back together. Do not infer domain from source elite flags, enemy count or account reward displays. Boss uses a separate explicit-policy row without enlarging the legacy three-label domain-choice route.</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>VersionedProjectPolicy: after each verified won battle, credit the authored fixed base amount for the authenticated domain before separate Curio victory grants and Blessing generation. Combat and Aberration proxies grant 40; Elite proxies grant 100. These amounts are engineering choices, not observed game values: they provide a nonzero repeatable combat income with an explicit higher Elite reward while original drop distributions remain unavailable. Apply the existing global fragment-gain pipeline to this credit independently of each Curio credit. Loss/fault grants nothing, Blessing suppression does not suppress fragments, and no reward RNG is drawn. Result verification, carry, all reward stages and automatic advance roll back together. Do not infer domain from source elite flags, enemy count or account reward displays. No boss policy is declared until that route exists.</t>
+          <t>VersionedProjectPolicy: after each verified won battle, credit the authored fixed base amount for the authenticated domain before separate Curio victory grants and Blessing generation. Combat and Aberration proxies grant 40; Elite proxies grant 100. These amounts are engineering choices, not observed game values: they provide a nonzero repeatable combat income with an explicit higher Elite reward while original drop distributions remain unavailable. Apply the existing global fragment-gain pipeline to this credit independently of each Curio credit. Loss/fault grants nothing, Blessing suppression does not suppress fragments, and no reward RNG is drawn. Result verification, carry, all reward stages and automatic advance roll back together. Do not infer domain from source elite flags, enemy count or account reward displays. Boss uses a separate explicit-policy row without enlarging the legacy three-label domain-choice route.</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>VersionedProjectPolicy: after each verified won battle, credit the authored fixed base amount for the authenticated domain before separate Curio victory grants and Blessing generation. Combat and Aberration proxies grant 40; Elite proxies grant 100. These amounts are engineering choices, not observed game values: they provide a nonzero repeatable combat income with an explicit higher Elite reward while original drop distributions remain unavailable. Apply the existing global fragment-gain pipeline to this credit independently of each Curio credit. Loss/fault grants nothing, Blessing suppression does not suppress fragments, and no reward RNG is drawn. Result verification, carry, all reward stages and automatic advance roll back together. Do not infer domain from source elite flags, enemy count or account reward displays. No boss policy is declared until that route exists.</t>
+          <t>VersionedProjectPolicy: after each verified won battle, credit the authored fixed base amount for the authenticated domain before separate Curio victory grants and Blessing generation. Combat and Aberration proxies grant 40; Elite proxies grant 100. These amounts are engineering choices, not observed game values: they provide a nonzero repeatable combat income with an explicit higher Elite reward while original drop distributions remain unavailable. Apply the existing global fragment-gain pipeline to this credit independently of each Curio credit. Loss/fault grants nothing, Blessing suppression does not suppress fragments, and no reward RNG is drawn. Result verification, carry, all reward stages and automatic advance roll back together. Do not infer domain from source elite flags, enemy count or account reward displays. Boss uses a separate explicit-policy row without enlarging the legacy three-label domain-choice route.</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -11586,8 +11586,48 @@
       </c>
       <c r="J10" s="9" t="n"/>
     </row>
+    <row r="11">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>du.battle-fragments.boss</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>FixedVerifiedDomainCredit</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: credit 100 base fragments after a verified win in an explicitly bound Boss reward domain, before separate Curio victory grants, battle lifetimes and the existing provisional Blessing offer. This is an engineering choice, not an observed game amount or a claim of original Boss eligibility, AI, phases or drops. Use the same nonzero base as the existing Elite proxy to extend the bounded reward pipeline without inventing a higher Boss multiplier; the domains remain independently replaceable. Select the domain only from the immutable room binding, never from preset level, stage elite flags or an adapter label. Apply current global fragment-gain modifiers to this credit separately from each Curio credit. Loss/fault grants nothing; Blessing suppression does not suppress fragments; the fixed base draws no RNG. Verified result, carry, all grants and next-node initialization commit or roll back together. The three-label legacy domain-choice route remains unchanged.</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>Replace Boss amount, fixed versus random distribution, per-battle versus per-enemy timing, difficulty scaling, base Blessing pool and reward ordering independently when released current-profile drop programs or reproducible observations establish them. Alternatives are a zero Boss base, a larger Boss-specific constant or integer range sampling; none is proven by the inspected constants, source labels or public domain overview. This explicit 100-fragment policy has low parity confidence, preserves independent Boss-domain authentication, and must not terminalize original Boss programs or source obligations.</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>14|24|41|66</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:J10"/>
+  <autoFilter ref="A3:J11"/>
   <dataValidations count="4">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -35,6 +35,8 @@
     <sheet name="DomainLayout" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="DomainDecks" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="DomainCards" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="ShopStocks" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="ShopItems" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$76</definedName>
@@ -66,6 +68,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'DomainLayout'!$A$3:$L$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'DomainDecks'!$A$3:$J$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'DomainCards'!$A$3:$J$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'ShopStocks'!$A$3:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'ShopItems'!$A$3:$J$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25270,6 +25274,818 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuShopStocks</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>15003b1e2dd908c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="n"/>
+      <c r="J2" s="9" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="9" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuShopStockPolicy&gt;</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="n"/>
+      <c r="J4" s="9" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="n"/>
+      <c r="J6" s="9" t="n"/>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="9" t="n"/>
+      <c r="J7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.shop-stock.acquisition-policy</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>ExplicitFixedStockAndPriceBaseRewards</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Fixed policy stock demonstrating base Blessing and immediate Curio acquisition.</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>固定项目策略库存，包含基础祝福及会触发即时获得效果的奇物。</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: explicit three-item stock and positive fixed Fragment prices; one purchase per owner per logical room, no sampling, refresh or discount. Merchant membership, original prices and stock weights are unavailable. Reward source links prove identities only. Prices 50/70/40 preserve deterministic payment and mandatory reward coverage, not observed parity. Alternatives: disable shops or reuse unproven catalog pools; explicit stock keeps behavior replaceable without asserting membership. Original-parity confidence is unproven; data admission and Ordinary/Cyclical shop controller tests freeze this policy.</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Replace stock, price and admission fields when released merchant selectors or reproducible current-version observations establish exact membership, weights, costs, discounts, quantities and refresh. No default profile placement is implied.</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J8"/>
+  <dataValidations count="2">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="D8:D1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExplicitFixedStockAndPriceBaseRewards" promptTitle="DuShopStockPolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"ExplicitFixedStockAndPriceBaseRewards"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="8"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuShopItems</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>32462bf5e4f1062f</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>stock_id</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>ordinal</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>reward_kind</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>reward_key</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>stock_id</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>ordinal</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>reward_kind</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>reward_key</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>ref&lt;DuShopStocks.id&gt;</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuShopRewardKind&gt;</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n"/>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.shop-item.acquisition-policy.blessing</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Blessing</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.blessing.615130</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>du.shop-item.acquisition-policy.wax</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Curio</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.curio-state.9043</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>7|8|9</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>du.shop-item.acquisition-policy.fragments</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Curio</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.curio-state.9053</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>4|5|6</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J10"/>
+  <dataValidations count="3">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="E8:E1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="F8:F1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Blessing, Curio" promptTitle="DuShopRewardKind enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"Blessing,Curio"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -37,9 +37,10 @@
     <sheet name="DomainCards" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="ShopStocks" sheetId="30" state="visible" r:id="rId30"/>
     <sheet name="ShopItems" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="CoinRewards" sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -70,6 +71,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'DomainCards'!$A$3:$J$132</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'ShopStocks'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'ShopItems'!$A$3:$J$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'CoinRewards'!$A$3:$L$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -577,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4463,8 +4465,59 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="9" t="n"/>
+      <c r="B77" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>du.source.wealth-description</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapEN.json; hashes=6523492130013154265,12602106085340263013,12397529171261210903; RoguePersonaRoomCompType=6</t>
+        </is>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>afc6d0ff9eeb20d09042e61c311e60d4ed56e69757f1ac42466ca4840e6ed789</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K77" s="9" t="inlineStr">
+        <is>
+          <t>Current Wealth description establishes chests and facilities, plus increased rewards at higher levels; no exact chest amounts, counts or selectors.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K76"/>
+  <autoFilter ref="A3:K77"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -26086,6 +26139,588 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="9"/>
+    <col width="28" customWidth="1" style="5" min="10" max="10"/>
+    <col width="28" customWidth="1" style="5" min="11" max="11"/>
+    <col width="28" customWidth="1" style="5" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuCoinRewards</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>c4bf737b5b73e514</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>preset_source</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>preset_source</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuCoinRewardPolicy&gt;</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..5</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.coin-reward.preset-1008</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>FixedSingleChestCreditNoAmusementFacilities</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>One explicitly collected Wealth chest reward; amusement facilities remain unimplemented.</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>显式领取一次财富域宝箱碎片；游乐设施仍未实现。</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: one aggregate chest pickup per reviewed logical room, 100 base Fragments for selected level-one presets and 200 for the selected level-two preset. Exact amounts, chest counts, refresh and collection timing are unavailable. Explicit Collect credits through the existing active Curio gain pipeline; Leave grants nothing. No RNG, automatic entry payout, guessed original chest selector or facility outcome. Alternatives: disable pickup or substitute battle rewards; explicit fixed operands preserve a replaceable chest boundary and the known level-two increase. Original-parity confidence is unproven; data, atomic pickup and Ordinary/Cyclical controller fixtures freeze this policy.</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>Replace amount, count and timing when current released chest/level programs or reproducible observations establish them. Add facilities separately; this row does not complete Wealth gameplay or infer mask/room/NPC admission.</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>68|69|70</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>du.coin-reward.preset-1024</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>FixedSingleChestCreditNoAmusementFacilities</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>One explicitly collected Wealth chest reward; amusement facilities remain unimplemented.</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>显式领取一次财富域宝箱碎片；游乐设施仍未实现。</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: one aggregate chest pickup per reviewed logical room, 100 base Fragments for selected level-one presets and 200 for the selected level-two preset. Exact amounts, chest counts, refresh and collection timing are unavailable. Explicit Collect credits through the existing active Curio gain pipeline; Leave grants nothing. No RNG, automatic entry payout, guessed original chest selector or facility outcome. Alternatives: disable pickup or substitute battle rewards; explicit fixed operands preserve a replaceable chest boundary and the known level-two increase. Original-parity confidence is unproven; data, atomic pickup and Ordinary/Cyclical controller fixtures freeze this policy.</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>Replace amount, count and timing when current released chest/level programs or reproducible observations establish them. Add facilities separately; this row does not complete Wealth gameplay or infer mask/room/NPC admission.</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>68|69|70</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>du.coin-reward.preset-9008</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>9008</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>FixedSingleChestCreditNoAmusementFacilities</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>One explicitly collected Wealth chest reward; amusement facilities remain unimplemented.</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>显式领取一次财富域宝箱碎片；游乐设施仍未实现。</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: one aggregate chest pickup per reviewed logical room, 100 base Fragments for selected level-one presets and 200 for the selected level-two preset. Exact amounts, chest counts, refresh and collection timing are unavailable. Explicit Collect credits through the existing active Curio gain pipeline; Leave grants nothing. No RNG, automatic entry payout, guessed original chest selector or facility outcome. Alternatives: disable pickup or substitute battle rewards; explicit fixed operands preserve a replaceable chest boundary and the known level-two increase. Original-parity confidence is unproven; data, atomic pickup and Ordinary/Cyclical controller fixtures freeze this policy.</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>Replace amount, count and timing when current released chest/level programs or reproducible observations establish them. Add facilities separately; this row does not complete Wealth gameplay or infer mask/room/NPC admission.</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>68|69|70</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:L10"/>
+  <dataValidations count="3">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="E8:E1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 5." promptTitle="Integer range" prompt="Enter an integer from 1 to 5." type="whole">
+      <formula1>1</formula1>
+      <formula2>5</formula2>
+    </dataValidation>
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: FixedSingleChestCreditNoAmusementFacilities" promptTitle="DuCoinRewardPolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"FixedSingleChestCreditNoAmusementFacilities"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -38,9 +38,10 @@
     <sheet name="ShopStocks" sheetId="30" state="visible" r:id="rId30"/>
     <sheet name="ShopItems" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="CoinRewards" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="RewardOccurrences" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -72,6 +73,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'ShopStocks'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'ShopItems'!$A$3:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'CoinRewards'!$A$3:$L$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'RewardOccurrences'!$A$3:$L$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -579,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4516,8 +4518,59 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="9" t="n"/>
+      <c r="B78" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>du.source.reward-description</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapEN.json; hashes=14965428722118379034,9124085505769711186,13329877192670394962; RoguePersonaRoomCompType=8</t>
+        </is>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>afc6d0ff9eeb20d09042e61c311e60d4ed56e69757f1ac42466ca4840e6ed789</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K78" s="9" t="inlineStr">
+        <is>
+          <t>Current Reward description establishes one reward occurrence at level one; it does not establish candidate identities, pools or weights.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K77"/>
+  <autoFilter ref="A3:K78"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -26721,6 +26774,474 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="9"/>
+    <col width="28" customWidth="1" style="5" min="10" max="10"/>
+    <col width="28" customWidth="1" style="5" min="11" max="11"/>
+    <col width="28" customWidth="1" style="5" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuRewardOccurrences</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>0545eb170f7529e1</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>preset_source</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>occurrence_id</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>preset_source</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>occurrence_id</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>ref&lt;DuDecisionOccurrences.id&gt;</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuRewardOccurrencePolicy&gt;</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..5</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.reward-room.level-one-substitute</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>SingleExplicitRewardOnlySubstituteNoPoolSampling</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>One free authored reward occurrence at the reviewed level-one Reward card; original membership is unproven.</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>已审定的一级奖励卡执行一次免费奖励事件；所选事件的原版池归属未经证实。</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: select the already executable A Dash of Color program as a reward-only substitute for preset 1010, without claiming it belongs to the original Reward-type pool. The source-backed level-one count is one. Candidate identity, selection distribution and refresh are unavailable; no event-pool RNG or hidden NPC graph is invented. Its three existing policy choices grant 200 Fragments, two Curios or two Blessings through the shared acquisition pipeline. Alternatives are disabling the card or fabricating candidate weights; this bounded substitute preserves a real reward/finish/Leave boundary. Membership-parity confidence is unproven. Data admission and Ordinary/Cyclical sampled-card tests freeze the selected policy independently of the event's existing reward-selection policy.</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>Replace the substitute identity/selection when current released Reward event graphs or reproducible observations prove the preset's candidate pool and distribution. Other levels, fixed Reward rooms, NPC presentation and original pool parity remain unimplemented; raw neighboring presets are not current-profile admission evidence.</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>68|69|71|1|2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:L8"/>
+  <dataValidations count="3">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="E8:E1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 5." promptTitle="Integer range" prompt="Enter an integer from 1 to 5." type="whole">
+      <formula1>1</formula1>
+      <formula2>5</formula2>
+    </dataValidation>
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: SingleExplicitRewardOnlySubstituteNoPoolSampling" promptTitle="DuRewardOccurrencePolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"SingleExplicitRewardOnlySubstituteNoPoolSampling"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -39,9 +39,10 @@
     <sheet name="ShopItems" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="CoinRewards" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="RewardOccurrences" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="AdventureRewards" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -74,6 +75,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'ShopItems'!$A$3:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'CoinRewards'!$A$3:$L$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'RewardOccurrences'!$A$3:$L$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'AdventureRewards'!$A$3:$M$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -581,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4569,8 +4571,59 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="9" t="n"/>
+      <c r="B79" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>du.source.adventure-description</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapEN.json; hashes=3196724585769076860,12097919368463049754,10649614652576832174; RoguePersonaRoomCompType=9</t>
+        </is>
+      </c>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>afc6d0ff9eeb20d09042e61c311e60d4ed56e69757f1ac42466ca4840e6ed789</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K79" s="9" t="inlineStr">
+        <is>
+          <t>Current Adventure description bounds level-one rewards at three chests; exact payouts and challenge selection/scoring/timing are unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K78"/>
+  <autoFilter ref="A3:K79"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -27242,6 +27295,515 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="9"/>
+    <col width="28" customWidth="1" style="5" min="10" max="10"/>
+    <col width="28" customWidth="1" style="5" min="11" max="11"/>
+    <col width="28" customWidth="1" style="5" min="12" max="12"/>
+    <col width="28" customWidth="1" style="5" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuAdventureRewards</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>6056789b0fbbcef6</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>preset_source</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>maximum_chests</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>fragments_per_chest</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>preset_source</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>maximum_chests</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>fragments_per_chest</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuAdventureRewardPolicy&gt;</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..5</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..3</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.adventure-reward.level-one-aggregate</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>ExternalEarnedChestCountAggregateFragmentsOnly</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>External earned-chest count settles Fragments; challenge simulation remains unimplemented.</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>外部输入已赢得宝箱数并结算碎片；挑战模拟仍未实现。</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: explicit external earned count 0..3; 100 base Fragments per chest, aggregated before the current active Curio gain pipeline and its integer rounding. Exact reward composition, amounts and timing are unavailable after bounded released-source research. No RNG, automatic entry payout, guessed challenge pool, score/time simulation or higher-level reward. Alternatives: disable settlement or guess original mini-games; the explicit host result preserves the known level-one bound without inventing gameplay. Original-parity confidence is unproven. Production Sora, all-count settlement, overflow/rejection and fresh-definition fixtures freeze policy.</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>Replace amount/composition/rounding/timing when current released chest programs or reproducible observations establish them. Implement source-selected challenges and Adventure-specific Curio time/extra-chest/rank effects separately; this row does not complete Adventure gameplay.</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>68|69|72</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:M8"/>
+  <dataValidations count="4">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="E8:E1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 5." promptTitle="Integer range" prompt="Enter an integer from 1 to 5." type="whole">
+      <formula1>1</formula1>
+      <formula2>5</formula2>
+    </dataValidation>
+    <dataValidation sqref="F8:F1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 3." promptTitle="Integer range" prompt="Enter an integer from 1 to 3." type="whole">
+      <formula1>1</formula1>
+      <formula2>3</formula2>
+    </dataValidation>
+    <dataValidation sqref="H8:H1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExternalEarnedChestCountAggregateFragmentsOnly" promptTitle="DuAdventureRewardPolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"ExternalEarnedChestCountAggregateFragmentsOnly"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -40,9 +40,10 @@
     <sheet name="CoinRewards" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="RewardOccurrences" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="AdventureRewards" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="WeightedCurioSplashes" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -76,6 +77,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'CoinRewards'!$A$3:$L$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'RewardOccurrences'!$A$3:$L$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'AdventureRewards'!$A$3:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'WeightedCurioSplashes'!$A$3:$N$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -583,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4622,8 +4624,212 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="9" t="n"/>
+      <c r="B80" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-splash.hex</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/RogueTournHex.json; HexID=1001; TournMode=Tourn3; MazeBuffID=633401; AvatarType=Rogue; DisplayID=1014</t>
+        </is>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>51e91a6f53ab0545330e477d806a165108f6c7e5e70ad52b02f92c1dc4d36455</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K80" s="9" t="inlineStr">
+        <is>
+          <t>Exact current membership, generic MazeBuff join and operand. The missing RogueMazeBuff row is not absence of released MazeBuff data. Trigger cardinality and copied-damage execution are separate policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n"/>
+      <c r="B81" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-splash.maze-buff</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/MazeBuff.json; ID=633401; Lv=1; ParamList[0].Value=0.3; InBattleBindingType=StageAbilityBeforeCharacterBorn; InBattleBindingKey=StageAbility_633401</t>
+        </is>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>2fab98b723ee20d8798c68e200cc9c3704abc347b0983b2955cbd40b85bfeeac</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K81" s="9" t="inlineStr">
+        <is>
+          <t>Exact current membership, generic MazeBuff join and operand. The missing RogueMazeBuff row is not absence of released MazeBuff data. Trigger cardinality and copied-damage execution are separate policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="n"/>
+      <c r="B82" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-splash.text-en</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapEN.json; hash=8678628073262894449; Hunt attack damage copies thirty percent to adjacent targets</t>
+        </is>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>afc6d0ff9eeb20d09042e61c311e60d4ed56e69757f1ac42466ca4840e6ed789</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K82" s="9" t="inlineStr">
+        <is>
+          <t>Exact current membership, generic MazeBuff join and operand. The missing RogueMazeBuff row is not absence of released MazeBuff data. Trigger cardinality and copied-damage execution are separate policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="n"/>
+      <c r="B83" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-splash.text-zh</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapCHS.json; hash=8678628073262894449; Hunt attack damage copies thirty percent to adjacent targets</t>
+        </is>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>ec49e07932b4ed8aba9679e247d8e554ca69e831fea7931d94682551de567147</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K83" s="9" t="inlineStr">
+        <is>
+          <t>Exact current membership, generic MazeBuff join and operand. The missing RogueMazeBuff row is not absence of released MazeBuff data. Trigger cardinality and copied-damage execution are separate policy.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K79"/>
+  <autoFilter ref="A3:K83"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -27804,6 +28010,546 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="9"/>
+    <col width="28" customWidth="1" style="5" min="10" max="10"/>
+    <col width="28" customWidth="1" style="5" min="11" max="11"/>
+    <col width="28" customWidth="1" style="5" min="12" max="12"/>
+    <col width="28" customWidth="1" style="5" min="13" max="13"/>
+    <col width="28" customWidth="1" style="5" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuWeightedCurioSplashes</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>e8562d10ab8b36e1</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="9" t="n"/>
+      <c r="N1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>character_path</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>fraction_parameter</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>damage_fraction</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>character_path</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>fraction_parameter</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>damage_fraction</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuWeightedCurioSplashPolicy&gt;</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-splash.ten-light-years</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1001</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>633401</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Rogue</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>HitCalculatedCopyAdjacentTrueDamage</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>Hunt attack damage copies 30% of calculated damage to adjacent enemies.</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>巡猎角色攻击造成伤害后，向相邻敌人复制计算伤害的 30%。</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: bind only mapped player combatants whose immutable build Path is Hunt. Observe each positive ordinary Ability damage event with an action, once per event, at the shared AfterEvent phase. Copy its calculated integer damage, including shield-absorbed and overkill portions, multiplied by the exact 0.3 with checked fixed-point floor. Select alive present opposing units exactly one formation slot from the damaged target in current state, ordered by formation and stable ID. Emit shared TrueDamage operations, which can defeat and bypass source/target multipliers and critical rolls; no recursive splash, RNG or live Activity mutation. Multiple hits and multiple struck targets each retain their own event. A defeated primary remains the adjacency origin. Equipment lasts until replacement/unequip or Run teardown; each immutable battle assembles a fresh source-attributed rule. Linked or newly summoned unit inheritance is not implicit.</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>Replace trigger cardinality, source-class/action eligibility, calculated versus effective-HP basis, damage category, shield/overkill handling, target presence/adjacency snapshot and summon inheritance independently when released executable programs or reproducible observations establish them. Alternatives include per-action aggregation and source-unboosted elemental additional damage, which would reapply target factors to already-calculated damage. Hidden timing/category confidence is low; this is not observed parity. Preserve released Hunt eligibility and thirty percent. Forge placement/offers and encoded equipment-command replay remain separate pending requirements.</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>73|74|75|76</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:N8"/>
+  <dataValidations count="3">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="I8:I1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: HitCalculatedCopyAdjacentTrueDamage" promptTitle="DuWeightedCurioSplashPolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"HitCalculatedCopyAdjacentTrueDamage"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -41,9 +41,10 @@
     <sheet name="RewardOccurrences" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="AdventureRewards" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="WeightedCurioSplashes" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="WeightedCurioShields" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -78,6 +79,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'RewardOccurrences'!$A$3:$L$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'AdventureRewards'!$A$3:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'WeightedCurioSplashes'!$A$3:$N$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'WeightedCurioShields'!$A$3:$P$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -585,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4828,8 +4830,212 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="9" t="n"/>
+      <c r="B84" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-shield.hex</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/RogueTournHex.json; HexID=1002; TournMode=Tourn3; MazeBuffID=633402; AvatarType=Shaman; DisplayID=1015</t>
+        </is>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>51e91a6f53ab0545330e477d806a165108f6c7e5e70ad52b02f92c1dc4d36455</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K84" s="9" t="inlineStr">
+        <is>
+          <t>Released current Hex join, Harmony eligibility, ally-directed action kinds, respective maximum-HP basis, 0.35 fraction and two-turn duration. Trigger phase, refresh, scope and coexistence are separate policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="n"/>
+      <c r="B85" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-shield.maze-buff</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/MazeBuff.json; ID=633402; Lv=1; ParamList[0].Value=0.35; ParamList[1].Value=2; InBattleBindingKey=StageAbility_633402</t>
+        </is>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>2fab98b723ee20d8798c68e200cc9c3704abc347b0983b2955cbd40b85bfeeac</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K85" s="9" t="inlineStr">
+        <is>
+          <t>Released current Hex join, Harmony eligibility, ally-directed action kinds, respective maximum-HP basis, 0.35 fraction and two-turn duration. Trigger phase, refresh, scope and coexistence are separate policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="n"/>
+      <c r="B86" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-shield.text-en</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapEN.json; hash=18303557854201536316; Harmony Basic/Skill/Ultimate on allies shields all allies using respective maximum HP for two turns</t>
+        </is>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>afc6d0ff9eeb20d09042e61c311e60d4ed56e69757f1ac42466ca4840e6ed789</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K86" s="9" t="inlineStr">
+        <is>
+          <t>Released current Hex join, Harmony eligibility, ally-directed action kinds, respective maximum-HP basis, 0.35 fraction and two-turn duration. Trigger phase, refresh, scope and coexistence are separate policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="n"/>
+      <c r="B87" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-shield.text-zh</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapCHS.json; hash=18303557854201536316; Harmony Basic/Skill/Ultimate on allies shields all allies using respective maximum HP for two turns</t>
+        </is>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>ec49e07932b4ed8aba9679e247d8e554ca69e831fea7931d94682551de567147</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K87" s="9" t="inlineStr">
+        <is>
+          <t>Released current Hex join, Harmony eligibility, ally-directed action kinds, respective maximum-HP basis, 0.35 fraction and two-turn duration. Trigger phase, refresh, scope and coexistence are separate policy.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K83"/>
+  <autoFilter ref="A3:K87"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -28550,6 +28756,616 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="9"/>
+    <col width="28" customWidth="1" style="5" min="10" max="10"/>
+    <col width="28" customWidth="1" style="5" min="11" max="11"/>
+    <col width="28" customWidth="1" style="5" min="12" max="12"/>
+    <col width="28" customWidth="1" style="5" min="13" max="13"/>
+    <col width="28" customWidth="1" style="5" min="14" max="14"/>
+    <col width="28" customWidth="1" style="5" min="15" max="15"/>
+    <col width="28" customWidth="1" style="5" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuWeightedCurioShields</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>ff5977a6e4b4c06f</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="9" t="n"/>
+      <c r="N1" s="9" t="n"/>
+      <c r="O1" s="9" t="n"/>
+      <c r="P1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>character_path</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>fraction_parameter</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>shield_fraction</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>duration_parameter</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>duration_turns</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>character_path</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>fraction_parameter</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>shield_fraction</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>duration_parameter</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>duration_turns</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuWeightedCurioShieldPolicy&gt;</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..65535</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-shield.silent-song</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1002</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>633402</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Shaman</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>AllyActionResolvedReplaceTargetTurnShield</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>Harmony ally-directed Basic, Skill or Ultimate gives each living present ally a two-turn shield based on 35% of their own maximum HP.</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>同谐角色对我方施放普攻、战技或终结技后，为在场存活队友提供各自生命上限 35% 的两回合护盾。</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: bind action producers only to mapped player characters whose immutable build Path is Harmony. Observe ActionResolved at AfterAction once per action, require actor owner, Basic/Skill/Ultimate kind and nonempty committed allied targets; this includes self and team-wide actions without a controller primary. Affect current alive present team units in formation/stable-ID order, including the caster. Snapshot each recipient's current maximum HP at application; multiply by exact 0.35 with checked fixed-point floor through the shared shield formula (normal shield boosts remain applicable). Remove only this definition's prior shield/effect, then create one non-dispellable replacement shield with duration two at TargetTurnEnd; the shared clock includes an already-running recipient turn. Every mapped recipient owns expiry cleanup, independent of caster survival; delayed old-effect removal cannot clear a replacement. Other shields coexist using ConcurrentLargest absorption. No RNG, damage/heal-only inference, enemy-action activation or live Activity mutation. No implicit linked/new summon inheritance. Equipment remains Run-scoped; battle effects teardown with their battle/recipient.</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>Hidden phase, committed-target versus declaration-target admission, current alive/present recipient scope, immediate target-turn tick, shield-boost handling, refresh across multiple Harmony casters and coexistence are low-confidence policy, not observed parity. Alternatives include declaration-time shield, independent per-caster layers or refresh-only duration. Replace each independently using released executable programs or reproducible current observations; preserve exact Harmony, action kinds, ally direction (including self/team-wide actions), per-recipient maximum HP, 0.35 and two turns. Forge admission and encoded equipment-command replay remain pending.</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>77|78|79|80</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:P8"/>
+  <dataValidations count="5">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="I8:I1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 65535." promptTitle="Integer range" prompt="Enter an integer from 1 to 65535." type="whole">
+      <formula1>1</formula1>
+      <formula2>65535</formula2>
+    </dataValidation>
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AllyActionResolvedReplaceTargetTurnShield" promptTitle="DuWeightedCurioShieldPolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AllyActionResolvedReplaceTargetTurnShield"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -42,9 +42,10 @@
     <sheet name="AdventureRewards" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="WeightedCurioSplashes" sheetId="35" state="visible" r:id="rId35"/>
     <sheet name="WeightedCurioShields" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="WeightedCurioAttackDebuffs" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -80,6 +81,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'AdventureRewards'!$A$3:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'WeightedCurioSplashes'!$A$3:$N$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'WeightedCurioShields'!$A$3:$P$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'WeightedCurioAttackDebuffs'!$A$3:$R$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -587,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5034,8 +5036,212 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="9" t="n"/>
+      <c r="B88" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-attack-debuff.hex</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G88" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/RogueTournHex.json; HexID=1014; TournMode=Tourn3; MazeBuffID=633414; AvatarType=Warrior|Warlock; DisplayID=1021</t>
+        </is>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>51e91a6f53ab0545330e477d806a165108f6c7e5e70ad52b02f92c1dc4d36455</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K88" s="9" t="inlineStr">
+        <is>
+          <t>Released Tourn3 Hex join, both Paths, attack condition, attacked enemy direction, 0.2 advance, 0.3 reduction and one turn. Hidden phase, formula coverage, refresh and dispel remain separate policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="n"/>
+      <c r="B89" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-attack-debuff.maze-buff</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/MazeBuff.json; ID=633414; Lv=1; ParamList[0].Value=0.2; ParamList[1].Value=0.3; ParamList[2].Value=1; InBattleBindingKey=StageAbility_633414</t>
+        </is>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>2fab98b723ee20d8798c68e200cc9c3704abc347b0983b2955cbd40b85bfeeac</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K89" s="9" t="inlineStr">
+        <is>
+          <t>Released Tourn3 Hex join, both Paths, attack condition, attacked enemy direction, 0.2 advance, 0.3 reduction and one turn. Hidden phase, formula coverage, refresh and dispel remain separate policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="n"/>
+      <c r="B90" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-attack-debuff.text-en</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapEN.json; hash=4217722633224787979; Destruction or Nihility attack advances attacked enemy and reduces outgoing damage for one turn</t>
+        </is>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>afc6d0ff9eeb20d09042e61c311e60d4ed56e69757f1ac42466ca4840e6ed789</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K90" s="9" t="inlineStr">
+        <is>
+          <t>Released Tourn3 Hex join, both Paths, attack condition, attacked enemy direction, 0.2 advance, 0.3 reduction and one turn. Hidden phase, formula coverage, refresh and dispel remain separate policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="n"/>
+      <c r="B91" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-attack-debuff.text-zh</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G91" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapCHS.json; hash=4217722633224787979; Destruction or Nihility attack advances attacked enemy and reduces outgoing damage for one turn</t>
+        </is>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>ec49e07932b4ed8aba9679e247d8e554ca69e831fea7931d94682551de567147</t>
+        </is>
+      </c>
+      <c r="J91" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K91" s="9" t="inlineStr">
+        <is>
+          <t>Released Tourn3 Hex join, both Paths, attack condition, attacked enemy direction, 0.2 advance, 0.3 reduction and one turn. Hidden phase, formula coverage, refresh and dispel remain separate policy.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K87"/>
+  <autoFilter ref="A3:K91"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -29366,6 +29572,684 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="9"/>
+    <col width="28" customWidth="1" style="5" min="10" max="11"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" style="5" min="12" max="12"/>
+    <col width="28" customWidth="1" style="5" min="13" max="13"/>
+    <col width="28" customWidth="1" style="5" min="14" max="14"/>
+    <col width="28" customWidth="1" style="5" min="15" max="15"/>
+    <col width="28" customWidth="1" style="5" min="16" max="16"/>
+    <col width="28" customWidth="1" style="5" min="17" max="17"/>
+    <col width="28" customWidth="1" style="5" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuWeightedCurioAttackDebuffs</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>681201f862b66467</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="9" t="n"/>
+      <c r="N1" s="9" t="n"/>
+      <c r="O1" s="9" t="n"/>
+      <c r="P1" s="9" t="n"/>
+      <c r="Q1" s="9" t="n"/>
+      <c r="R1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>character_paths</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>advance_parameter</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>advance_fraction</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>reduction_parameter</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>reduction_fraction</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>duration_parameter</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>duration_turns</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="Q2" s="10" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>character_paths</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>advance_parameter</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>advance_fraction</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>reduction_parameter</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>reduction_fraction</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>duration_parameter</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>duration_turns</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="Q3" s="12" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="R3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuCurioAttackDebuffPolicy&gt;</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="R4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="Q5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..65535</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="n"/>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-attack-debuff.automated-experience</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1014</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>633414</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Warrior|Warlock</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>AttackResolvedAdvanceAndTargetTurnFinalReduction</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>After a Destruction or Nihility attack, attacked enemies advance 20% and deal 30% less damage for one turn.</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>毁灭或虚无角色攻击后，受击敌人行动提前 20%，造成伤害降低 30%，持续一回合。</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: bind only mapped Destruction/Nihility player producers. Observe ActionResolved at AfterAction with Attack tag, owner actor and committed opposing targets; once per action, not hit. Visit current living present targets in formation/stable-ID order. Advance each through shared AdvanceAction by exact 0.2; replace this definition's prior effect with one guaranteed non-dispellable Debuff, duration one at TargetTurnEnd (an already-running target turn counts). Six outgoing purposes OrdinaryDamage/Dot/AdditionalDamage/ElationDamage/Break/SuperBreak use a dynamic source-owned final product factor 1-0.3; no ATK or incoming-damage change. True damage, explicit damage overrides and deliberately unboosted operations retain their shared bypass semantics. Refresh replaces across casters, does not multiply reductions; unrelated modifiers coexist in separate groups. No resistance roll, RNG, recursive attack, implicit summon inheritance or live Activity mutation. Equipment is Run-scoped; effects and modifiers teardown with battle/target.</t>
+        </is>
+      </c>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t>Hidden phase, committed versus declared targets, dead/absent admission, formula position/category coverage, dispel, immediate turn tick and cross-caster replacement are low-confidence policy, not observed parity. Alternatives: declaration-time trigger, source Weaken aggregation (not final product), break exemption, dispellable debuff or independent caster layers. Chosen policy preserves both exact effects and bounded shared execution; affected tests weighted_curio_attack_debuff and its production data rejection fixtures. Replace each field independently with released executable programs or reproducible current traces; preserve both Paths, attack/enemy direction, 0.2/0.3/one turn. Forge menus and encoded equipment replay remain pending.</t>
+        </is>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>81|82|83|84</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:R8"/>
+  <dataValidations count="6">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="I8:I1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 65535." promptTitle="Integer range" prompt="Enter an integer from 1 to 65535." type="whole">
+      <formula1>1</formula1>
+      <formula2>65535</formula2>
+    </dataValidation>
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AttackResolvedAdvanceAndTargetTurnFinalReduction" promptTitle="DuCurioAttackDebuffPolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AttackResolvedAdvanceAndTargetTurnFinalReduction"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -43,9 +43,10 @@
     <sheet name="WeightedCurioSplashes" sheetId="35" state="visible" r:id="rId35"/>
     <sheet name="WeightedCurioShields" sheetId="36" state="visible" r:id="rId36"/>
     <sheet name="WeightedCurioAttackDebuffs" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="WeightedCurioSupportAttacks" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -82,6 +83,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'WeightedCurioSplashes'!$A$3:$N$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'WeightedCurioShields'!$A$3:$P$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'WeightedCurioAttackDebuffs'!$A$3:$R$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'WeightedCurioSupportAttacks'!$A$3:$R$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -589,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5240,8 +5242,212 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="9" t="n"/>
+      <c r="B92" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-support-attack.hex</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G92" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/RogueTournHex.json; HexID=1017; TournMode=Tourn3; MazeBuffID=633417; AvatarType=Shaman|Priest|Knight; DisplayID=1020</t>
+        </is>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>51e91a6f53ab0545330e477d806a165108f6c7e5e70ad52b02f92c1dc4d36455</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K92" s="9" t="inlineStr">
+        <is>
+          <t>Released Tourn3 join: three Paths; each roster character gives 0.15 crit rate and 0.3 crit damage to eligible characters; attack additional damage is 1 times Max HP plus DEF plus ATK. Hidden lifecycle and damage details remain policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="n"/>
+      <c r="B93" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-support-attack.maze-buff</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G93" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/MazeBuff.json; ID=633417; Lv=1; ParamList[0].Value=0.15; ParamList[1].Value=0.3; ParamList[2].Value=1; InBattleBindingKey=StageAbility_633417</t>
+        </is>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>2fab98b723ee20d8798c68e200cc9c3704abc347b0983b2955cbd40b85bfeeac</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K93" s="9" t="inlineStr">
+        <is>
+          <t>Released Tourn3 join: three Paths; each roster character gives 0.15 crit rate and 0.3 crit damage to eligible characters; attack additional damage is 1 times Max HP plus DEF plus ATK. Hidden lifecycle and damage details remain policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="n"/>
+      <c r="B94" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-support-attack.text-en</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapEN.json; hash=18107300873516931386; Harmony Abundance Preservation roster count grants their characters crit and attack additional damage from Max HP plus DEF plus ATK</t>
+        </is>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>afc6d0ff9eeb20d09042e61c311e60d4ed56e69757f1ac42466ca4840e6ed789</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K94" s="9" t="inlineStr">
+        <is>
+          <t>Released Tourn3 join: three Paths; each roster character gives 0.15 crit rate and 0.3 crit damage to eligible characters; attack additional damage is 1 times Max HP plus DEF plus ATK. Hidden lifecycle and damage details remain policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="n"/>
+      <c r="B95" s="9" t="n">
+        <v>88</v>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-support-attack.text-zh</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapCHS.json; hash=18107300873516931386; Harmony Abundance Preservation roster count grants their characters crit and attack additional damage from Max HP plus DEF plus ATK</t>
+        </is>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>ec49e07932b4ed8aba9679e247d8e554ca69e831fea7931d94682551de567147</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K95" s="9" t="inlineStr">
+        <is>
+          <t>Released Tourn3 join: three Paths; each roster character gives 0.15 crit rate and 0.3 crit damage to eligible characters; attack additional damage is 1 times Max HP plus DEF plus ATK. Hidden lifecycle and damage details remain policy.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K91"/>
+  <autoFilter ref="A3:K95"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -30250,6 +30456,682 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="9"/>
+    <col width="28" customWidth="1" style="5" min="10" max="11"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" style="5" min="12" max="12"/>
+    <col width="28" customWidth="1" style="5" min="13" max="13"/>
+    <col width="28" customWidth="1" style="5" min="14" max="14"/>
+    <col width="28" customWidth="1" style="5" min="15" max="15"/>
+    <col width="28" customWidth="1" style="5" min="16" max="16"/>
+    <col width="28" customWidth="1" style="5" min="17" max="17"/>
+    <col width="28" customWidth="1" style="5" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuWeightedCurioSupportAttacks</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>8c8d15811d86d472</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="9" t="n"/>
+      <c r="N1" s="9" t="n"/>
+      <c r="O1" s="9" t="n"/>
+      <c r="P1" s="9" t="n"/>
+      <c r="Q1" s="9" t="n"/>
+      <c r="R1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>character_paths</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>crit_rate_parameter</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>crit_rate_fraction</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>crit_damage_parameter</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>crit_damage_fraction</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>additional_parameter</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>additional_multiplier</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="Q2" s="10" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>character_paths</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>crit_rate_parameter</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>crit_rate_fraction</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>crit_damage_parameter</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>crit_damage_fraction</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>additional_parameter</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>additional_multiplier</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="Q3" s="12" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="R3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuCurioSupportAttackPolicy&gt;</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="R4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="Q5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="n"/>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-support-attack.the-story-presently</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1017</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>633417</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Shaman|Priest|Knight</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>RosterCountCritAndAttackResolvedAdditional</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>Each Harmony, Abundance or Preservation teammate grants those Paths 15% CRIT Rate and 30% CRIT DMG; their attacks add damage equal to Max HP plus DEF plus ATK.</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>每名同谐、丰饶或存护队员使上述命途角色暴击率提高 15%、暴击伤害提高 30%；攻击后造成生命上限、防御力与攻击力之和的附加伤害。</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: count the immutable mapped player character roster at battle assembly, including down/absent characters but excluding linked actors and summons. Bind only Harmony/Abundance/Preservation players. Two battle-lifetime flat Stat modifiers add count times exact crit operands, with unique-per-source groups and no extra cap (shared crit sampling bounds apply). Owner ActionResolved at AfterAction with Attack tag, once per action, visits committed opposing alive/present targets in formation/stable-ID order. Additional damage uses the owner's dynamic effective HP stat plus DEF plus ATK, multiplied by exact 1, shared nearest-ties-even arithmetic and final damage floor. Use actor Basic element, shared AdditionalDamage formula modifiers, no crit or toughness reduction, can defeat. No recursive action, new summon inheritance or live Activity mutation. Unequip affects later snapshots only.</t>
+        </is>
+      </c>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t>Hidden roster life/presence counting, phase, target cardinality, stat snapshot, element, critical eligibility and toughness are low-confidence policy, not observed parity. Alternatives: live eligible-count updates, once per hit, only primary target, application snapshot, attack-event element, crit-capable additional damage or toughness damage. Selected behavior preserves all displayed operands and bounds shared execution; affected tests weighted_curio_support_attack and production data rejection fixtures. Replace each field independently with released programs or reproducible current traces. Do not substitute Human Comedy 0.25/0.75 or Remembrance variants for this Tourn3 row; Forge admission and equipment replay remain pending.</t>
+        </is>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>85|86|87|88</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:R8"/>
+  <dataValidations count="5">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="I8:I1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: RosterCountCritAndAttackResolvedAdditional" promptTitle="DuCurioSupportAttackPolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"RosterCountCritAndAttackResolvedAdditional"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -44,9 +44,10 @@
     <sheet name="WeightedCurioShields" sheetId="36" state="visible" r:id="rId36"/>
     <sheet name="WeightedCurioAttackDebuffs" sheetId="37" state="visible" r:id="rId37"/>
     <sheet name="WeightedCurioSupportAttacks" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="WeightedCurioPrayers" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -84,6 +85,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'WeightedCurioShields'!$A$3:$P$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'WeightedCurioAttackDebuffs'!$A$3:$R$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'WeightedCurioSupportAttacks'!$A$3:$R$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'WeightedCurioPrayers'!$A$3:$R$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -591,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5446,8 +5448,212 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="9" t="n"/>
+      <c r="B96" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-prayer.hex</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G96" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/RogueTournHex.json; HexID=1004; TournMode=Tourn3; MazeBuffID=633404; AvatarType=Mage|Warlock; DisplayID=1022</t>
+        </is>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>51e91a6f53ab0545330e477d806a165108f6c7e5e70ad52b02f92c1dc4d36455</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K96" s="9" t="inlineStr">
+        <is>
+          <t>Released Tourn3 join and exact 0.6 maximum HP, 0.15 current HP consumption and 0.25 maximum HP shield operands. Hidden stacking, entry adjustment, phase, floor and shield lifetime remain policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="n"/>
+      <c r="B97" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-prayer.maze-buff</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G97" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/MazeBuff.json; ID=633404; Lv=1; ParamList[0].Value=0.6; ParamList[1].Value=0.15; ParamList[2].Value=0.25; InBattleBindingKey=StageAbility_633404</t>
+        </is>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>2fab98b723ee20d8798c68e200cc9c3704abc347b0983b2955cbd40b85bfeeac</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K97" s="9" t="inlineStr">
+        <is>
+          <t>Released Tourn3 join and exact 0.6 maximum HP, 0.15 current HP consumption and 0.25 maximum HP shield operands. Hidden stacking, entry adjustment, phase, floor and shield lifetime remain policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="n"/>
+      <c r="B98" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-prayer.text-en</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G98" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapEN.json; hash=16252001468855081658; Erudition Nihility maximum HP bonus and turn-start current HP consumption followed by maximum-HP shield</t>
+        </is>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>afc6d0ff9eeb20d09042e61c311e60d4ed56e69757f1ac42466ca4840e6ed789</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K98" s="9" t="inlineStr">
+        <is>
+          <t>Released Tourn3 join and exact 0.6 maximum HP, 0.15 current HP consumption and 0.25 maximum HP shield operands. Hidden stacking, entry adjustment, phase, floor and shield lifetime remain policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="n"/>
+      <c r="B99" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-prayer.text-zh</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G99" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapCHS.json; hash=16252001468855081658; Erudition Nihility maximum HP bonus and turn-start current HP consumption followed by maximum-HP shield</t>
+        </is>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>ec49e07932b4ed8aba9679e247d8e554ca69e831fea7931d94682551de567147</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K99" s="9" t="inlineStr">
+        <is>
+          <t>Released Tourn3 join and exact 0.6 maximum HP, 0.15 current HP consumption and 0.25 maximum HP shield operands. Hidden stacking, entry adjustment, phase, floor and shield lifetime remain policy.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K95"/>
+  <autoFilter ref="A3:K99"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -31132,6 +31338,682 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="8"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="9"/>
+    <col width="28" customWidth="1" style="5" min="10" max="11"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" style="5" min="12" max="12"/>
+    <col width="28" customWidth="1" style="5" min="13" max="13"/>
+    <col width="28" customWidth="1" style="5" min="14" max="14"/>
+    <col width="28" customWidth="1" style="5" min="15" max="15"/>
+    <col width="28" customWidth="1" style="5" min="16" max="16"/>
+    <col width="28" customWidth="1" style="5" min="17" max="17"/>
+    <col width="28" customWidth="1" style="5" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuWeightedCurioPrayers</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>167c53616f8ef2cd</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="9" t="n"/>
+      <c r="N1" s="9" t="n"/>
+      <c r="O1" s="9" t="n"/>
+      <c r="P1" s="9" t="n"/>
+      <c r="Q1" s="9" t="n"/>
+      <c r="R1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>character_paths</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>hp_parameter</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>hp_fraction</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>consume_parameter</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>consume_fraction</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>shield_parameter</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>shield_fraction</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="Q2" s="10" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>character_paths</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>hp_parameter</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>hp_fraction</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>consume_parameter</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>consume_fraction</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>shield_parameter</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>shield_fraction</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="Q3" s="12" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="R3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuCurioPrayerPolicy&gt;</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="R4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="Q5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="n"/>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-prayer.road-of-prayers</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1004</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>633404</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Mage|Warlock</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>EntryHpAndTurnStartConsumeShield</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>Erudition and Nihility characters gain 60% maximum HP; their turn starts consume 15% current HP and grant a shield for 25% maximum HP.</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>智识、虚无角色生命上限提高 60%；回合开始时消耗 15% 当前生命值并获得等同于 25% 生命上限的护盾。</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: use the immutable resolved entry HP capacity as the bonus basis, adding floor(base times 0.6) exactly once to a fresh sealed ParticipantSpec. Preserve every build field and locked build digest; do not add a second HP modifier. No extra healing of carried HP: first entry uses explicit initial state or full new capacity; later entry follows the declared Activity carry policies, including clamping on unequip. Bind mapped Erudition/Nihility player characters, with no linked/summon inheritance. Owner TurnStarted AfterEvent, once per Turn, priority zero and alive/present owner selector: consume floor(current HP times 0.15) with HP floor one, then remove only this source-owned shield/effect and apply one non-dispellable battle-lifetime replacement shield. Shield uses the live HP resource capacity times 0.25 with floor, shared shield modifiers and shared operations; no HP-stat substitute. Refresh on the next owner's turn, not per hit or Ultimate interrupt. Source operations retain ordered events and snapshot reads; no battle mutation of Activity. Down/absent actors do not trigger; teardown belongs to battle.</t>
+        </is>
+      </c>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t>Hidden base/additive stacking, entry HP adjustment, phase, consume rounding and lethal floor, duration/refresh/dispel and summon inheritance have low policy confidence, not observed parity. Alternatives: pure base-character HP, additive live HP modifiers, proportional current-HP scaling, lethal drain, target-turn shield expiry or accumulating layers. Selected entry-capacity policy executes all three exact operands through real resources and bounded shared operations without pretending a stat-only bonus changes HP capacity. Affected tests weighted_curio_prayer and production data rejection fixtures. Replace each field independently when released executable programs or reproducible current traces establish it. Forge offers, equipment-command replay and complete runs remain pending.</t>
+        </is>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>89|90|91|92</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:R8"/>
+  <dataValidations count="5">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="I8:I1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: EntryHpAndTurnStartConsumeShield" promptTitle="DuCurioPrayerPolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"EntryHpAndTurnStartConsumeShield"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -45,9 +45,10 @@
     <sheet name="WeightedCurioAttackDebuffs" sheetId="37" state="visible" r:id="rId37"/>
     <sheet name="WeightedCurioSupportAttacks" sheetId="38" state="visible" r:id="rId38"/>
     <sheet name="WeightedCurioPrayers" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="WeightedCurioRetaliations" sheetId="40" state="visible" r:id="rId40"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$105</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -86,6 +87,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'WeightedCurioAttackDebuffs'!$A$3:$R$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'WeightedCurioSupportAttacks'!$A$3:$R$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'WeightedCurioPrayers'!$A$3:$R$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="39" hidden="1">'WeightedCurioRetaliations'!$A$3:$Y$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -593,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K99"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5652,8 +5654,314 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="9" t="n"/>
+      <c r="B100" s="9" t="n">
+        <v>93</v>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-retaliation.hex</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/RogueTournHex.json; HexID=1013; TournMode=Tourn3; MazeBuffID=633413; AvatarDamageType=Physical; DisplayID=1026</t>
+        </is>
+      </c>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>51e91a6f53ab0545330e477d806a165108f6c7e5e70ad52b02f92c1dc4d36455</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K100" s="9" t="inlineStr">
+        <is>
+          <t>Released current Hex join, Physical eligibility, exact 4 and 0.3 operands and representative path BaseAggro values. Mapping the second operand, baseline targeting admission, trigger cardinality/timing, damage element/crit and linked inheritance remain field-level policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="n"/>
+      <c r="B101" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-retaliation.maze-buff</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G101" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/MazeBuff.json; ID=633413; Lv=1; ParamList[0].Value=4; ParamList[1].Value=0.3; InBattleBindingKey=StageAbility_633413</t>
+        </is>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>2fab98b723ee20d8798c68e200cc9c3704abc347b0983b2955cbd40b85bfeeac</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K101" s="9" t="inlineStr">
+        <is>
+          <t>Released current Hex join, Physical eligibility, exact 4 and 0.3 operands and representative path BaseAggro values. Mapping the second operand, baseline targeting admission, trigger cardinality/timing, damage element/crit and linked inheritance remain field-level policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="n"/>
+      <c r="B102" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-retaliation.text-en</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G102" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H102" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapEN.json; hash=6457248194266440334; Physical attacked-target weight increase and owner-ATK additional damage that cannot defeat enemies</t>
+        </is>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>afc6d0ff9eeb20d09042e61c311e60d4ed56e69757f1ac42466ca4840e6ed789</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K102" s="9" t="inlineStr">
+        <is>
+          <t>Released current Hex join, Physical eligibility, exact 4 and 0.3 operands and representative path BaseAggro values. Mapping the second operand, baseline targeting admission, trigger cardinality/timing, damage element/crit and linked inheritance remain field-level policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="n"/>
+      <c r="B103" s="9" t="n">
+        <v>96</v>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-retaliation.text-zh</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G103" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H103" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapCHS.json; hash=6457248194266440334; Physical attacked-target weight increase and owner-ATK additional damage that cannot defeat enemies</t>
+        </is>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>ec49e07932b4ed8aba9679e247d8e554ca69e831fea7931d94682551de567147</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K103" s="9" t="inlineStr">
+        <is>
+          <t>Released current Hex join, Physical eligibility, exact 4 and 0.3 operands and representative path BaseAggro values. Mapping the second operand, baseline targeting admission, trigger cardinality/timing, damage element/crit and linked inheritance remain field-level policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="n"/>
+      <c r="B104" s="9" t="n">
+        <v>97</v>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-retaliation.avatar-path</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G104" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H104" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/AvatarConfig.json; AvatarID=1001:Knight|1002:Rogue|1003:Mage|1004:Warlock|1008:Warrior|1009:Shaman|1105:Priest|1402:Memory|1501:Elation; released representative path joins</t>
+        </is>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>c14584519e2feda70e9932501f7b79d67242d700585fe44119bbce9da9678e98</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K104" s="9" t="inlineStr">
+        <is>
+          <t>Released current Hex join, Physical eligibility, exact 4 and 0.3 operands and representative path BaseAggro values. Mapping the second operand, baseline targeting admission, trigger cardinality/timing, damage element/crit and linked inheritance remain field-level policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="n"/>
+      <c r="B105" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-retaliation.avatar-aggro</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G105" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/AvatarPromotionConfig.json; AvatarID=1001:150|1002:75|1003:75|1004:100|1008:125|1009:100|1105:100|1402:100|1501:100; Promotion=0..6; BaseAggro.Value; representative path weights</t>
+        </is>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>4453f206d6b79658128f22ce4d923e2e608f92b48175ba5c913ed2be322d24c5</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K105" s="9" t="inlineStr">
+        <is>
+          <t>Released current Hex join, Physical eligibility, exact 4 and 0.3 operands and representative path BaseAggro values. Mapping the second operand, baseline targeting admission, trigger cardinality/timing, damage element/crit and linked inheritance remain field-level policy.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K99"/>
+  <autoFilter ref="A3:K105"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -32457,6 +32765,911 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="9"/>
+    <col width="28" customWidth="1" style="5" min="10" max="10"/>
+    <col width="28" customWidth="1" style="5" min="11" max="11"/>
+    <col width="28" customWidth="1" style="5" min="12" max="12"/>
+    <col width="28" customWidth="1" style="5" min="13" max="13"/>
+    <col width="28" customWidth="1" style="5" min="14" max="14"/>
+    <col width="28" customWidth="1" style="5" min="15" max="15"/>
+    <col width="28" customWidth="1" style="5" min="16" max="16"/>
+    <col width="28" customWidth="1" style="5" min="17" max="17"/>
+    <col width="28" customWidth="1" style="5" min="18" max="18"/>
+    <col width="28" customWidth="1" style="5" min="19" max="19"/>
+    <col width="28" customWidth="1" style="5" min="20" max="20"/>
+    <col width="28" customWidth="1" style="5" min="21" max="21"/>
+    <col width="28" customWidth="1" style="5" min="22" max="22"/>
+    <col width="28" customWidth="1" style="5" min="23" max="23"/>
+    <col width="28" customWidth="1" style="5" min="24" max="24"/>
+    <col width="28" customWidth="1" style="5" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuWeightedCurioRetaliations</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>55e830dc5f843182</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="9" t="n"/>
+      <c r="N1" s="9" t="n"/>
+      <c r="O1" s="9" t="n"/>
+      <c r="P1" s="9" t="n"/>
+      <c r="Q1" s="9" t="n"/>
+      <c r="R1" s="9" t="n"/>
+      <c r="S1" s="9" t="n"/>
+      <c r="T1" s="9" t="n"/>
+      <c r="U1" s="9" t="n"/>
+      <c r="V1" s="9" t="n"/>
+      <c r="W1" s="9" t="n"/>
+      <c r="X1" s="9" t="n"/>
+      <c r="Y1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>character_elements</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>additional_parameter</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>additional_multiplier</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>aggro_parameter</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>aggro_fraction</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>base_aggro_destruction</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>base_aggro_hunt</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>base_aggro_erudition</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>base_aggro_harmony</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="inlineStr">
+        <is>
+          <t>base_aggro_nihility</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>base_aggro_preservation</t>
+        </is>
+      </c>
+      <c r="Q2" s="10" t="inlineStr">
+        <is>
+          <t>base_aggro_abundance</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>base_aggro_remembrance</t>
+        </is>
+      </c>
+      <c r="S2" s="10" t="inlineStr">
+        <is>
+          <t>base_aggro_elation</t>
+        </is>
+      </c>
+      <c r="T2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="U2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="V2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="W2" s="10" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="X2" s="10" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="Y2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>character_elements</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>additional_parameter</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>additional_multiplier</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>aggro_parameter</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>aggro_fraction</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>base_aggro_destruction</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>base_aggro_hunt</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>base_aggro_erudition</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>base_aggro_harmony</t>
+        </is>
+      </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>base_aggro_nihility</t>
+        </is>
+      </c>
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t>base_aggro_preservation</t>
+        </is>
+      </c>
+      <c r="Q3" s="12" t="inlineStr">
+        <is>
+          <t>base_aggro_abundance</t>
+        </is>
+      </c>
+      <c r="R3" s="12" t="inlineStr">
+        <is>
+          <t>base_aggro_remembrance</t>
+        </is>
+      </c>
+      <c r="S3" s="12" t="inlineStr">
+        <is>
+          <t>base_aggro_elation</t>
+        </is>
+      </c>
+      <c r="T3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="U3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="V3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="W3" s="12" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="X3" s="12" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="Y3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="R4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="S4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="T4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuCurioRetaliationPolicy&gt;</t>
+        </is>
+      </c>
+      <c r="U4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="V4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="W4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="X4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Y4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="Q5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="S5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="T5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="U5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="V5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="W5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="X5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="Y5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="S6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="T6" s="12" t="n"/>
+      <c r="U6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="V6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="W6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="X6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="Y6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
+      <c r="W7" s="6" t="n"/>
+      <c r="X7" s="6" t="n"/>
+      <c r="Y7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-retaliation.self-amusement</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1013</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>633413</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="S8" s="9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="T8" s="9" t="inlineStr">
+        <is>
+          <t>PhysicalAggroAndOwnerAdditional</t>
+        </is>
+      </c>
+      <c r="U8" s="9" t="inlineStr">
+        <is>
+          <t>Physical characters gain target weight; attacked survivors deal additional damage equal to 400% of their own ATK to the attacker, without defeating it.</t>
+        </is>
+      </c>
+      <c r="V8" s="9" t="inlineStr">
+        <is>
+          <t>物理角色受击权重提高；受击后存活的角色对攻击者造成等同于自身攻击力 400% 的附加伤害，不能击败敌方。</t>
+        </is>
+      </c>
+      <c r="W8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: qualify mapped player characters by their immutable canonical Basic scaling element, with no linked/summon inheritance. Interpret the exact second operand 0.3 as a +30% percent-of-base Aggro modifier. While equipped, explicitly bind each mapped character's path baseline as one Aggro-purpose final multiplier after the normalized factor; weight is BaseAggro times (1 plus the Curio bonus and other applicable modifiers), never a second inferred multiplier. Representative path values are exact; applying the path-wide model is policy. Bind materialized enemies' unbound normal Basic/Skill Opposing Single/Blast abilities to the shared current-state weighted single-primary selector, formation order and aggro-target battle RNG. Preserve ability choice/order, explicitly bound selectors, All/self actions, queued/forced targeting and each later-hit invalidation policy. This does not rewrite other modes or assert unreconstructed enemy target-lock parity. Ordinary DamageApplied with Attack tag and an action, target equal to alive/present Physical owner and alive/present opposing actor: AfterEvent, priority zero, once per owner per Action, including fully shielded and zero-loss hits. Emit DamageFromOwner with trigger-snapshot effective owner ATK times 4, Physical Additional, no crit, no Toughness, cannot defeat. No extra action/turn, no attack proc on DoT, Break, Additional or reflected damage, and no retaliation from down/departed victims. Unequip removes future battle bindings through fresh assembly; no battle mutation of Activity.</t>
+        </is>
+      </c>
+      <c r="X8" s="9" t="inlineStr">
+        <is>
+          <t>Low confidence for hidden mapping of 0.3, path-wide exceptions, normal-primary admission, hit/action cardinality, phase, shield/zero-hit admission, snapshot, Physical element, crit and linked inheritance; not observed parity. Alternatives include multiplicative weight bonus, per-hit reactions, after-action timing, effective-loss-only admission, crit-enabled or attacker-element damage and retaining unsupported first-target behavior. Selected policy executes both released clauses with the shared sampler, owner-sourced Additional formula and explicit nonlethal floor. Tests weighted_curio_retaliation and data rejection cases cover these fields. Replace each field independently when released executable selectors/programs or reproducible current traces establish it. Forge offers, equipment-command replay and complete original runs remain pending.</t>
+        </is>
+      </c>
+      <c r="Y8" s="9" t="inlineStr">
+        <is>
+          <t>93|94|95|96|97|98</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:Y8"/>
+  <dataValidations count="4">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="I8:I1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="T8:T1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: PhysicalAggroAndOwnerAdditional" promptTitle="DuCurioRetaliationPolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"PhysicalAggroAndOwnerAdditional"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -46,9 +46,10 @@
     <sheet name="WeightedCurioSupportAttacks" sheetId="38" state="visible" r:id="rId38"/>
     <sheet name="WeightedCurioPrayers" sheetId="39" state="visible" r:id="rId39"/>
     <sheet name="WeightedCurioRetaliations" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="WeightedCurioBreakEffects" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -88,6 +89,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'WeightedCurioSupportAttacks'!$A$3:$R$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'WeightedCurioPrayers'!$A$3:$R$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="39" hidden="1">'WeightedCurioRetaliations'!$A$3:$Y$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="40" hidden="1">'WeightedCurioBreakEffects'!$A$3:$N$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -595,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5960,8 +5962,212 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="9" t="n"/>
+      <c r="B106" s="9" t="n">
+        <v>99</v>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-break-effect.hex</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/RogueTournHex.json; HexID=1005; TournMode=Tourn3; MazeBuffID=633405; AvatarDamageType=Wind|Thunder; DisplayID=1018</t>
+        </is>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>51e91a6f53ab0545330e477d806a165108f6c7e5e70ad52b02f92c1dc4d36455</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K106" s="9" t="inlineStr">
+        <is>
+          <t>Exact current Tourn3 Hex/MazeBuff join, Wind/Thunder eligibility, 1.2 operand and highest-team raise-to clause. Hidden entry ordering, inactive roster, element mapping, rounding and capture lifetime remain field-level policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="n"/>
+      <c r="B107" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-break-effect.maze-buff</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G107" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/MazeBuff.json; ID=633405; Lv=1; ParamList[0].Value=1.2; InBattleBindingType=StageAbilityBeforeCharacterBorn; InBattleBindingKey=StageAbility_633405</t>
+        </is>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>2fab98b723ee20d8798c68e200cc9c3704abc347b0983b2955cbd40b85bfeeac</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K107" s="9" t="inlineStr">
+        <is>
+          <t>Exact current Tourn3 Hex/MazeBuff join, Wind/Thunder eligibility, 1.2 operand and highest-team raise-to clause. Hidden entry ordering, inactive roster, element mapping, rounding and capture lifetime remain field-level policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="n"/>
+      <c r="B108" s="9" t="n">
+        <v>101</v>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-break-effect.text-en</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapEN.json; hash=6003923322476481427; entry raises Wind/Lightning allies Break Effect to 120 percent of highest team ally Break Effect</t>
+        </is>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>afc6d0ff9eeb20d09042e61c311e60d4ed56e69757f1ac42466ca4840e6ed789</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K108" s="9" t="inlineStr">
+        <is>
+          <t>Exact current Tourn3 Hex/MazeBuff join, Wind/Thunder eligibility, 1.2 operand and highest-team raise-to clause. Hidden entry ordering, inactive roster, element mapping, rounding and capture lifetime remain field-level policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="n"/>
+      <c r="B109" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-break-effect.text-zh</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapCHS.json; hash=6003923322476481427; entry raises Wind/Lightning allies Break Effect to 120 percent of highest team ally Break Effect</t>
+        </is>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>ec49e07932b4ed8aba9679e247d8e554ca69e831fea7931d94682551de567147</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K109" s="9" t="inlineStr">
+        <is>
+          <t>Exact current Tourn3 Hex/MazeBuff join, Wind/Thunder eligibility, 1.2 operand and highest-team raise-to clause. Hidden entry ordering, inactive roster, element mapping, rounding and capture lifetime remain field-level policy.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K105"/>
+  <autoFilter ref="A3:K109"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -33670,6 +33876,546 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="9"/>
+    <col width="28" customWidth="1" style="5" min="10" max="10"/>
+    <col width="28" customWidth="1" style="5" min="11" max="11"/>
+    <col width="28" customWidth="1" style="5" min="12" max="12"/>
+    <col width="28" customWidth="1" style="5" min="13" max="13"/>
+    <col width="28" customWidth="1" style="5" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuWeightedCurioBreakEffects</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>0f1880a1a9067e77</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="9" t="n"/>
+      <c r="N1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>character_elements</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>multiplier_parameter</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>multiplier</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>character_elements</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>multiplier_parameter</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>multiplier</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuCurioBreakEffectPolicy&gt;</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-break-effect.converse-of-entropy</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1005</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>633405</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Wind|Thunder</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>EntryHighestTeamBreakEffectCapture</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>At battle entry, raise Wind and Lightning allies' Break Effect to 120% of the highest ally Break Effect in the team.</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>进入战斗时，将风、雷属性角色的击破特攻提高至队伍最高击破特攻的 120%。</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: BattleStarted AfterEvent, priority zero, once per battle. Qualify current locked player forms by immutable canonical Basic scaling element; no linked, summon or transformed-form inheritance. Bind all party owners but admit only the first alive/present member in formation order. Snapshot highest effective Break Effect among alive/present original party forms, including ineligible elements. One ApplyEffect operation resolves all eligible recipients from one immutable input before any insertion. Capture max(1.2 times highest minus recipient entry Break Effect, 0) as modifier-local Scalar, NearestTiesEven multiplication, permanent non-dispellable Flat/Stat Break Effect addition with OnApplication snapshot. Later modifiers remain live without recomputing this entry bonus; no dynamic aura, absolute override, per-owner compounding, later-wave recapture or Activity mutation. Unequip changes only future assembled battles.</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>Low confidence for hidden before-character-born equivalence, other entry-effect ordering, inactive eligibility, canonical Basic element mapping, linked inheritance, snapshot/teardown, rounding and negative input handling; not observed parity. Alternatives include authored before-birth scheduling, inactive-roster maxima, dynamic recomputation and absolute stat override. Tests weighted_curio_break_effect execute both eligible elements, unequal/tied/zero stats, ineligible maxima, downed first owner, later modifiers, real Break damage, fresh reconstruction, rejection and unequip in both families. Replace each field independently when released executable programs or reproducible current traces establish it. Forge admission, equipment-command replay and complete original runs remain pending.</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>99|100|101|102</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:N8"/>
+  <dataValidations count="3">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="I8:I1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: EntryHighestTeamBreakEffectCapture" promptTitle="DuCurioBreakEffectPolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"EntryHighestTeamBreakEffectCapture"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -47,9 +47,10 @@
     <sheet name="WeightedCurioPrayers" sheetId="39" state="visible" r:id="rId39"/>
     <sheet name="WeightedCurioRetaliations" sheetId="40" state="visible" r:id="rId40"/>
     <sheet name="WeightedCurioBreakEffects" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="WeightedCurioNecroses" sheetId="42" state="visible" r:id="rId42"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -90,6 +91,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'WeightedCurioPrayers'!$A$3:$R$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="39" hidden="1">'WeightedCurioRetaliations'!$A$3:$Y$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="40" hidden="1">'WeightedCurioBreakEffects'!$A$3:$N$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="41" hidden="1">'WeightedCurioNecroses'!$A$3:$T$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -597,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K109"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6166,8 +6168,212 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="9" t="n"/>
+      <c r="B110" s="9" t="n">
+        <v>103</v>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-necrosis.hex</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G110" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H110" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/RogueTournHex.json; HexID=1003; TournMode=Tourn3; MazeBuffID=633403; AvatarType=Priest; DisplayID=1016</t>
+        </is>
+      </c>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>51e91a6f53ab0545330e477d806a165108f6c7e5e70ad52b02f92c1dc4d36455</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K110" s="9" t="inlineStr">
+        <is>
+          <t>Exact released eligibility and four MazeBuff operands. Attack cardinality, chance scheduling, snapshot, replacement and the immediate Burn clause's observation point remain policy, not observed parity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="n"/>
+      <c r="B111" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-necrosis.maze-buff</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G111" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/MazeBuff.json; ID=633403; Lv=1; ParamList=1.5|6|3|2; InBattleBindingType=StageAbilityBeforeCharacterBorn; InBattleBindingKey=StageAbility_633403</t>
+        </is>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>2fab98b723ee20d8798c68e200cc9c3704abc347b0983b2955cbd40b85bfeeac</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K111" s="9" t="inlineStr">
+        <is>
+          <t>Exact released eligibility and four MazeBuff operands. Attack cardinality, chance scheduling, snapshot, replacement and the immediate Burn clause's observation point remain policy, not observed parity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="n"/>
+      <c r="B112" s="9" t="n">
+        <v>105</v>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-necrosis.text-en</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G112" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H112" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapEN.json; hash=14457895563947008111; Abundance attacks inflict Necrosis, turn-start Fire DoT and other Burn immediate damage</t>
+        </is>
+      </c>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>afc6d0ff9eeb20d09042e61c311e60d4ed56e69757f1ac42466ca4840e6ed789</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K112" s="9" t="inlineStr">
+        <is>
+          <t>Exact released eligibility and four MazeBuff operands. Attack cardinality, chance scheduling, snapshot, replacement and the immediate Burn clause's observation point remain policy, not observed parity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="n"/>
+      <c r="B113" s="9" t="n">
+        <v>106</v>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-necrosis.text-zh</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G113" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H113" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapCHS.json; hash=14457895563947008111; Abundance attacks inflict Necrosis, turn-start Fire DoT and other Burn immediate damage</t>
+        </is>
+      </c>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>ec49e07932b4ed8aba9679e247d8e554ca69e831fea7931d94682551de567147</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K113" s="9" t="inlineStr">
+        <is>
+          <t>Exact released eligibility and four MazeBuff operands. Attack cardinality, chance scheduling, snapshot, replacement and the immediate Burn clause's observation point remain policy, not observed parity.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K109"/>
+  <autoFilter ref="A3:K113"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -34416,6 +34622,752 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="9"/>
+    <col width="28" customWidth="1" style="5" min="10" max="10"/>
+    <col width="28" customWidth="1" style="5" min="11" max="11"/>
+    <col width="28" customWidth="1" style="5" min="12" max="12"/>
+    <col width="28" customWidth="1" style="5" min="13" max="13"/>
+    <col width="28" customWidth="1" style="5" min="14" max="14"/>
+    <col width="28" customWidth="1" style="5" min="15" max="15"/>
+    <col width="28" customWidth="1" style="5" min="16" max="16"/>
+    <col width="28" customWidth="1" style="5" min="17" max="17"/>
+    <col width="28" customWidth="1" style="5" min="18" max="18"/>
+    <col width="28" customWidth="1" style="5" min="19" max="19"/>
+    <col width="28" customWidth="1" style="5" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuWeightedCurioNecroses</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>c3af3f1bfed9abb2</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="9" t="n"/>
+      <c r="N1" s="9" t="n"/>
+      <c r="O1" s="9" t="n"/>
+      <c r="P1" s="9" t="n"/>
+      <c r="Q1" s="9" t="n"/>
+      <c r="R1" s="9" t="n"/>
+      <c r="S1" s="9" t="n"/>
+      <c r="T1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>character_paths</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>chance_parameter</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>base_chance</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>damage_parameter</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>attack_multiplier</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>duration_parameter</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>duration_turns</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>detonation_parameter</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>detonation_fraction</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="Q2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="S2" s="10" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="T2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>character_paths</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>chance_parameter</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>base_chance</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>damage_parameter</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>attack_multiplier</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>duration_parameter</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>duration_turns</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>detonation_parameter</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>detonation_fraction</t>
+        </is>
+      </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="Q3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="R3" s="12" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="S3" s="12" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="T3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuCurioNecrosisPolicy&gt;</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="R4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="S4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="T4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="Q5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="S5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="T5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..65535</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="n"/>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="S6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="T6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-necrosis.mock-crimson-moon</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1003</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>633403</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Priest</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>AttackResolvedNecrosisAndDotDamageBurnDetonation</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>Abundance attacks can inflict three-turn Necrosis: 600% ATK Fire DoT at turn start, with other Burns producing 200% immediate damage.</t>
+        </is>
+      </c>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t>丰饶角色攻击可施加持续三回合的坏死：回合开始造成攻击力六倍的火属性持续伤害，并使其他灼烧立即造成两倍伤害。</t>
+        </is>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: ActionResolved AfterAction priority zero once per action, original Abundance party owners only; distinct living/present opposing EventTargets in formation order, one resistible 1.5-base-chance roll per target with live EffectHitRate and EffectResistance, no authored specific-resistance stat. Successful applications replace the target's previous Necrosis even across casters, capture six times effective applier ATK with NearestTiesEven, one stack, dispellable, SourceSnapshotTargetDynamic, target TurnStart tick and TargetTurnEnd three-turn duration. On each Necrosis DamageApplied AfterEvent priority zero once per event, including externally detonated Necrosis, the original applier's bound rule detonates all other classified Burns at fraction two; ordinary and periodic Break stores share a stable effect-instance pool, exclude every Necrosis instance, retain original Burn sources, and floor only after full formula and fraction. No Burn detonation on application, resisted attempts, nonattack/allied/inactive targets or unrelated DoT; no recursive Necrosis/Burn chain, duration refresh or Activity mutation.</t>
+        </is>
+      </c>
+      <c r="S8" s="9" t="inlineStr">
+        <is>
+          <t>Low confidence for attack cardinality, chance ordering, cross-caster replacement, dispel, source snapshot and the Burn clause's placement on Necrosis damage rather than application or turn-boundary notification. Public text and released operands do not expose the executable stage program. Bounded 2026-10-01 cross-checks: BWIKI oldid=81596 and Fandom Mock_Crimson_Moon; older 400% text is not current. Alternatives: per-hit application, source-independent stacking, dynamic ATK, application-only detonation or natural-tick-only detonation. Tests weighted_curio_necrosis cover both run families, multihit/multitarget, probabilities, refresh, turn ticks, mixed-store Burns, exclusions, independent sources, deterministic reconstruction, rejection and unequip. Replace fields independently when released StageAbility_633403 or reproducible current traces establish timing, lifetime, membership or snapshot; equipment Forge and full original-run coverage remain separate pending work.</t>
+        </is>
+      </c>
+      <c r="T8" s="9" t="inlineStr">
+        <is>
+          <t>103|104|105|106</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:T8"/>
+  <dataValidations count="7">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="I8:I1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 65535." promptTitle="Integer range" prompt="Enter an integer from 1 to 65535." type="whole">
+      <formula1>1</formula1>
+      <formula2>65535</formula2>
+    </dataValidation>
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="O8:O1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AttackResolvedNecrosisAndDotDamageBurnDetonation" promptTitle="DuCurioNecrosisPolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AttackResolvedNecrosisAndDotDamageBurnDetonation"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -48,9 +48,10 @@
     <sheet name="WeightedCurioRetaliations" sheetId="40" state="visible" r:id="rId40"/>
     <sheet name="WeightedCurioBreakEffects" sheetId="41" state="visible" r:id="rId41"/>
     <sheet name="WeightedCurioNecroses" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="WeightedCurioElations" sheetId="43" state="visible" r:id="rId43"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -92,6 +93,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="39" hidden="1">'WeightedCurioRetaliations'!$A$3:$Y$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="40" hidden="1">'WeightedCurioBreakEffects'!$A$3:$N$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="41" hidden="1">'WeightedCurioNecroses'!$A$3:$T$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="42" hidden="1">'WeightedCurioElations'!$A$3:$R$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -599,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K113"/>
+  <dimension ref="A1:K117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6372,8 +6374,212 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="9" t="n"/>
+      <c r="B114" s="9" t="n">
+        <v>107</v>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-elation.hex</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G114" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H114" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/RogueTournHex.json; HexID=1015; TournMode=Tourn3; MazeBuffID=633415; AvatarType=Elation; DisplayID=1027</t>
+        </is>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>51e91a6f53ab0545330e477d806a165108f6c7e5e70ad52b02f92c1dc4d36455</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K114" s="9" t="inlineStr">
+        <is>
+          <t>Exact current Tourn3 eligibility and MazeBuff operands. Hidden trigger, recipient, refresh and meter lifecycle semantics are not observed parity. This row does not implement the Curio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="n"/>
+      <c r="B115" s="9" t="n">
+        <v>108</v>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-elation.maze-buff</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G115" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/MazeBuff.json; ID=633415; Lv=1; ParamList=2|0.5|2; InBattleBindingType=StageAbilityBeforeCharacterBorn; InBattleBindingKey=StageAbility_633415</t>
+        </is>
+      </c>
+      <c r="I115" s="9" t="inlineStr">
+        <is>
+          <t>2fab98b723ee20d8798c68e200cc9c3704abc347b0983b2955cbd40b85bfeeac</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K115" s="9" t="inlineStr">
+        <is>
+          <t>Exact current Tourn3 eligibility and MazeBuff operands. Hidden trigger, recipient, refresh and meter lifecycle semantics are not observed parity. This row does not implement the Curio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="n"/>
+      <c r="B116" s="9" t="n">
+        <v>109</v>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-elation.text-en</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G116" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H116" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapEN.json; hash=7976287788830292485; Elation party presence; non-Elation Basic or Skill; Punchline and timed Elation bonus</t>
+        </is>
+      </c>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>afc6d0ff9eeb20d09042e61c311e60d4ed56e69757f1ac42466ca4840e6ed789</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K116" s="9" t="inlineStr">
+        <is>
+          <t>Exact current Tourn3 eligibility and MazeBuff operands. Hidden trigger, recipient, refresh and meter lifecycle semantics are not observed parity. This row does not implement the Curio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="n"/>
+      <c r="B117" s="9" t="n">
+        <v>110</v>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-elation.text-zh</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G117" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H117" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapCHS.json; hash=7976287788830292485; Elation party presence; non-Elation Basic or Skill; Punchline and timed Elation bonus</t>
+        </is>
+      </c>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>ec49e07932b4ed8aba9679e247d8e554ca69e831fea7931d94682551de567147</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K117" s="9" t="inlineStr">
+        <is>
+          <t>Exact current Tourn3 eligibility and MazeBuff operands. Hidden trigger, recipient, refresh and meter lifecycle semantics are not observed parity. This row does not implement the Curio.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K113"/>
+  <autoFilter ref="A3:K117"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -35368,6 +35574,686 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="8"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="9"/>
+    <col width="28" customWidth="1" style="5" min="10" max="10"/>
+    <col width="28" customWidth="1" style="5" min="11" max="11"/>
+    <col width="28" customWidth="1" style="5" min="12" max="12"/>
+    <col width="28" customWidth="1" style="5" min="13" max="13"/>
+    <col width="28" customWidth="1" style="5" min="14" max="14"/>
+    <col width="28" customWidth="1" style="5" min="15" max="15"/>
+    <col width="28" customWidth="1" style="5" min="16" max="16"/>
+    <col width="28" customWidth="1" style="5" min="17" max="17"/>
+    <col width="28" customWidth="1" style="5" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuWeightedCurioElations</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>63b66e242e9964f7</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="9" t="n"/>
+      <c r="N1" s="9" t="n"/>
+      <c r="O1" s="9" t="n"/>
+      <c r="P1" s="9" t="n"/>
+      <c r="Q1" s="9" t="n"/>
+      <c r="R1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>character_paths</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>gain_parameter</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>punchline_gain</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>bonus_parameter</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>elation_bonus</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>duration_parameter</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>duration_turns</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="Q2" s="10" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>character_paths</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>gain_parameter</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>punchline_gain</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>bonus_parameter</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>elation_bonus</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>duration_parameter</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>duration_turns</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="Q3" s="12" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="R3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuCurioElationPolicy&gt;</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="R4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="Q5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..65535</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..65535</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="n"/>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-elation.sapient-pen</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1015</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>633415</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Elation</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>ActionResolvedOriginalPartyRefresh</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>With an Elation character in the party, non-Elation Basic or Skill use grants two Punchlines and adds 50% Elation to Elation characters for two turns.</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>队伍含欢愉角色时，非欢愉角色施放普攻或战技后获得两点笑点，并使欢愉角色的欢愉度提高50%，持续两回合。</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy, authored but not yet executed: original party combat forms determine Path membership; any original Elation party form satisfies presence, including a defeated member. Eligible original non-Elation owners trigger at ActionResolved AfterAction, priority zero, once per action for Basic or Skill regardless of Attack tag or hit count. Grant two to the side's single shared.punchline binding, then apply one dispellable additive StatKind::Elation bonus of 0.5 to each living/present original Elation recipient in formation order. TargetTurnEnd duration two, replace and refresh across casters rather than stack; no Ultimate, follow-up, summon, memosprite or shared-actor trigger. No RNG or Activity mutation. Shared-meter initial value, maximum, overflow and wave/battle carry are separate unimplemented assembly policy fields, not Curio operands or defaults.</t>
+        </is>
+      </c>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t>Low confidence for party presence while defeated, original-form membership, action observation point, cause ownership, ordering, dispel and cross-caster refresh. Bounded 2026-10-02 public cross-check: https://honkai-star-rail.fandom.com/wiki/Sapient_Pen confirms only the current Arcadian Chronicles player-facing clauses, not hidden scheduling; its older Quantum/Wind variant is excluded. Alternatives: active-only presence, per-hit triggers, caster-specific stacking, nondispellable bonus and source-turn duration. Data tests weighted_curio_elation validate exact operands, joins, policy labels and all four sources; they do not prove battle execution. Replace fields independently when released StageAbility_633415 or reproducible current observations establish trigger/recipient/refresh semantics. Runtime admission still requires real-command fixtures for both run families and explicit shared-meter assembly, overflow, lifecycle and reconstruction tests.</t>
+        </is>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>107|108|109|110</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:R8"/>
+  <dataValidations count="7">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="H8:H1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 65535." promptTitle="Integer range" prompt="Enter an integer from 1 to 65535." type="whole">
+      <formula1>1</formula1>
+      <formula2>65535</formula2>
+    </dataValidation>
+    <dataValidation sqref="I8:I1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 65535." promptTitle="Integer range" prompt="Enter an integer from 1 to 65535." type="whole">
+      <formula1>1</formula1>
+      <formula2>65535</formula2>
+    </dataValidation>
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ActionResolvedOriginalPartyRefresh" promptTitle="DuCurioElationPolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"ActionResolvedOriginalPartyRefresh"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -49,9 +49,10 @@
     <sheet name="WeightedCurioBreakEffects" sheetId="41" state="visible" r:id="rId41"/>
     <sheet name="WeightedCurioNecroses" sheetId="42" state="visible" r:id="rId42"/>
     <sheet name="WeightedCurioElations" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="BattleTeamResources" sheetId="44" state="visible" r:id="rId44"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$120</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -94,6 +95,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="40" hidden="1">'WeightedCurioBreakEffects'!$A$3:$N$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="41" hidden="1">'WeightedCurioNecroses'!$A$3:$T$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="42" hidden="1">'WeightedCurioElations'!$A$3:$R$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="43" hidden="1">'BattleTeamResources'!$A$3:$M$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -601,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K117"/>
+  <dimension ref="A1:K120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6578,8 +6580,161 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="9" t="n"/>
+      <c r="B118" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>du.source.battle-team-resource.global-cap</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E118" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F118" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G118" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t>Config/GlobalConfig/GameCoreConstValue.json; ElationPointMax=9999</t>
+        </is>
+      </c>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>5511ff36c631da99925c8aadae8ae46f50d620f4f937dbbed952fd61b16b80e3</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K118" s="9" t="inlineStr">
+        <is>
+          <t>Exact global field or released bilingual team-sharing text. Mapping the global field to this resource and its initialization/lifecycle remains VersionedProjectPolicy. Activity-specific ElationBattle_MaxPower=99 is not this field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="n"/>
+      <c r="B119" s="9" t="n">
+        <v>112</v>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>du.source.battle-team-resource.text-en</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G119" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H119" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapEN.json; hash=8389201339365092983; Punchline team sharing</t>
+        </is>
+      </c>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
+          <t>afc6d0ff9eeb20d09042e61c311e60d4ed56e69757f1ac42466ca4840e6ed789</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K119" s="9" t="inlineStr">
+        <is>
+          <t>Exact global field or released bilingual team-sharing text. Mapping the global field to this resource and its initialization/lifecycle remains VersionedProjectPolicy. Activity-specific ElationBattle_MaxPower=99 is not this field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="n"/>
+      <c r="B120" s="9" t="n">
+        <v>113</v>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>du.source.battle-team-resource.text-zh</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G120" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H120" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapCHS.json; hash=8389201339365092983; Punchline team sharing</t>
+        </is>
+      </c>
+      <c r="I120" s="9" t="inlineStr">
+        <is>
+          <t>ec49e07932b4ed8aba9679e247d8e554ca69e831fea7931d94682551de567147</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K120" s="9" t="inlineStr">
+        <is>
+          <t>Exact global field or released bilingual team-sharing text. Mapping the global field to this resource and its initialization/lifecycle remains VersionedProjectPolicy. Activity-specific ElationBattle_MaxPower=99 is not this field.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K117"/>
+  <autoFilter ref="A3:K120"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -36205,7 +36360,7 @@
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>VersionedProjectPolicy, authored but not yet executed: original party combat forms determine Path membership; any original Elation party form satisfies presence, including a defeated member. Eligible original non-Elation owners trigger at ActionResolved AfterAction, priority zero, once per action for Basic or Skill regardless of Attack tag or hit count. Grant two to the side's single shared.punchline binding, then apply one dispellable additive StatKind::Elation bonus of 0.5 to each living/present original Elation recipient in formation order. TargetTurnEnd duration two, replace and refresh across casters rather than stack; no Ultimate, follow-up, summon, memosprite or shared-actor trigger. No RNG or Activity mutation. Shared-meter initial value, maximum, overflow and wave/battle carry are separate unimplemented assembly policy fields, not Curio operands or defaults.</t>
+          <t>VersionedProjectPolicy, authored but not yet executed: original party combat forms determine Path membership; any original Elation party form satisfies presence, including a defeated member. Eligible original non-Elation owners trigger at ActionResolved AfterAction, priority zero, once per action for Basic or Skill regardless of Attack tag or hit count. Grant two to the side's single shared.punchline binding, then apply one dispellable additive StatKind::Elation bonus of 0.5 to each living/present original Elation recipient in formation order. TargetTurnEnd duration two, replace and refresh across casters rather than stack; no Ultimate, follow-up, summon, memosprite or shared-actor trigger. No RNG or Activity mutation. Shared-meter initial value, maximum, overflow and wave/battle carry belong to the separate BattleTeamResources assembly policy, not Curio operands or defaults; implementing the meter does not implement this Curio.</t>
         </is>
       </c>
       <c r="Q8" s="9" t="inlineStr">
@@ -36248,6 +36403,515 @@
     </dataValidation>
     <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ActionResolvedOriginalPartyRefresh" promptTitle="DuCurioElationPolicy enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ActionResolvedOriginalPartyRefresh"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="9"/>
+    <col width="28" customWidth="1" style="5" min="10" max="10"/>
+    <col width="90" customWidth="1" style="5" min="11" max="11"/>
+    <col width="90" customWidth="1" style="5" min="12" max="12"/>
+    <col width="28" customWidth="1" style="5" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuBattleTeamResources</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>0ccaeb7a31908794</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>resource_key</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>character_paths</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>initial_value</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>maximum_value</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>resource_key</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>character_paths</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>initial_value</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>maximum_value</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuBattleTeamResourcePolicy&gt;</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>range=0..65535</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..65535</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="240" customHeight="1">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.battle-team-resource.punchline</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>shared.punchline</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Elation</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>9999</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>OriginalElationZeroClampPersist</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Punchline is a team resource. A mapped original Elation party enables one player-side binding.</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>笑点为队伍共享资源；映射后的原始队伍含欢愉角色时装配一个我方资源。</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: original mapped party Path membership enables one shared.punchline player binding independently of equipped Curios, life/presence changes and linked actors. Start each battle at zero; map the released global ElationPointMax field to maximum 9999. Generic Gain clamps to maximum with attempted/effective/overflow events, Spend rejects insufficient balance without mutation, and Set follows generic bounds. Persist across waves. Reconstruct at zero for a fresh battle or retry; no Activity inventory or cross-battle carry. Source fact is the global field value and team-sharing text, not observed initialization or lifecycle parity. No Aha actor, Certified Banger, automatic gain, damage scaling or meter reset trigger is implied.</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>Low confidence for the field-to-resource mapping, enabling condition, zero initial value, cap overflow and wave/battle carry. Alternatives: unconditional binding, entry gain by Elation roster count, wave reset, checked overflow or cross-battle carry. Command tests battle_team_resources cover production resource assembly, the pending non-cost Skill delta lowering boundary, controlled overflow/spending/Set, wave carry, rejection and fresh reconstruction in both run families. Replace each field independently when a released executable binding or reproducible current Divergent Universe observation establishes it. ElationBattle_MaxPower=99 belongs to another activity and is excluded.</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>111|112|113</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:M8"/>
+  <dataValidations count="4">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="F8:F1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 0 to 65535." promptTitle="Integer range" prompt="Enter an integer from 0 to 65535." type="whole">
+      <formula1>0</formula1>
+      <formula2>65535</formula2>
+    </dataValidation>
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 65535." promptTitle="Integer range" prompt="Enter an integer from 1 to 65535." type="whole">
+      <formula1>1</formula1>
+      <formula2>65535</formula2>
+    </dataValidation>
+    <dataValidation sqref="H8:H1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: OriginalElationZeroClampPersist" promptTitle="DuBattleTeamResourcePolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"OriginalElationZeroClampPersist"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -35753,8 +35753,8 @@
     <col width="28" customWidth="1" style="5" min="13" max="13"/>
     <col width="28" customWidth="1" style="5" min="14" max="14"/>
     <col width="28" customWidth="1" style="5" min="15" max="15"/>
-    <col width="28" customWidth="1" style="5" min="16" max="16"/>
-    <col width="28" customWidth="1" style="5" min="17" max="17"/>
+    <col width="90" customWidth="1" style="5" min="16" max="16"/>
+    <col width="90" customWidth="1" style="5" min="17" max="17"/>
     <col width="28" customWidth="1" style="5" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -36298,7 +36298,7 @@
       <c r="Q7" s="6" t="n"/>
       <c r="R7" s="6" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" ht="260" customHeight="1">
       <c r="A8" s="9" t="n"/>
       <c r="B8" s="9" t="n">
         <v>1</v>
@@ -36360,12 +36360,12 @@
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>VersionedProjectPolicy, authored but not yet executed: original party combat forms determine Path membership; any original Elation party form satisfies presence, including a defeated member. Eligible original non-Elation owners trigger at ActionResolved AfterAction, priority zero, once per action for Basic or Skill regardless of Attack tag or hit count. Grant two to the side's single shared.punchline binding, then apply one dispellable additive StatKind::Elation bonus of 0.5 to each living/present original Elation recipient in formation order. TargetTurnEnd duration two, replace and refresh across casters rather than stack; no Ultimate, follow-up, summon, memosprite or shared-actor trigger. No RNG or Activity mutation. Shared-meter initial value, maximum, overflow and wave/battle carry belong to the separate BattleTeamResources assembly policy, not Curio operands or defaults; implementing the meter does not implement this Curio.</t>
+          <t>VersionedProjectPolicy: original party combat forms determine Path membership; any original Elation party form satisfies presence, including a defeated member. Eligible original non-Elation owners trigger at ActionResolved AfterAction, priority zero, once per action for Basic or Skill regardless of Attack tag or hit count. Grant two to the side's single shared.punchline binding, then apply one dispellable additive StatKind::Elation bonus of 0.5 to each living/present original Elation recipient in formation order. TargetTurnEnd duration two, replace and refresh across casters rather than stack. Recipient-scoped persistence survives provider defeat and waves until expiry or dispel. No Ultimate, follow-up, summon, memosprite or shared-actor trigger. No RNG or Activity mutation. Shared-meter initial value, maximum, overflow and wave/battle carry belong to the separate BattleTeamResources assembly policy, not Curio operands or defaults. Character Skill resource deltas and Aha/Certified Banger lifecycle are separate unimplemented boundaries.</t>
         </is>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
-          <t>Low confidence for party presence while defeated, original-form membership, action observation point, cause ownership, ordering, dispel and cross-caster refresh. Bounded 2026-10-02 public cross-check: https://honkai-star-rail.fandom.com/wiki/Sapient_Pen confirms only the current Arcadian Chronicles player-facing clauses, not hidden scheduling; its older Quantum/Wind variant is excluded. Alternatives: active-only presence, per-hit triggers, caster-specific stacking, nondispellable bonus and source-turn duration. Data tests weighted_curio_elation validate exact operands, joins, policy labels and all four sources; they do not prove battle execution. Replace fields independently when released StageAbility_633415 or reproducible current observations establish trigger/recipient/refresh semantics. Runtime admission still requires real-command fixtures for both run families and explicit shared-meter assembly, overflow, lifecycle and reconstruction tests.</t>
+          <t>Low confidence for party presence while defeated, original-form membership, action observation point, cause ownership, ordering, dispel and cross-caster refresh. Bounded 2026-10-02 public cross-check: https://honkai-star-rail.fandom.com/wiki/Sapient_Pen confirms only the current Arcadian Chronicles player-facing clauses, not hidden scheduling; its older Quantum/Wind variant is excluded. Alternatives: active-only presence, per-hit triggers, caster-specific stacking, nondispellable bonus and source-turn duration. Data tests weighted_curio_elation validate exact operands, joins, policy labels and all four sources; they do not prove battle execution. Mode fixtures weighted_curio_elation separately execute real commands in both run families and controlled resource/stat/lifecycle/reconstruction boundaries. Replace fields independently when released StageAbility_633415 or reproducible current observations establish trigger/recipient/refresh semantics. Forge offer/slot admission and full-run release coverage remain pending.</t>
         </is>
       </c>
       <c r="R8" s="9" t="inlineStr">

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -50,9 +50,10 @@
     <sheet name="WeightedCurioNecroses" sheetId="42" state="visible" r:id="rId42"/>
     <sheet name="WeightedCurioElations" sheetId="43" state="visible" r:id="rId43"/>
     <sheet name="BattleTeamResources" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="WeightedCurioExcitations" sheetId="45" state="visible" r:id="rId45"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$124</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -96,6 +97,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="41" hidden="1">'WeightedCurioNecroses'!$A$3:$T$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="42" hidden="1">'WeightedCurioElations'!$A$3:$R$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="43" hidden="1">'BattleTeamResources'!$A$3:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="44" hidden="1">'WeightedCurioExcitations'!$A$3:$W$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -603,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K120"/>
+  <dimension ref="A1:K124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6733,8 +6735,212 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="9" t="n"/>
+      <c r="B121" s="9" t="n">
+        <v>114</v>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-excitation.hex</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F121" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G121" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H121" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/RogueTournHex.json; HexID=1006; TournMode=Tourn3; MazeBuffID=633406; AvatarDamageType=Quantum; DisplayID=1011</t>
+        </is>
+      </c>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>51e91a6f53ab0545330e477d806a165108f6c7e5e70ad52b02f92c1dc4d36455</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K121" s="9" t="inlineStr">
+        <is>
+          <t>Exact Tourn3 Quantum eligibility and all five MazeBuff operands. Hidden gain attribution, timing, stacking and non-Break Entanglement semantics remain policy, not observed parity. Authoring does not implement this Curio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="n"/>
+      <c r="B122" s="9" t="n">
+        <v>115</v>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-excitation.maze-buff</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F122" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G122" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H122" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/MazeBuff.json; ID=633406; Lv=1; ParamList=2|1|2.5|0.5|1; InBattleBindingType=StageAbilityBeforeCharacterBorn; InBattleBindingKey=StageAbility_633406</t>
+        </is>
+      </c>
+      <c r="I122" s="9" t="inlineStr">
+        <is>
+          <t>2fab98b723ee20d8798c68e200cc9c3704abc347b0983b2955cbd40b85bfeeac</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K122" s="9" t="inlineStr">
+        <is>
+          <t>Exact Tourn3 Quantum eligibility and all five MazeBuff operands. Hidden gain attribution, timing, stacking and non-Break Entanglement semantics remain policy, not observed parity. Authoring does not implement this Curio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="n"/>
+      <c r="B123" s="9" t="n">
+        <v>116</v>
+      </c>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-excitation.text-en</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E123" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F123" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G123" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H123" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapEN.json; hash=332970425552739522; Quantum Skill Point gain; team Excitation; Basic or Skill attack; Quantum Additional damage; Entanglement</t>
+        </is>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>afc6d0ff9eeb20d09042e61c311e60d4ed56e69757f1ac42466ca4840e6ed789</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K123" s="9" t="inlineStr">
+        <is>
+          <t>Exact Tourn3 Quantum eligibility and all five MazeBuff operands. Hidden gain attribution, timing, stacking and non-Break Entanglement semantics remain policy, not observed parity. Authoring does not implement this Curio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="n"/>
+      <c r="B124" s="9" t="n">
+        <v>117</v>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-excitation.text-zh</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E124" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F124" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G124" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H124" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapCHS.json; hash=332970425552739522; Quantum Skill Point gain; team Excitation; Basic or Skill attack; Quantum Additional damage; Entanglement</t>
+        </is>
+      </c>
+      <c r="I124" s="9" t="inlineStr">
+        <is>
+          <t>ec49e07932b4ed8aba9679e247d8e554ca69e831fea7931d94682551de567147</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K124" s="9" t="inlineStr">
+        <is>
+          <t>Exact Tourn3 Quantum eligibility and all five MazeBuff operands. Hidden gain attribution, timing, stacking and non-Break Entanglement semantics remain policy, not observed parity. Authoring does not implement this Curio.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K120"/>
+  <autoFilter ref="A3:K124"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -36918,6 +37124,859 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="10"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" style="5" min="11" max="11"/>
+    <col width="28" customWidth="1" style="5" min="12" max="12"/>
+    <col width="28" customWidth="1" style="5" min="13" max="13"/>
+    <col width="28" customWidth="1" style="5" min="14" max="14"/>
+    <col width="28" customWidth="1" style="5" min="15" max="15"/>
+    <col width="28" customWidth="1" style="5" min="16" max="16"/>
+    <col width="28" customWidth="1" style="5" min="17" max="17"/>
+    <col width="28" customWidth="1" style="5" min="18" max="18"/>
+    <col width="28" customWidth="1" style="5" min="19" max="19"/>
+    <col width="28" customWidth="1" style="5" min="20" max="20"/>
+    <col width="110" customWidth="1" style="5" min="21" max="21"/>
+    <col width="110" customWidth="1" style="5" min="22" max="22"/>
+    <col width="28" customWidth="1" style="5" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuWeightedCurioExcitations</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>72b8aabd7498ebac</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="9" t="n"/>
+      <c r="N1" s="9" t="n"/>
+      <c r="O1" s="9" t="n"/>
+      <c r="P1" s="9" t="n"/>
+      <c r="Q1" s="9" t="n"/>
+      <c r="R1" s="9" t="n"/>
+      <c r="S1" s="9" t="n"/>
+      <c r="T1" s="9" t="n"/>
+      <c r="U1" s="9" t="n"/>
+      <c r="V1" s="9" t="n"/>
+      <c r="W1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>character_elements</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>gain_parameter</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>stack_gain</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>consume_parameter</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>stack_consumption</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>damage_parameter</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>attack_multiplier</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>chance_parameter</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>base_chance</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="inlineStr">
+        <is>
+          <t>duration_parameter</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>duration_turns</t>
+        </is>
+      </c>
+      <c r="Q2" s="10" t="inlineStr">
+        <is>
+          <t>policy_maximum_stacks</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="S2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="T2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="U2" s="10" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="V2" s="10" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="W2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>character_elements</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>gain_parameter</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>stack_gain</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>consume_parameter</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>stack_consumption</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>damage_parameter</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>attack_multiplier</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>chance_parameter</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>base_chance</t>
+        </is>
+      </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>duration_parameter</t>
+        </is>
+      </c>
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t>duration_turns</t>
+        </is>
+      </c>
+      <c r="Q3" s="12" t="inlineStr">
+        <is>
+          <t>policy_maximum_stacks</t>
+        </is>
+      </c>
+      <c r="R3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="S3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="T3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="U3" s="12" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="V3" s="12" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="W3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="R4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuCurioExcitationPolicy&gt;</t>
+        </is>
+      </c>
+      <c r="S4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="T4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="U4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="V4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="W4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="Q5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="S5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="T5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="U5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="V5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="W5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..65535</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..65535</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..65535</t>
+        </is>
+      </c>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..65535</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="n"/>
+      <c r="S6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="T6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="U6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="V6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="W6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
+      <c r="W7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="300" customHeight="1">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-excitation.genius-confusion</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1006</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>633406</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Quantum</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>65535</v>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>EffectiveGainActionResolvedTeamConsumption</t>
+        </is>
+      </c>
+      <c r="S8" s="9" t="inlineStr">
+        <is>
+          <t>Quantum allies gaining Skill Points grant two Excitation stacks to all allies. Basic or Skill attacks consume one team-wide stack to deal 250% ATK Quantum Additional damage and have a 50% base chance of one-turn Entanglement.</t>
+        </is>
+      </c>
+      <c r="T8" s="9" t="inlineStr">
+        <is>
+          <t>量子属性我方获得战技点后，全体获得两层激发；普攻或战技攻击后消耗全体一层，造成250%攻击力量子附加伤害，并有50%基础概率施加一回合纠缠。</t>
+        </is>
+      </c>
+      <c r="U8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: original mapped party elements qualify Skill Point gain actors; exclude linked/shared actors even when Present. Observe positive effective Skill Point balance changes AfterMutation, once per resource event, granting two stacks per event rather than per point. Cap each living/present original party recipient at the authored policy maximum 65535; zero stacks at fresh battle entry, nondispellable, persist across waves and provider defeat, no Activity carry. At ActionResolved AfterAction priority zero, once per original party Basic/Skill action tagged Attack, require the living/present actor's positive Excitation; subtract up to one from each living/present original party recipient before damage. Resolve one actor-sourced Quantum Additional packet per surviving attacked target in formation order, using actor ATK queried at the trigger boundary times 2.5, ordinary target-dynamic stages and independent crit. Then attempt one Entanglement per surviving target through ordinary effect-hit/control-resistance and labeled battle RNG. Do not reclassify Additional damage as another action. Entanglement must retain delay, hit accumulation and delayed damage, not just a marker or action skip; use the reviewed shared Quantum base-effect calculation as replaceable policy without setting Weakness Broken, reducing Toughness, dealing initial Break damage or adding the universal Break delay. Refresh same-definition Entanglement across casters without repeating delay while active; cleanse removes it without expiry damage. This authoring batch does not implement or admit the effect.</t>
+        </is>
+      </c>
+      <c r="V8" s="9" t="inlineStr">
+        <is>
+          <t>Low confidence for effective rather than attempted gains, cause-actor attribution, per-event rather than per-point gain, original-party scope, stack cap, gain-before-consumption ordering, actor stack admission, partial-team subtraction, source snapshots, crit, refresh and non-Break Entanglement internals. Pinned Git tree has no StageAbility_633406 program. Bounded 2026-10-02 public cross-check: https://honkai-star-rail.fandom.com/wiki/Divergent_Universe%3A_Arcadian_Chronicles/Curio confirms current player-facing clauses only. Alternatives include overflow-triggered or per-point stacks, shared single counter, all-recipient positive-stack admission, independent caster Entanglement and repeat delay. Data fixtures weighted_curio_excitation verify operands, joins, cap-policy separation, provenance and rejection; they do not prove battle execution. Implement native Ordinary/Cyclical gain, cap, consumption, damage, control, cleanse, wave, provider-defeat and fresh-reconstruction fixtures before admission. Replace each unavailable field independently when released StageAbility_633406 or reproducible current observations establish it. Entanglement formula/lifecycle and equipment execution remain pending; Forge and full-run release credit remain pending.</t>
+        </is>
+      </c>
+      <c r="W8" s="9" t="inlineStr">
+        <is>
+          <t>114|115|116|117</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:W8"/>
+  <dataValidations count="11">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="H8:H1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 65535." promptTitle="Integer range" prompt="Enter an integer from 1 to 65535." type="whole">
+      <formula1>1</formula1>
+      <formula2>65535</formula2>
+    </dataValidation>
+    <dataValidation sqref="I8:I1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 65535." promptTitle="Integer range" prompt="Enter an integer from 1 to 65535." type="whole">
+      <formula1>1</formula1>
+      <formula2>65535</formula2>
+    </dataValidation>
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="O8:O1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="P8:P1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 65535." promptTitle="Integer range" prompt="Enter an integer from 1 to 65535." type="whole">
+      <formula1>1</formula1>
+      <formula2>65535</formula2>
+    </dataValidation>
+    <dataValidation sqref="Q8:Q1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 65535." promptTitle="Integer range" prompt="Enter an integer from 1 to 65535." type="whole">
+      <formula1>1</formula1>
+      <formula2>65535</formula2>
+    </dataValidation>
+    <dataValidation sqref="R8:R1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: EffectiveGainActionResolvedTeamConsumption" promptTitle="DuCurioExcitationPolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"EffectiveGainActionResolvedTeamConsumption"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -51,9 +51,10 @@
     <sheet name="WeightedCurioElations" sheetId="43" state="visible" r:id="rId43"/>
     <sheet name="BattleTeamResources" sheetId="44" state="visible" r:id="rId44"/>
     <sheet name="WeightedCurioExcitations" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="WeightedCurioEncouragements" sheetId="46" state="visible" r:id="rId46"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$128</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -98,6 +99,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="42" hidden="1">'WeightedCurioElations'!$A$3:$R$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="43" hidden="1">'BattleTeamResources'!$A$3:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="44" hidden="1">'WeightedCurioExcitations'!$A$3:$W$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="45" hidden="1">'WeightedCurioEncouragements'!$A$3:$N$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -605,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6939,8 +6941,212 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="9" t="n"/>
+      <c r="B125" s="9" t="n">
+        <v>118</v>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-encouragement.hex</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G125" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H125" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/RogueTournHex.json; HexID=1008; TournMode=Tourn3; MazeBuffID=633408; AvatarType=Elation; DisplayID=1029</t>
+        </is>
+      </c>
+      <c r="I125" s="9" t="inlineStr">
+        <is>
+          <t>51e91a6f53ab0545330e477d806a165108f6c7e5e70ad52b02f92c1dc4d36455</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K125" s="9" t="inlineStr">
+        <is>
+          <t>Exact current Tourn3 eligibility and generic MazeBuff operand. Hidden damage-label routing, source ownership and formula interaction remain policy, not observed parity. Loading does not implement or admit this effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="n"/>
+      <c r="B126" s="9" t="n">
+        <v>119</v>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-encouragement.maze-buff</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F126" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H126" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/MazeBuff.json; ID=633408; Lv=1; ParamList=1.5; InBattleBindingType=StageAbilityBeforeCharacterBorn; InBattleBindingKey=StageAbility_633408</t>
+        </is>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>2fab98b723ee20d8798c68e200cc9c3704abc347b0983b2955cbd40b85bfeeac</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K126" s="9" t="inlineStr">
+        <is>
+          <t>Exact current Tourn3 eligibility and generic MazeBuff operand. Hidden damage-label routing, source ownership and formula interaction remain policy, not observed parity. Loading does not implement or admit this effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="n"/>
+      <c r="B127" s="9" t="n">
+        <v>120</v>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-encouragement.text-en</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F127" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G127" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H127" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapEN.json; hash=2693397682820933078; Elation character damage classification and Follow-Up CRIT DMG</t>
+        </is>
+      </c>
+      <c r="I127" s="9" t="inlineStr">
+        <is>
+          <t>afc6d0ff9eeb20d09042e61c311e60d4ed56e69757f1ac42466ca4840e6ed789</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K127" s="9" t="inlineStr">
+        <is>
+          <t>Exact current Tourn3 eligibility and generic MazeBuff operand. Hidden damage-label routing, source ownership and formula interaction remain policy, not observed parity. Loading does not implement or admit this effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="n"/>
+      <c r="B128" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-encouragement.text-zh</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F128" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G128" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H128" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapCHS.json; hash=2693397682820933078; Elation character damage classification and Follow-Up CRIT DMG</t>
+        </is>
+      </c>
+      <c r="I128" s="9" t="inlineStr">
+        <is>
+          <t>ec49e07932b4ed8aba9679e247d8e554ca69e831fea7931d94682551de567147</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K128" s="9" t="inlineStr">
+        <is>
+          <t>Exact current Tourn3 eligibility and generic MazeBuff operand. Hidden damage-label routing, source ownership and formula interaction remain policy, not observed parity. Loading does not implement or admit this effect.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K124"/>
+  <autoFilter ref="A3:K128"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -37977,6 +38183,546 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="48" customWidth="1" style="5" min="9" max="9"/>
+    <col width="48" customWidth="1" style="5" min="10" max="10"/>
+    <col width="54" customWidth="1" style="5" min="11" max="11"/>
+    <col width="110" customWidth="1" style="5" min="12" max="12"/>
+    <col width="110" customWidth="1" style="5" min="13" max="13"/>
+    <col width="28" customWidth="1" style="5" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuWeightedCurioEncouragements</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>f4fe2c1acec5d8f0</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="9" t="n"/>
+      <c r="N1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>character_paths</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>crit_parameter</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>follow_up_crit_damage</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>character_paths</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>crit_parameter</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>follow_up_crit_damage</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuCurioEncouragementPolicy&gt;</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="300" customHeight="1">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-encouragement.encouragement-for-you</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1008</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>633408</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Elation</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>OriginalElationFollowUpDamage</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>Elation characters retain their Elation formula while their Elation damage also qualifies as follow-up damage; their follow-up critical damage gains an additive 150%.</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>欢愉角色的欢愉伤害保留欢愉公式并同时满足追加攻击伤害判定，其追加攻击伤害的暴击伤害额外提高150%。</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: original mapped party forms determine Elation Path eligibility before battle assembly. Add FollowUp damage semantics to eligible owners' Elation hits without changing DamageClass::Elation, the Elation calculator, action kind/origin, hit count, costs, triggers or RNG grouping. Already-classified follow-up hits from those original owners also qualify. Add the canonical 1.5 ratio once to the eligible hit's CritDamage stat query before ordinary or Elation critical multiplication; no bonus to noncritical damage, CritRate, Elation stat or ordinary DMG Boost. Classification does not create a second action, hit, damage event or reaction. Do not transfer eligibility to summons, memosprites or shared actors through inherited forms/bundles. Battle-lifetime ownership is reconstructed from accepted equipment, persists across waves and never writes Activity state. Non-Elation owners, DoT, Break, Super Break and True damage receive no bonus. This authoring batch does not implement or admit the effect; shared orthogonal damage-label routing and command fixtures remain pending.</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>Low confidence for original-owner scope, additive label propagation to selectors/events/modifiers, preservation of action identity, and scoped critical-stat timing. Released StageAbility_633408 is absent from the pinned Git object tree. Bounded public cross-check on 2026-10-02: https://honkai-star-rail.fandom.com/wiki/Encouragement_for_You supports only the current Arcadian Chronicles clauses; its older Remembrance/memosprite variant is excluded. Alternatives: replace rather than add labels, reclassify the whole action, inherit owner eligibility for linked actors, or apply a formula-stage bonus instead of a scoped critical stat. Data tests weighted_curio_encouragement validate canonical operands, policy/provenance and exact joins; they do not prove battle execution. Replace each hidden field independently when released programs or reproducible current observations establish it. Forge, equipment replay and full-run release remain pending.</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>118|119|120|121</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:N8"/>
+  <dataValidations count="3">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="I8:I1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: OriginalElationFollowUpDamage" promptTitle="DuCurioEncouragementPolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"OriginalElationFollowUpDamage"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -38690,7 +38690,7 @@
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>VersionedProjectPolicy: original mapped party forms determine Elation Path eligibility before battle assembly. Add FollowUp damage semantics to eligible owners' Elation hits without changing DamageClass::Elation, the Elation calculator, action kind/origin, hit count, costs, triggers or RNG grouping. Already-classified follow-up hits from those original owners also qualify. Add the canonical 1.5 ratio once to the eligible hit's CritDamage stat query before ordinary or Elation critical multiplication; no bonus to noncritical damage, CritRate, Elation stat or ordinary DMG Boost. Classification does not create a second action, hit, damage event or reaction. Do not transfer eligibility to summons, memosprites or shared actors through inherited forms/bundles. Battle-lifetime ownership is reconstructed from accepted equipment, persists across waves and never writes Activity state. Non-Elation owners, DoT, Break, Super Break and True damage receive no bonus. This authoring batch does not implement or admit the effect; shared orthogonal damage-label routing and command fixtures remain pending.</t>
+          <t>VersionedProjectPolicy: original mapped party forms determine Elation Path eligibility before battle assembly. At BattleStarted/AfterEvent, once per battle per original owner, apply one permanent NonDispellable Replace effect with PersistByScope teardown. Ownership links, not presence, exclude linked recipients. Add FollowUp damage semantics to eligible owners' Elation hits without changing DamageClass::Elation, the Elation calculator, action kind/origin, hit count, costs or RNG grouping. Native follow-up hits also qualify. Add the canonical 1.5 ratio once to the qualifying damage operation's CritDamage stat query before ordinary or Elation critical multiplication. Both classification and critical-stat filters require an actual original-unit producer. Summons, memosprites, shared actors and unitless timeline actors cannot borrow eligibility through forms, bundles, forced effect attachment or formula-owner fallback. No bonus to noncritical damage, CritRate, Elation stat or ordinary DMG Boost. Classification creates no extra action, hit, damage event or reaction. Reconstruct ownership from accepted equipment for each battle, persist through waves and never write Activity state. Non-Elation owners, DoT, Break, Super Break and True damage receive no bonus. Data loading alone does not implement or admit the effect. Forge placement, equipment replay and complete-run release remain pending.</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -52,9 +52,10 @@
     <sheet name="BattleTeamResources" sheetId="44" state="visible" r:id="rId44"/>
     <sheet name="WeightedCurioExcitations" sheetId="45" state="visible" r:id="rId45"/>
     <sheet name="WeightedCurioEncouragements" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="WeightedCurioTransfers" sheetId="47" state="visible" r:id="rId47"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$132</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -100,6 +101,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="43" hidden="1">'BattleTeamResources'!$A$3:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="44" hidden="1">'WeightedCurioExcitations'!$A$3:$W$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="45" hidden="1">'WeightedCurioEncouragements'!$A$3:$N$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="46" hidden="1">'WeightedCurioTransfers'!$A$3:$T$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -607,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K128"/>
+  <dimension ref="A1:K132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7145,8 +7147,212 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="9" t="n"/>
+      <c r="B129" s="9" t="n">
+        <v>122</v>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-transfer.hex</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F129" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G129" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H129" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/RogueTournHex.json; HexID=1009; TournMode=Tourn3; MazeBuffID=633409; AvatarType=Knight; DisplayID=1002</t>
+        </is>
+      </c>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>51e91a6f53ab0545330e477d806a165108f6c7e5e70ad52b02f92c1dc4d36455</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K129" s="9" t="inlineStr">
+        <is>
+          <t>Current Tourn3 joins and four exact decimal operands. Hidden ordering, birth scope, overlap, rounding and formula-modifier treatment are independent policy, not observed parity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="n"/>
+      <c r="B130" s="9" t="n">
+        <v>123</v>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-transfer.maze-buff</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E130" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F130" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G130" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H130" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/MazeBuff.json; ID=633409; Lv=1; ParamList=0.75,0.3,0.9,0.1; InBattleBindingType=StageAbilityBeforeCharacterBorn; InBattleBindingKey=StageAbility_633409</t>
+        </is>
+      </c>
+      <c r="I130" s="9" t="inlineStr">
+        <is>
+          <t>2fab98b723ee20d8798c68e200cc9c3704abc347b0983b2955cbd40b85bfeeac</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K130" s="9" t="inlineStr">
+        <is>
+          <t>Current Tourn3 joins and four exact decimal operands. Hidden ordering, birth scope, overlap, rounding and formula-modifier treatment are independent policy, not observed parity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="n"/>
+      <c r="B131" s="9" t="n">
+        <v>124</v>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-transfer.text-en</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F131" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G131" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H131" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapEN.json; hash=14114601434821166552; Preservation team admission, other-shield transfer, owner-turn excess decay and healing from lost capacity</t>
+        </is>
+      </c>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>afc6d0ff9eeb20d09042e61c311e60d4ed56e69757f1ac42466ca4840e6ed789</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K131" s="9" t="inlineStr">
+        <is>
+          <t>Current Tourn3 joins and four exact decimal operands. Hidden ordering, birth scope, overlap, rounding and formula-modifier treatment are independent policy, not observed parity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="n"/>
+      <c r="B132" s="9" t="n">
+        <v>125</v>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-transfer.text-zh</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G132" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapCHS.json; hash=14114601434821166552; Preservation team admission, other-shield transfer, owner-turn excess decay and healing from lost capacity</t>
+        </is>
+      </c>
+      <c r="I132" s="9" t="inlineStr">
+        <is>
+          <t>ec49e07932b4ed8aba9679e247d8e554ca69e831fea7931d94682551de567147</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K132" s="9" t="inlineStr">
+        <is>
+          <t>Current Tourn3 joins and four exact decimal operands. Hidden ordering, birth scope, overlap, rounding and formula-modifier treatment are independent policy, not observed parity.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K128"/>
+  <autoFilter ref="A3:K132"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -38723,6 +38929,725 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="9"/>
+    <col width="28" customWidth="1" style="5" min="10" max="10"/>
+    <col width="28" customWidth="1" style="5" min="11" max="11"/>
+    <col width="28" customWidth="1" style="5" min="12" max="13"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" style="5" min="14" max="14"/>
+    <col width="28" customWidth="1" style="5" min="15" max="15"/>
+    <col width="60" customWidth="1" style="5" min="16" max="16"/>
+    <col width="60" customWidth="1" style="5" min="17" max="17"/>
+    <col width="110" customWidth="1" style="5" min="18" max="18"/>
+    <col width="110" customWidth="1" style="5" min="19" max="19"/>
+    <col width="28" customWidth="1" style="5" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuWeightedCurioTransfers</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>64ac6b5d093629d3</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="9" t="n"/>
+      <c r="N1" s="9" t="n"/>
+      <c r="O1" s="9" t="n"/>
+      <c r="P1" s="9" t="n"/>
+      <c r="Q1" s="9" t="n"/>
+      <c r="R1" s="9" t="n"/>
+      <c r="S1" s="9" t="n"/>
+      <c r="T1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>character_path</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>transfer_parameter</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>transfer_fraction</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>threshold_parameter</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>threshold_fraction</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>decay_parameter</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>decay_fraction</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>heal_parameter</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>heal_fraction</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="Q2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="S2" s="10" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="T2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>character_path</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>transfer_parameter</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>transfer_fraction</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>threshold_parameter</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>threshold_fraction</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>decay_parameter</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>decay_fraction</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>heal_parameter</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>heal_fraction</t>
+        </is>
+      </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="Q3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="R3" s="12" t="inlineStr">
+        <is>
+          <t>policy_note</t>
+        </is>
+      </c>
+      <c r="S3" s="12" t="inlineStr">
+        <is>
+          <t>replacement_condition</t>
+        </is>
+      </c>
+      <c r="T3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuCurioTransferPolicy&gt;</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="R4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="S4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="T4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="Q5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="S5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="T5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="n"/>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="S6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="T6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="340" customHeight="1">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-transfer.dignity-and-passion</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1009</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>633409</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Knight</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>OtherShieldAppliedOwnerTurnExcessDecay</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>A Preservation teammate enables an ally special shield. Other shields add 75% of their applied capacity. At its owner's turn start, 90% of capacity above 30% maximum HP is lost, healing for 10% of the actual loss.</t>
+        </is>
+      </c>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t>队伍中有存护角色时，我方获得特殊护盾；其他护盾实际获得量的75%转存至此护盾。本人回合开始时，超过生命上限30%的部分衰减90%，按实际衰减量的10%回复生命。</t>
+        </is>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: immutable mapped original party Paths admit the whole party if any is Preservation, irrespective of later caster death or absence. Bind only original player recipients; no automatic linked/new summon inheritance. At BattleStarted/AfterEvent install a permanent NonDispellable Replace marker with initially zero capacity; retain through waves with PersistByScope. Each positive ordinary Shield Applied event targeting a living present owner transfers its actual post-formula applied capacity once at AfterMutation, including independent repeated or replacement grants, without reapplying shield bonuses. Ensure the marker exists before a transfer. Exact effect-owned capacity uses ConcurrentLargest coexistence with ordinary shields. At recipient TurnStarted/AfterEvent once per turn, read current special capacity and current maximum HP from one immutable snapshot; decrease floor(0.9 * max(capacity - 0.3 * maximum HP, 0)), retaining fractional threshold until the final integer boundary. A separate AfterMutation reaction filters Adjusted events for this definition and a negative actual delta, healing floor(0.1 * actual loss) without healing modifiers. Absorption, removal, other definitions, increases, actions and other recipients' turns cannot heal. Explicit marker removal clears only its shield when no replacement marker exists. Alive/present selectors prevent death from producing gains/decay/healing. Stable participant/event order, checked fixed-point arithmetic, no RNG and no Activity mutation. Equipment changes affect future battle snapshots only.</t>
+        </is>
+      </c>
+      <c r="S8" s="9" t="inlineStr">
+        <is>
+          <t>Low confidence, not observed parity: original-party eligibility snapshot, birth/linked scope, event ordering, replacement-grant interpretation, ConcurrentLargest overlap, dynamic maximum HP, threshold precision, shield/healing modifier handling and marker teardown. Pinned StageAbility_633409 is absent from the filename tree; bounded public cross-check cannot establish hidden timing. Alternatives include additive absorption, per-caster layers, initial HP-based capacity, inheritance by summons, threshold flooring before decay, or boosted healing. Replace each independently with released programs or reproducible current traces. Data and both-family battle fixtures must cover exact operands, eligibility, repeated grants, zero/threshold/fractional decay, actual-loss-only healing, absorption, teardown and fresh deterministic commands. Original Forge admission, equipment replay and full-run release remain pending.</t>
+        </is>
+      </c>
+      <c r="T8" s="9" t="inlineStr">
+        <is>
+          <t>122|123|124|125</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:T8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -53,9 +53,10 @@
     <sheet name="WeightedCurioExcitations" sheetId="45" state="visible" r:id="rId45"/>
     <sheet name="WeightedCurioEncouragements" sheetId="46" state="visible" r:id="rId46"/>
     <sheet name="WeightedCurioTransfers" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="WeightedCurioOverflows" sheetId="48" state="visible" r:id="rId48"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$137</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -102,6 +103,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="44" hidden="1">'WeightedCurioExcitations'!$A$3:$W$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="45" hidden="1">'WeightedCurioEncouragements'!$A$3:$N$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="46" hidden="1">'WeightedCurioTransfers'!$A$3:$T$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="47" hidden="1">'WeightedCurioOverflows'!$A$3:$R$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -609,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K132"/>
+  <dimension ref="A1:K137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7351,8 +7353,263 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="9" t="n"/>
+      <c r="B133" s="9" t="n">
+        <v>126</v>
+      </c>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-overflow.hex</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E133" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G133" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="H133" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/RogueTournHex.json; HexID=1016; TournMode=Tourn3; MazeBuffID=633416; AvatarType=Mage,Rogue; DisplayID=1007</t>
+        </is>
+      </c>
+      <c r="I133" s="9" t="inlineStr">
+        <is>
+          <t>51e91a6f53ab0545330e477d806a165108f6c7e5e70ad52b02f92c1dc4d36455</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K133" s="9" t="inlineStr">
+        <is>
+          <t>Exact current membership, operands and named callback structure. The merged source program exists; no claim that opaque postfix semantics, hidden difficulty query or the native consumer is implemented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="n"/>
+      <c r="B134" s="9" t="n">
+        <v>127</v>
+      </c>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-overflow.maze-buff</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G134" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="H134" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/MazeBuff.json; ID=633416; Lv=1; ParamList=10,1,0.8; StageAbilityBeforeCharacterBorn; StageAbility_633416</t>
+        </is>
+      </c>
+      <c r="I134" s="9" t="inlineStr">
+        <is>
+          <t>2fab98b723ee20d8798c68e200cc9c3704abc347b0983b2955cbd40b85bfeeac</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K134" s="9" t="inlineStr">
+        <is>
+          <t>Exact current membership, operands and named callback structure. The merged source program exists; no claim that opaque postfix semantics, hidden difficulty query or the native consumer is implemented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="n"/>
+      <c r="B135" s="9" t="n">
+        <v>128</v>
+      </c>
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-overflow.text-en</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E135" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F135" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G135" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="H135" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapEN.json; hash=12104045893670599658; attack increase and attack-kill overflow conversion</t>
+        </is>
+      </c>
+      <c r="I135" s="9" t="inlineStr">
+        <is>
+          <t>afc6d0ff9eeb20d09042e61c311e60d4ed56e69757f1ac42466ca4840e6ed789</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K135" s="9" t="inlineStr">
+        <is>
+          <t>Exact current membership, operands and named callback structure. The merged source program exists; no claim that opaque postfix semantics, hidden difficulty query or the native consumer is implemented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="n"/>
+      <c r="B136" s="9" t="n">
+        <v>129</v>
+      </c>
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-overflow.text-zh</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F136" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G136" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="H136" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapCHS.json; hash=12104045893670599658; attack increase and attack-kill overflow conversion</t>
+        </is>
+      </c>
+      <c r="I136" s="9" t="inlineStr">
+        <is>
+          <t>ec49e07932b4ed8aba9679e247d8e554ca69e831fea7931d94682551de567147</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K136" s="9" t="inlineStr">
+        <is>
+          <t>Exact current membership, operands and named callback structure. The merged source program exists; no claim that opaque postfix semantics, hidden difficulty query or the native consumer is implemented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="n"/>
+      <c r="B137" s="9" t="n">
+        <v>130</v>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-overflow.program</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E137" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G137" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="H137" s="9" t="inlineStr">
+        <is>
+          <t>Config/ConfigAbility/Level/Rogue_S7/Level_RogueBuff_Ability_HEX_S7.json; Name=StageAbility_633416; Modifier_StageAbility_633416_Character; OnAfterHitAll,OnTriggerDeath,OnTriggerDeathrattle,OnBeforeAttack,OnAfterAttackEnd</t>
+        </is>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>5ad6c48751023184f5572e0069c5d02c841aef4de3cec092d0c2bc4913d17e47</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K137" s="9" t="inlineStr">
+        <is>
+          <t>Exact current membership, operands and named callback structure. The merged source program exists; no claim that opaque postfix semantics, hidden difficulty query or the native consumer is implemented.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K132"/>
+  <autoFilter ref="A3:K137"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -39648,6 +39905,661 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="40" customWidth="1" style="5" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="9"/>
+    <col width="28" customWidth="1" style="5" min="10" max="10"/>
+    <col width="28" customWidth="1" style="5" min="11" max="11"/>
+    <col width="28" customWidth="1" style="5" min="12" max="12"/>
+    <col width="48" customWidth="1" style="5" min="13" max="13"/>
+    <col width="65" customWidth="1" style="5" min="14" max="14"/>
+    <col width="65" customWidth="1" style="5" min="15" max="15"/>
+    <col width="110" customWidth="1" style="5" min="16" max="16"/>
+    <col width="110" customWidth="1" style="5" min="17" max="17"/>
+    <col width="28" customWidth="1" style="5" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuWeightedCurioOverflows</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>7a414d6be44b58ed</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="9" t="n"/>
+      <c r="N1" s="9" t="n"/>
+      <c r="O1" s="9" t="n"/>
+      <c r="P1" s="9" t="n"/>
+      <c r="Q1" s="9" t="n"/>
+      <c r="R1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>character_paths</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>base_parameter</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>base_multiplier</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>overflow_parameter</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>overflow_multiplier</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>attack_parameter</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>attack_increase</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>source_semantics</t>
+        </is>
+      </c>
+      <c r="Q2" s="10" t="inlineStr">
+        <is>
+          <t>unresolved_runtime</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>character_paths</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>base_parameter</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>base_multiplier</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>overflow_parameter</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>overflow_multiplier</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>attack_parameter</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>attack_increase</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t>source_semantics</t>
+        </is>
+      </c>
+      <c r="Q3" s="12" t="inlineStr">
+        <is>
+          <t>unresolved_runtime</t>
+        </is>
+      </c>
+      <c r="R3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuCurioOverflowStatus&gt;</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="R4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="Q5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="n"/>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="250" customHeight="1">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.parallel-universe-walkie-talkie</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>633416</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Mage|Rogue</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>PendingNativeDeathCallbackAndBaseDamage</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>Erudition and Hunt characters gain 80% ATK. Attack-kill overflow converts into True damage of ten times base damage plus the overflow, aimed at the highest-current-HP attacked enemy.</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>智识和巡猎角色攻击力提高80%。攻击消灭敌人后的溢出值转化为10倍基础伤害加溢出值的真实伤害，目标为已攻击敌人中当前生命值最高者。</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>Released structure: character-create Path filtering, a Replace AttackAddedRatio modifier, attack-start reset, hit-target marks and zero-current-HP damage observation, distinct death/deathrattle conversion callbacks, marked-current-HP maximum retarget with random ties, TrueDamage/ByBaseDamage conversion, then accumulator and mark cleanup. Attack-end clears During_Attack. No postfix decoding is inferred from opcode bytes or numeric hashes.</t>
+        </is>
+      </c>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t>Unimplemented: native death/deathrattle callback correspondence, hit/attack observation ordering, accumulator expression decoding, linked-actor ownership, tied-target labeled RNG and last-kill behavior. The base-DMG expression reads HPRatio, an opaque difficulty query and unresolved postfix operands; its exact level/difficulty formula is not established. Do not substitute character ATK, a constant or zero and claim parity. Replace each uncertainty with released typed semantics or a separately reviewed deterministic VersionedProjectPolicy preserving the known constraints. Bounded public cross-check on 2026-10-03: https://honkai-star-rail.fandom.com/wiki/Parallel_Universe_Walkie-Talkie corroborates current Arcadian Chronicles terms and level/Threshold-Protocol dependence, not the hidden formula. Ordinary/Cyclical consumer, Forge, replay and terminal coverage remain pending.</t>
+        </is>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>126|127|128|129|130</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:R8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -54,9 +54,10 @@
     <sheet name="WeightedCurioEncouragements" sheetId="46" state="visible" r:id="rId46"/>
     <sheet name="WeightedCurioTransfers" sheetId="47" state="visible" r:id="rId47"/>
     <sheet name="WeightedCurioOverflows" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="WeightedCurioOverflowLevels" sheetId="49" state="visible" r:id="rId49"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$139</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -103,7 +104,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="44" hidden="1">'WeightedCurioExcitations'!$A$3:$W$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="45" hidden="1">'WeightedCurioEncouragements'!$A$3:$N$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="46" hidden="1">'WeightedCurioTransfers'!$A$3:$T$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="47" hidden="1">'WeightedCurioOverflows'!$A$3:$R$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="47" hidden="1">'WeightedCurioOverflows'!$A$3:$W$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="48" hidden="1">'WeightedCurioOverflowLevels'!$A$3:$J$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -611,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K137"/>
+  <dimension ref="A1:K139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7608,8 +7610,110 @@
         </is>
       </c>
     </row>
+    <row r="138" ht="360" customHeight="1">
+      <c r="A138" s="9" t="n"/>
+      <c r="B138" s="9" t="n">
+        <v>131</v>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-overflow.hard-level</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G138" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H138" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/HardLevelGroup.json; HardLevelGroup=1; Level=1..95; HPRatio.Value</t>
+        </is>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>d185c09b5388f4eeb368199276ee8a815b406fd9902744027b72a5011b962978</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K138" s="9" t="inlineStr">
+        <is>
+          <t>Exact released Group 1 HPRatio decimals. Membership of this group in the Curio formula is not source-proven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="360" customHeight="1">
+      <c r="A139" s="9" t="n"/>
+      <c r="B139" s="9" t="n">
+        <v>132</v>
+      </c>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-overflow.base-policy</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E139" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F139" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G139" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H139" s="9" t="inlineStr">
+        <is>
+          <t>docs/divergent-universe-weighted-curio-overflow.md#base-damage-policy</t>
+        </is>
+      </c>
+      <c r="I139" s="9" t="inlineStr">
+        <is>
+          <t>1d0cf9d303e321dde4867bd315189f31bfb041766c082bc7f0babc95017b55e1</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="inlineStr">
+        <is>
+          <t>ProjectPolicy</t>
+        </is>
+      </c>
+      <c r="K139" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: base damage is 100 times released HardLevelGroup 1 HPRatio at the selected enemy's own immutable level, then multiplied by one plus the immutable battle contribution's Protocol maximum-HP increase. Use checked fixed-point multiplication, flooring to six fractional places after each multiplication; the shared final TrueDamage operation floors to integral damage. The source contains FixedValues 100 and a HPRatio read but does not establish this group, the opaque difficulty-query mapping, operator order or rounding. Group 1, Protocol HP scaling and these multiplication boundaries are independent low-confidence policies, not decoded postfix or observed parity.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K137"/>
+  <autoFilter ref="A3:K139"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -39911,7 +40015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:W8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -39932,6 +40036,11 @@
     <col width="110" customWidth="1" style="5" min="16" max="16"/>
     <col width="110" customWidth="1" style="5" min="17" max="17"/>
     <col width="28" customWidth="1" style="5" min="18" max="18"/>
+    <col width="28" customWidth="1" style="5" min="19" max="19"/>
+    <col width="28" customWidth="1" style="5" min="20" max="20"/>
+    <col width="60" customWidth="1" style="5" min="21" max="21"/>
+    <col width="110" customWidth="1" style="5" min="22" max="22"/>
+    <col width="110" customWidth="1" style="5" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39982,7 +40091,7 @@
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>7a414d6be44b58ed</t>
+          <t>ad5f29c71db84e40</t>
         </is>
       </c>
       <c r="K1" s="9" t="n"/>
@@ -39993,6 +40102,11 @@
       <c r="P1" s="9" t="n"/>
       <c r="Q1" s="9" t="n"/>
       <c r="R1" s="9" t="n"/>
+      <c r="S1" s="9" t="n"/>
+      <c r="T1" s="9" t="n"/>
+      <c r="U1" s="9" t="n"/>
+      <c r="V1" s="9" t="n"/>
+      <c r="W1" s="9" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
@@ -40085,6 +40199,31 @@
           <t>source_ids</t>
         </is>
       </c>
+      <c r="S2" s="10" t="inlineStr">
+        <is>
+          <t>base_fixed_damage</t>
+        </is>
+      </c>
+      <c r="T2" s="10" t="inlineStr">
+        <is>
+          <t>base_hard_level_group</t>
+        </is>
+      </c>
+      <c r="U2" s="10" t="inlineStr">
+        <is>
+          <t>base_policy</t>
+        </is>
+      </c>
+      <c r="V2" s="10" t="inlineStr">
+        <is>
+          <t>base_policy_note</t>
+        </is>
+      </c>
+      <c r="W2" s="10" t="inlineStr">
+        <is>
+          <t>base_replacement_condition</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -40177,6 +40316,31 @@
           <t>source_ids</t>
         </is>
       </c>
+      <c r="S3" s="12" t="inlineStr">
+        <is>
+          <t>base_fixed_damage</t>
+        </is>
+      </c>
+      <c r="T3" s="12" t="inlineStr">
+        <is>
+          <t>base_hard_level_group</t>
+        </is>
+      </c>
+      <c r="U3" s="12" t="inlineStr">
+        <is>
+          <t>base_policy</t>
+        </is>
+      </c>
+      <c r="V3" s="12" t="inlineStr">
+        <is>
+          <t>base_policy_note</t>
+        </is>
+      </c>
+      <c r="W3" s="12" t="inlineStr">
+        <is>
+          <t>base_replacement_condition</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -40269,6 +40433,31 @@
           <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
         </is>
       </c>
+      <c r="S4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="T4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="U4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuCurioOverflowBasePolicy&gt;</t>
+        </is>
+      </c>
+      <c r="V4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="W4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
@@ -40361,6 +40550,31 @@
           <t>common</t>
         </is>
       </c>
+      <c r="S5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="T5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="U5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="V5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="W5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -40447,6 +40661,27 @@
       <c r="R6" s="12" t="inlineStr">
         <is>
           <t>parser=split;separator=|</t>
+        </is>
+      </c>
+      <c r="S6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="T6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..1</t>
+        </is>
+      </c>
+      <c r="U6" s="12" t="n"/>
+      <c r="V6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="W6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
         </is>
       </c>
     </row>
@@ -40473,6 +40708,11 @@
       <c r="P7" s="6" t="n"/>
       <c r="Q7" s="6" t="n"/>
       <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
+      <c r="W7" s="6" t="n"/>
     </row>
     <row r="8" ht="250" customHeight="1">
       <c r="A8" s="9" t="n"/>
@@ -40550,12 +40790,3580 @@
       </c>
       <c r="R8" s="9" t="inlineStr">
         <is>
-          <t>126|127|128|129|130</t>
+          <t>126|127|128|129|130|131|132</t>
+        </is>
+      </c>
+      <c r="S8" s="9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="T8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" s="9" t="inlineStr">
+        <is>
+          <t>EnemyGroupOneHpRatioProtocolHpMultiplierFloor</t>
+        </is>
+      </c>
+      <c r="V8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: base damage is 100 times released HardLevelGroup 1 HPRatio at the selected enemy's own immutable level, then multiplied by one plus the immutable battle contribution's Protocol maximum-HP increase. Use checked fixed-point multiplication, flooring to six fractional places after each multiplication; the shared final TrueDamage operation floors to integral damage. The source contains FixedValues 100 and a HPRatio read but does not establish this group, the opaque difficulty-query mapping, operator order or rounding. Group 1, Protocol HP scaling and these multiplication boundaries are independent low-confidence policies, not decoded postfix or observed parity.</t>
+        </is>
+      </c>
+      <c r="W8" s="9" t="inlineStr">
+        <is>
+          <t>Preserves known enemy-level and Threshold-Protocol dependence without substituting owner ATK, zero or an arbitrary level polynomial. Alternatives include other released HardLevelGroups, a Protocol-specific scaling field, additive difficulty or a different postfix order. Replace each field when released typed operands or reproducible current observations establish it. Data fixtures cover all 95 levels, canonical precision, missing/duplicate/foreign rows and provenance; native base-expression and both-family equipment tests are still required. Callback, ATK, Forge, replay and terminal runtime admission remain pending.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:R8"/>
+  <autoFilter ref="A3:W8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J102"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuWeightedCurioOverflowLevels</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>a9398377cd8e966e</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>hard_level_group</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>unit_level</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>hp_ratio</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="n"/>
+      <c r="J2" s="9" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>hard_level_group</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>unit_level</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>hp_ratio</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="9" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="n"/>
+      <c r="J4" s="9" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..1</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..95</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="n"/>
+      <c r="J6" s="9" t="n"/>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="9" t="n"/>
+      <c r="J7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.001</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.002</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="n"/>
+      <c r="J9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.003</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.004</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>1.362518</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.005</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>1.428762</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="n"/>
+      <c r="J12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.006</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>1.496191</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.007</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>1.564808</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="n"/>
+      <c r="J14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.008</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>1.634615</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="n"/>
+      <c r="J15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.009</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>1.705617</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.010</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>1.777814</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.011</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>1.902566</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.012</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>2.027318</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="n"/>
+      <c r="J19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.013</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>2.15207</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="n"/>
+      <c r="J20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.014</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>2.276821</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="n"/>
+      <c r="J21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.015</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>2.401573</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="n"/>
+      <c r="J22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.016</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>2.526325</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="n"/>
+      <c r="J23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.017</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>2.651077</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="n"/>
+      <c r="J24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.018</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>2.775828</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="n"/>
+      <c r="J25" s="9" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.019</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>2.90058</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="n"/>
+      <c r="J26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n"/>
+      <c r="B27" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.020</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>3.025332</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="n"/>
+      <c r="J27" s="9" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.021</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>3.24706</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="n"/>
+      <c r="J28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.022</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>3.468788</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="n"/>
+      <c r="J29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.023</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>3.690516</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="n"/>
+      <c r="J30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n"/>
+      <c r="B31" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.024</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>3.912244</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="n"/>
+      <c r="J31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n"/>
+      <c r="B32" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.025</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>4.133972</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="n"/>
+      <c r="J32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n"/>
+      <c r="B33" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.026</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>4.355701</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n"/>
+      <c r="B34" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.027</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>4.577429</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="n"/>
+      <c r="B35" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.028</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>4.799157</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n"/>
+      <c r="B36" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.029</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>5.020885</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="9" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n"/>
+      <c r="B37" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.030</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>5.242613</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n"/>
+      <c r="B38" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.031</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>5.67081</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="n"/>
+      <c r="J38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="n"/>
+      <c r="B39" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.032</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>6.099006</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="n"/>
+      <c r="J39" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n"/>
+      <c r="B40" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.033</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>6.527203</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="n"/>
+      <c r="J40" s="9" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="n"/>
+      <c r="B41" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.034</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>6.9554</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="n"/>
+      <c r="J41" s="9" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n"/>
+      <c r="B42" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.035</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>7.383597</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="n"/>
+      <c r="J42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="n"/>
+      <c r="B43" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.036</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>7.811794</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="n"/>
+      <c r="B44" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.037</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>8.23999</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="n"/>
+      <c r="J44" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="n"/>
+      <c r="B45" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.038</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>8.668187</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="n"/>
+      <c r="B46" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.039</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>9.096384</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="n"/>
+      <c r="J46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="n"/>
+      <c r="B47" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.040</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>9.524581</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="n"/>
+      <c r="J47" s="9" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="n"/>
+      <c r="B48" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.041</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>10.786134</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="n"/>
+      <c r="J48" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="n"/>
+      <c r="B49" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.042</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>12.047688</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="n"/>
+      <c r="J49" s="9" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="n"/>
+      <c r="B50" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.043</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>13.309242</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I50" s="9" t="n"/>
+      <c r="J50" s="9" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="n"/>
+      <c r="B51" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.044</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>14.570795</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="n"/>
+      <c r="J51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="n"/>
+      <c r="B52" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.045</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>15.832349</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I52" s="9" t="n"/>
+      <c r="J52" s="9" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="n"/>
+      <c r="B53" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.046</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>17.093903</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="n"/>
+      <c r="J53" s="9" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="n"/>
+      <c r="B54" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.047</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>18.355455</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="n"/>
+      <c r="J54" s="9" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="n"/>
+      <c r="B55" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.048</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>19.61701</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="n"/>
+      <c r="J55" s="9" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="n"/>
+      <c r="B56" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.049</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>20.878565</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="n"/>
+      <c r="J56" s="9" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="n"/>
+      <c r="B57" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.050</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>22.140118</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="n"/>
+      <c r="J57" s="9" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="n"/>
+      <c r="B58" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.051</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>25.19852</t>
+        </is>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="n"/>
+      <c r="J58" s="9" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="n"/>
+      <c r="B59" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.052</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>28.256924</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I59" s="9" t="n"/>
+      <c r="J59" s="9" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="n"/>
+      <c r="B60" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.053</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>31.315327</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I60" s="9" t="n"/>
+      <c r="J60" s="9" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.054</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>34.37373</t>
+        </is>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I61" s="9" t="n"/>
+      <c r="J61" s="9" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="n"/>
+      <c r="B62" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.055</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>37.432133</t>
+        </is>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I62" s="9" t="n"/>
+      <c r="J62" s="9" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="n"/>
+      <c r="B63" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.056</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>40.490536</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I63" s="9" t="n"/>
+      <c r="J63" s="9" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="n"/>
+      <c r="B64" s="9" t="n">
+        <v>57</v>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.057</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="9" t="n">
+        <v>57</v>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>43.54894</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I64" s="9" t="n"/>
+      <c r="J64" s="9" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="n"/>
+      <c r="B65" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.058</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>46.60734</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I65" s="9" t="n"/>
+      <c r="J65" s="9" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="n"/>
+      <c r="B66" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.059</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>49.665745</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I66" s="9" t="n"/>
+      <c r="J66" s="9" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="n"/>
+      <c r="B67" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.060</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>52.724148</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I67" s="9" t="n"/>
+      <c r="J67" s="9" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="n"/>
+      <c r="B68" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.061</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>56.95045</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I68" s="9" t="n"/>
+      <c r="J68" s="9" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="n"/>
+      <c r="B69" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.062</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>61.17675</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I69" s="9" t="n"/>
+      <c r="J69" s="9" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="n"/>
+      <c r="B70" s="9" t="n">
+        <v>63</v>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.063</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="9" t="n">
+        <v>63</v>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>65.40305</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I70" s="9" t="n"/>
+      <c r="J70" s="9" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="n"/>
+      <c r="B71" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.064</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>69.62936</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I71" s="9" t="n"/>
+      <c r="J71" s="9" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="n"/>
+      <c r="B72" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.065</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>73.85566</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I72" s="9" t="n"/>
+      <c r="J72" s="9" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="n"/>
+      <c r="B73" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.066</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>78.08196</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I73" s="9" t="n"/>
+      <c r="J73" s="9" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="n"/>
+      <c r="B74" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.067</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>82.30826</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I74" s="9" t="n"/>
+      <c r="J74" s="9" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="n"/>
+      <c r="B75" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.068</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>86.53456</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I75" s="9" t="n"/>
+      <c r="J75" s="9" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="n"/>
+      <c r="B76" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.069</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>90.760864</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I76" s="9" t="n"/>
+      <c r="J76" s="9" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="n"/>
+      <c r="B77" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.070</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>94.98717</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I77" s="9" t="n"/>
+      <c r="J77" s="9" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="n"/>
+      <c r="B78" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.071</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>100.28955</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I78" s="9" t="n"/>
+      <c r="J78" s="9" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="n"/>
+      <c r="B79" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.072</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>105.591934</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I79" s="9" t="n"/>
+      <c r="J79" s="9" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="n"/>
+      <c r="B80" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.073</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>110.894325</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I80" s="9" t="n"/>
+      <c r="J80" s="9" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n"/>
+      <c r="B81" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.074</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>116.19671</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I81" s="9" t="n"/>
+      <c r="J81" s="9" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="n"/>
+      <c r="B82" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.075</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>121.49909</t>
+        </is>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I82" s="9" t="n"/>
+      <c r="J82" s="9" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="n"/>
+      <c r="B83" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.076</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>126.80148</t>
+        </is>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I83" s="9" t="n"/>
+      <c r="J83" s="9" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="n"/>
+      <c r="B84" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.077</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>132.10387</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I84" s="9" t="n"/>
+      <c r="J84" s="9" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="n"/>
+      <c r="B85" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.078</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>137.40625</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I85" s="9" t="n"/>
+      <c r="J85" s="9" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="n"/>
+      <c r="B86" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.079</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t>142.70863</t>
+        </is>
+      </c>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I86" s="9" t="n"/>
+      <c r="J86" s="9" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="n"/>
+      <c r="B87" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.080</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>148.01102</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I87" s="9" t="n"/>
+      <c r="J87" s="9" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="n"/>
+      <c r="B88" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.081</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="G88" s="9" t="inlineStr">
+        <is>
+          <t>155.48743</t>
+        </is>
+      </c>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I88" s="9" t="n"/>
+      <c r="J88" s="9" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="n"/>
+      <c r="B89" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.082</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
+        <is>
+          <t>163.24046</t>
+        </is>
+      </c>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I89" s="9" t="n"/>
+      <c r="J89" s="9" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="n"/>
+      <c r="B90" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.083</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>171.28036</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I90" s="9" t="n"/>
+      <c r="J90" s="9" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="n"/>
+      <c r="B91" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.084</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="G91" s="9" t="inlineStr">
+        <is>
+          <t>179.61774</t>
+        </is>
+      </c>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I91" s="9" t="n"/>
+      <c r="J91" s="9" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="n"/>
+      <c r="B92" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.085</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="G92" s="9" t="inlineStr">
+        <is>
+          <t>188.2636</t>
+        </is>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I92" s="9" t="n"/>
+      <c r="J92" s="9" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="n"/>
+      <c r="B93" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.086</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="G93" s="9" t="inlineStr">
+        <is>
+          <t>197.22934</t>
+        </is>
+      </c>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I93" s="9" t="n"/>
+      <c r="J93" s="9" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="n"/>
+      <c r="B94" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.087</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>206.52684</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I94" s="9" t="n"/>
+      <c r="J94" s="9" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="n"/>
+      <c r="B95" s="9" t="n">
+        <v>88</v>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.088</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="9" t="n">
+        <v>88</v>
+      </c>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>216.16832</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I95" s="9" t="n"/>
+      <c r="J95" s="9" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="n"/>
+      <c r="B96" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.089</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="G96" s="9" t="inlineStr">
+        <is>
+          <t>226.16655</t>
+        </is>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I96" s="9" t="n"/>
+      <c r="J96" s="9" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="n"/>
+      <c r="B97" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.090</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="G97" s="9" t="inlineStr">
+        <is>
+          <t>236.53471</t>
+        </is>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I97" s="9" t="n"/>
+      <c r="J97" s="9" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="n"/>
+      <c r="B98" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.091</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="G98" s="9" t="inlineStr">
+        <is>
+          <t>247.2865</t>
+        </is>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I98" s="9" t="n"/>
+      <c r="J98" s="9" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="n"/>
+      <c r="B99" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.092</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="G99" s="9" t="inlineStr">
+        <is>
+          <t>258.4361</t>
+        </is>
+      </c>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I99" s="9" t="n"/>
+      <c r="J99" s="9" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="n"/>
+      <c r="B100" s="9" t="n">
+        <v>93</v>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.093</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="9" t="n">
+        <v>93</v>
+      </c>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>269.99823</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I100" s="9" t="n"/>
+      <c r="J100" s="9" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="n"/>
+      <c r="B101" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.094</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="G101" s="9" t="inlineStr">
+        <is>
+          <t>281.98816</t>
+        </is>
+      </c>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I101" s="9" t="n"/>
+      <c r="J101" s="9" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="n"/>
+      <c r="B102" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-overflow.level.095</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1016</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="G102" s="9" t="inlineStr">
+        <is>
+          <t>294.42172</t>
+        </is>
+      </c>
+      <c r="H102" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="I102" s="9" t="n"/>
+      <c r="J102" s="9" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J102"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -57,7 +57,7 @@
     <sheet name="WeightedCurioOverflowLevels" sheetId="49" state="visible" r:id="rId49"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$140</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -104,7 +104,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="44" hidden="1">'WeightedCurioExcitations'!$A$3:$W$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="45" hidden="1">'WeightedCurioEncouragements'!$A$3:$N$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="46" hidden="1">'WeightedCurioTransfers'!$A$3:$T$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="47" hidden="1">'WeightedCurioOverflows'!$A$3:$W$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="47" hidden="1">'WeightedCurioOverflows'!$A$3:$X$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="48" hidden="1">'WeightedCurioOverflowLevels'!$A$3:$J$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K139"/>
+  <dimension ref="A1:K140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7712,8 +7712,59 @@
         </is>
       </c>
     </row>
+    <row r="140" ht="360" customHeight="1">
+      <c r="A140" s="9" t="n"/>
+      <c r="B140" s="9" t="n">
+        <v>133</v>
+      </c>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-overflow.runtime-policy</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E140" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F140" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G140" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H140" s="9" t="inlineStr">
+        <is>
+          <t>docs/divergent-universe-weighted-curio-overflow.md#native-equipment-policy</t>
+        </is>
+      </c>
+      <c r="I140" s="9" t="inlineStr">
+        <is>
+          <t>59232d8757967cde076c43e6df41353919c2e44b5e87b34183d7c455453fcb9f</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="inlineStr">
+        <is>
+          <t>ProjectPolicy</t>
+        </is>
+      </c>
+      <c r="K140" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: original entry-form Hunt/Erudition only. BattleStarted/AfterEvent grants 80% base ATK, permanent, non-dispellable and unique per source. Original actor/applier Ability attacks collect positive post-shield excess only from defeated marked enemies, confirmed by UnitDefeated. HitEnded converts once to a living marked current-HP maximum; damage-target uniformly samples ties and draws once for a singleton, zero for empty/unready pools. Capture total, reset, then emit 10*authored base+overflow TrueDamage. Mode kills cannot recollect. ActionResolved/WaveEnded/Won/Lost clear. Nested starts reset owner-local state; resumed hits reopen. Linked/countdown actors are excluded. No separate delayed-deathrattle replay.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K139"/>
+  <autoFilter ref="A3:K140"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -40015,7 +40066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -40041,6 +40092,7 @@
     <col width="60" customWidth="1" style="5" min="21" max="21"/>
     <col width="110" customWidth="1" style="5" min="22" max="22"/>
     <col width="110" customWidth="1" style="5" min="23" max="23"/>
+    <col width="110" customWidth="1" style="5" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40091,7 +40143,7 @@
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>ad5f29c71db84e40</t>
+          <t>3d10e08827b592a6</t>
         </is>
       </c>
       <c r="K1" s="9" t="n"/>
@@ -40107,6 +40159,7 @@
       <c r="U1" s="9" t="n"/>
       <c r="V1" s="9" t="n"/>
       <c r="W1" s="9" t="n"/>
+      <c r="X1" s="9" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
@@ -40191,7 +40244,7 @@
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
-          <t>unresolved_runtime</t>
+          <t>runtime_policy_note</t>
         </is>
       </c>
       <c r="R2" s="10" t="inlineStr">
@@ -40222,6 +40275,11 @@
       <c r="W2" s="10" t="inlineStr">
         <is>
           <t>base_replacement_condition</t>
+        </is>
+      </c>
+      <c r="X2" s="10" t="inlineStr">
+        <is>
+          <t>runtime_replacement_condition</t>
         </is>
       </c>
     </row>
@@ -40308,7 +40366,7 @@
       </c>
       <c r="Q3" s="12" t="inlineStr">
         <is>
-          <t>unresolved_runtime</t>
+          <t>runtime_policy_note</t>
         </is>
       </c>
       <c r="R3" s="12" t="inlineStr">
@@ -40339,6 +40397,11 @@
       <c r="W3" s="12" t="inlineStr">
         <is>
           <t>base_replacement_condition</t>
+        </is>
+      </c>
+      <c r="X3" s="12" t="inlineStr">
+        <is>
+          <t>runtime_replacement_condition</t>
         </is>
       </c>
     </row>
@@ -40458,6 +40521,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="X4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
@@ -40575,6 +40643,11 @@
           <t>common</t>
         </is>
       </c>
+      <c r="X5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -40680,6 +40753,11 @@
         </is>
       </c>
       <c r="W6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="X6" s="12" t="inlineStr">
         <is>
           <t>length=1..4000</t>
         </is>
@@ -40713,6 +40791,7 @@
       <c r="U7" s="6" t="n"/>
       <c r="V7" s="6" t="n"/>
       <c r="W7" s="6" t="n"/>
+      <c r="X7" s="6" t="n"/>
     </row>
     <row r="8" ht="250" customHeight="1">
       <c r="A8" s="9" t="n"/>
@@ -40765,7 +40844,7 @@
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>PendingNativeDeathCallbackAndBaseDamage</t>
+          <t>NativeProjectPolicyHitEnded</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
@@ -40785,12 +40864,12 @@
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
-          <t>Unimplemented: native death/deathrattle callback correspondence, hit/attack observation ordering, accumulator expression decoding, linked-actor ownership, tied-target labeled RNG and last-kill behavior. The base-DMG expression reads HPRatio, an opaque difficulty query and unresolved postfix operands; its exact level/difficulty formula is not established. Do not substitute character ATK, a constant or zero and claim parity. Replace each uncertainty with released typed semantics or a separately reviewed deterministic VersionedProjectPolicy preserving the known constraints. Bounded public cross-check on 2026-10-03: https://honkai-star-rail.fandom.com/wiki/Parallel_Universe_Walkie-Talkie corroborates current Arcadian Chronicles terms and level/Threshold-Protocol dependence, not the hidden formula. Ordinary/Cyclical consumer, Forge, replay and terminal coverage remain pending.</t>
+          <t>VersionedProjectPolicy: original entry-form Hunt/Erudition only. BattleStarted/AfterEvent grants 80% base ATK, permanent, non-dispellable and unique per source. Original actor/applier Ability attacks collect positive post-shield excess only from defeated marked enemies, confirmed by UnitDefeated. HitEnded converts once to a living marked current-HP maximum; damage-target uniformly samples ties and draws once for a singleton, zero for empty/unready pools. Capture total, reset, then emit 10*authored base+overflow TrueDamage. Mode kills cannot recollect. ActionResolved/WaveEnded/Won/Lost clear. Nested starts reset owner-local state; resumed hits reopen. Linked/countdown actors are excluded. No separate delayed-deathrattle replay.</t>
         </is>
       </c>
       <c r="R8" s="9" t="inlineStr">
         <is>
-          <t>126|127|128|129|130|131|132</t>
+          <t>126|127|128|129|130|131|132|133</t>
         </is>
       </c>
       <c r="S8" s="9" t="inlineStr">
@@ -40813,12 +40892,17 @@
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
-          <t>Preserves known enemy-level and Threshold-Protocol dependence without substituting owner ATK, zero or an arbitrary level polynomial. Alternatives include other released HardLevelGroups, a Protocol-specific scaling field, additive difficulty or a different postfix order. Replace each field when released typed operands or reproducible current observations establish it. Data fixtures cover all 95 levels, canonical precision, missing/duplicate/foreign rows and provenance; native base-expression and both-family equipment tests are still required. Callback, ATK, Forge, replay and terminal runtime admission remain pending.</t>
+          <t>Preserves known enemy-level and Threshold-Protocol dependence without substituting owner ATK, zero or an arbitrary level polynomial. Alternatives include other released HardLevelGroups, a Protocol-specific scaling field, additive difficulty or a different postfix order. Replace each field when released typed operands or reproducible current observations establish it. Data fixtures cover all 95 levels, canonical precision, missing/duplicate/foreign rows and provenance. Native expression tests cover every level and immutable Protocol snapshots. This policy is not decoded postfix or observed numeric parity.</t>
+        </is>
+      </c>
+      <c r="X8" s="9" t="inlineStr">
+        <is>
+          <t>Released named structure does not establish callback ordering, ATK creation timing/stacking, historical mark snapshots or reentrant/deathrattle correspondence. These independently replaceable low-confidence policies preserve original-Path eligibility, attack-kill excess, marked current-HP retargeting, random ties and owner credit using shared commands/events only. Alternatives are immediate first-death conversion (misses same-hit later settlements), attack-end-only conversion (delays all conversions), or a second action stack/callback engine (violates shared ownership). A death confirmed only after ActionResolved has no active attack collector and does not replay earlier excess. Replace each field when released typed semantics or reproducible current observations establish it. Native tests cover multi-death, shields, phase/HP-floor/guard exclusion, original transform/restore, real linked/countdown exclusion, same-owner queued envelopes, target isolation, fresh hashes and rejected commands. Separate player-rescue and delayed-deathrattle interaction coverage, Forge and complete-run release gates are not implied by this policy's equipment admission.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:W8"/>
+  <autoFilter ref="A3:X8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -55,9 +55,10 @@
     <sheet name="WeightedCurioTransfers" sheetId="47" state="visible" r:id="rId47"/>
     <sheet name="WeightedCurioOverflows" sheetId="48" state="visible" r:id="rId48"/>
     <sheet name="WeightedCurioOverflowLevels" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="WeightedCurioFootsteps" sheetId="50" state="visible" r:id="rId50"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$147</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -106,6 +107,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="46" hidden="1">'WeightedCurioTransfers'!$A$3:$T$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="47" hidden="1">'WeightedCurioOverflows'!$A$3:$X$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="48" hidden="1">'WeightedCurioOverflowLevels'!$A$3:$J$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="49" hidden="1">'WeightedCurioFootsteps'!$A$3:$T$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -613,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K140"/>
+  <dimension ref="A1:K147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7763,15 +7765,365 @@
         </is>
       </c>
     </row>
+    <row r="141" ht="240" customHeight="1">
+      <c r="B141" s="9" t="n">
+        <v>134</v>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-footstep.hex</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E141" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F141" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G141" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H141" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/RogueTournHex.json; HexID=1011; TournMode=Tourn3; MazeBuffID=633411; AvatarType=Warrior,Memory</t>
+        </is>
+      </c>
+      <c r="I141" s="9" t="inlineStr">
+        <is>
+          <t>51e91a6f53ab0545330e477d806a165108f6c7e5e70ad52b02f92c1dc4d36455</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K141" s="9" t="inlineStr">
+        <is>
+          <t>Exact released joins, operands and named callback structure; hidden dynamic postfix and native timing parity are not inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="240" customHeight="1">
+      <c r="B142" s="9" t="n">
+        <v>135</v>
+      </c>
+      <c r="C142" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-footstep.maze-buff</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E142" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G142" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H142" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/MazeBuff.json; ID=633411; Lv=1; ParamList=0.5,0.08,10; StageAbility_633411</t>
+        </is>
+      </c>
+      <c r="I142" s="9" t="inlineStr">
+        <is>
+          <t>2fab98b723ee20d8798c68e200cc9c3704abc347b0983b2955cbd40b85bfeeac</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K142" s="9" t="inlineStr">
+        <is>
+          <t>Exact released joins, operands and named callback structure; hidden dynamic postfix and native timing parity are not inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="240" customHeight="1">
+      <c r="B143" s="9" t="n">
+        <v>136</v>
+      </c>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-footstep.text-en</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E143" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F143" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G143" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H143" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapEN.json; hash=10599000866283908992; HP-loss point and Skill damage clauses</t>
+        </is>
+      </c>
+      <c r="I143" s="9" t="inlineStr">
+        <is>
+          <t>afc6d0ff9eeb20d09042e61c311e60d4ed56e69757f1ac42466ca4840e6ed789</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K143" s="9" t="inlineStr">
+        <is>
+          <t>Exact released joins, operands and named callback structure; hidden dynamic postfix and native timing parity are not inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="240" customHeight="1">
+      <c r="B144" s="9" t="n">
+        <v>137</v>
+      </c>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-footstep.text-zh</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E144" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G144" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H144" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapCHS.json; hash=10599000866283908992; HP-loss point and Skill damage clauses</t>
+        </is>
+      </c>
+      <c r="I144" s="9" t="inlineStr">
+        <is>
+          <t>ec49e07932b4ed8aba9679e247d8e554ca69e831fea7931d94682551de567147</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K144" s="9" t="inlineStr">
+        <is>
+          <t>Exact released joins, operands and named callback structure; hidden dynamic postfix and native timing parity are not inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="240" customHeight="1">
+      <c r="B145" s="9" t="n">
+        <v>138</v>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-footstep.program</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G145" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H145" s="9" t="inlineStr">
+        <is>
+          <t>Config/ConfigAbility/Level/Rogue_S7/Level_RogueBuff_Ability_HEX_S7.json; Name=StageAbility_633411; Modifier_StageAbility_633411_Sub; OnListenHPChange,OnAfterSkillUse; AllDamageTypeAddedRatio</t>
+        </is>
+      </c>
+      <c r="I145" s="9" t="inlineStr">
+        <is>
+          <t>5ad6c48751023184f5572e0069c5d02c841aef4de3cec092d0c2bc4913d17e47</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K145" s="9" t="inlineStr">
+        <is>
+          <t>Exact released joins, operands and named callback structure; hidden dynamic postfix and native timing parity are not inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="240" customHeight="1">
+      <c r="B146" s="9" t="n">
+        <v>139</v>
+      </c>
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-footstep.hp-policy</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E146" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G146" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H146" s="9" t="inlineStr">
+        <is>
+          <t>docs/divergent-universe-weighted-curio-footstep.md#independently-replaceable-execution-policy</t>
+        </is>
+      </c>
+      <c r="I146" s="9" t="inlineStr">
+        <is>
+          <t>842d954f541977184ebeb37bb23d0ba32c9a695af26226cd9c868c5d36c8cea4</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="inlineStr">
+        <is>
+          <t>ProjectPolicy</t>
+        </is>
+      </c>
+      <c r="K146" s="9" t="inlineStr">
+        <is>
+          <t>Digest binds the corresponding hp-policy note in WeightedCurioFootsteps, not an upstream blob. See the independently replaceable execution fields and replacement conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="240" customHeight="1">
+      <c r="B147" s="9" t="n">
+        <v>140</v>
+      </c>
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-footstep.skill-policy</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E147" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F147" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G147" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H147" s="9" t="inlineStr">
+        <is>
+          <t>docs/divergent-universe-weighted-curio-footstep.md#after-skill-damage-policy</t>
+        </is>
+      </c>
+      <c r="I147" s="9" t="inlineStr">
+        <is>
+          <t>3804368a7a6e063b69666256b0563ca26fb135eed72032ffb1a920a59a191d6f</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="inlineStr">
+        <is>
+          <t>ProjectPolicy</t>
+        </is>
+      </c>
+      <c r="K147" s="9" t="inlineStr">
+        <is>
+          <t>Digest binds the corresponding skill-policy note in WeightedCurioFootsteps, not an upstream blob. See the independently replaceable execution fields and replacement conditions.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K140"/>
+  <autoFilter ref="A3:K147"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ObservedCommunity" promptTitle="DuDecisionEvidence enum" prompt="Select a value from the dropdown." type="list">
-      <formula1>"ExactStructured,ObservedCommunity"</formula1>
+    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ObservedCommunity, ProjectPolicy" promptTitle="DuDecisionEvidence enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"ExactStructured,ObservedCommunity,ProjectPolicy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -44902,6 +45254,750 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="40" customWidth="1" style="5" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="10"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" style="5" min="11" max="11"/>
+    <col width="28" customWidth="1" style="5" min="12" max="12"/>
+    <col width="62" customWidth="1" style="5" min="13" max="13"/>
+    <col width="60" customWidth="1" style="5" min="14" max="14"/>
+    <col width="60" customWidth="1" style="5" min="15" max="15"/>
+    <col width="110" customWidth="1" style="5" min="16" max="16"/>
+    <col width="110" customWidth="1" style="5" min="17" max="17"/>
+    <col width="110" customWidth="1" style="5" min="18" max="18"/>
+    <col width="110" customWidth="1" style="5" min="19" max="19"/>
+    <col width="28" customWidth="1" style="5" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuWeightedCurioFootsteps</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>8da07b1886f5e3f3</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="9" t="n"/>
+      <c r="N1" s="9" t="n"/>
+      <c r="O1" s="9" t="n"/>
+      <c r="P1" s="9" t="n"/>
+      <c r="Q1" s="9" t="n"/>
+      <c r="R1" s="9" t="n"/>
+      <c r="S1" s="9" t="n"/>
+      <c r="T1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>character_paths</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>loss_parameter</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>loss_fraction</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>damage_parameter</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>damage_per_stack</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>cap_parameter</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>maximum_stacks</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>hp_policy_note</t>
+        </is>
+      </c>
+      <c r="Q2" s="10" t="inlineStr">
+        <is>
+          <t>hp_replacement_condition</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>skill_policy_note</t>
+        </is>
+      </c>
+      <c r="S2" s="10" t="inlineStr">
+        <is>
+          <t>skill_replacement_condition</t>
+        </is>
+      </c>
+      <c r="T2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>character_paths</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>loss_parameter</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>loss_fraction</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>damage_parameter</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>damage_per_stack</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>cap_parameter</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>maximum_stacks</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t>hp_policy_note</t>
+        </is>
+      </c>
+      <c r="Q3" s="12" t="inlineStr">
+        <is>
+          <t>hp_replacement_condition</t>
+        </is>
+      </c>
+      <c r="R3" s="12" t="inlineStr">
+        <is>
+          <t>skill_policy_note</t>
+        </is>
+      </c>
+      <c r="S3" s="12" t="inlineStr">
+        <is>
+          <t>skill_replacement_condition</t>
+        </is>
+      </c>
+      <c r="T3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuCurioFootstepPolicy&gt;</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="R4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="S4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="T4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="Q5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="S5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="T5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..64</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..65535</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="n"/>
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="S6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="T6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="220" customHeight="1">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-footstep.footstep-of-gods</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1011</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>633411</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Warrior|Memory</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>EffectiveHpLossAfterSkillOriginalDamage</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>Destruction/Remembrance originals gain Skill Points from cumulative HP loss and stack a damage bonus after Skills.</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>毁灭／记忆原角色累计降低生命值获得战技点，战技结束后叠加伤害增益。</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: original entry-form Destruction/Remembrance only, excluding owned linked actors. Observe negative effective DamageApplied and explicit HpChanged AfterEvent, priority zero, once per event. Independent battle-local absolute HP residue accumulates actual loss; live maximum HP times the fraction floors to six places, then the accumulated loss divided by that threshold floors to integral Skill Points. Consume thresholds even for discarded capped gains; healing retains residue and maximum-HP clamps add none. Preserve observed cause actor/ancestry, with the original owner selector choosing the receiving team. Transformations and waves retain residue; Won/Lost clears it. Shared checked operations roll back numeric faults, with no RNG. Hidden callback correspondence, capacity/rounding, overflow banking and gain attribution are independent low-confidence fields, not source parity.</t>
+        </is>
+      </c>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t>Alternatives are entry-max thresholds, percentage residue, including capacity clamps, healing reset, banking capped points or owner-sourced gain attribution. The selected fields reuse immutable shared event facts and bounded checked operations. Replace each field independently when released typed executable evidence or reproducible observations establish it. Command tests cover actual consumption/damage, shields, fractions/caps, healing, original Paths, independent owners, lifecycle, terminal reset, arithmetic rollback and fresh hashes. Equipment admission is not Forge, complete-run release or terminal reference coverage.</t>
+        </is>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: original entry-form Destruction/Remembrance only. Observe complete Skill ActionResolved at AfterAction, priority zero, once per Action, including nondamaging Skills. Add one permanent non-dispellable RefreshAndAddStacks Buff up to the exact cap, independent per original. Dynamic modifier-local stacks multiply the additive ratio with six-place Floor in Ordinary/DoT/Additional DamageBoost; only actual OriginalUnit producers qualify. Current Skill damage is not retroactively changed; Basic/Ultimate/FollowUp and linked/countdown actors add no layer. Waves and transformations retain stacks; explicit removal and Won/Lost tear down captures, and a fresh battle starts empty. Timing, calculator reach, retention and actor borrowing are independent low-confidence execution fields, not decoded source parity.</t>
+        </is>
+      </c>
+      <c r="S8" s="9" t="inlineStr">
+        <is>
+          <t>Alternatives include declaration-time or same-Skill stacking, different damage-purpose sets, linked recipients, reset-on-transform/wave or different removal retention. The selected complete-action boundary and original ownership use shared events/effects/formulas, checked arithmetic and no RNG. Replace each field independently with released typed semantics or reproducible current observations. Command tests cover multi-hit versus one Skill, nondamaging Skills, caps, all original Paths, independent/inherited owners, actual damage, removal, terminal cleanup, invalid operands, numeric rollback and fresh hashes. Normal equipment admission is not Forge, full-run replay or terminal reference coverage.</t>
+        </is>
+      </c>
+      <c r="T8" s="9" t="inlineStr">
+        <is>
+          <t>134|135|136|137|138|139|140</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:T8"/>
+  <dataValidations count="6">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="I8:I1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 64." promptTitle="Integer range" prompt="Enter an integer from 1 to 64." type="whole">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 65535." promptTitle="Integer range" prompt="Enter an integer from 1 to 65535." type="whole">
+      <formula1>1</formula1>
+      <formula2>65535</formula2>
+    </dataValidation>
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: EffectiveHpLossAfterSkillOriginalDamage" promptTitle="DuCurioFootstepPolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"EffectiveHpLossAfterSkillOriginalDamage"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -56,9 +56,11 @@
     <sheet name="WeightedCurioOverflows" sheetId="48" state="visible" r:id="rId48"/>
     <sheet name="WeightedCurioOverflowLevels" sheetId="49" state="visible" r:id="rId49"/>
     <sheet name="WeightedCurioFootsteps" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="WeightedCurioDeflagrations" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="WeightedCurioDeflagrationLevels" sheetId="52" state="visible" r:id="rId52"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sources'!$A$3:$K$155</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Policies'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Occurrences'!$A$3:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Choices'!$A$3:$J$10</definedName>
@@ -108,6 +110,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="47" hidden="1">'WeightedCurioOverflows'!$A$3:$X$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="48" hidden="1">'WeightedCurioOverflowLevels'!$A$3:$J$102</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="49" hidden="1">'WeightedCurioFootsteps'!$A$3:$T$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="50" hidden="1">'WeightedCurioDeflagrations'!$A$3:$W$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="51" hidden="1">'WeightedCurioDeflagrationLevels'!$A$3:$J$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -615,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K147"/>
+  <dimension ref="A1:K155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -8115,8 +8119,408 @@
         </is>
       </c>
     </row>
+    <row r="148" ht="360" customHeight="1">
+      <c r="B148" s="9" t="n">
+        <v>141</v>
+      </c>
+      <c r="C148" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-deflagration.hex</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E148" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F148" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G148" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H148" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/RogueTournHex.json; HexID=1012; TournMode=Tourn3; MazeBuffID=633412; AvatarDamageType=Fire</t>
+        </is>
+      </c>
+      <c r="I148" s="9" t="inlineStr">
+        <is>
+          <t>51e91a6f53ab0545330e477d806a165108f6c7e5e70ad52b02f92c1dc4d36455</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K148" s="9" t="inlineStr">
+        <is>
+          <t>Exact released joins, operands, curve values and named callbacks. Hidden postfix and Starclock timing/ownership parity are not inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="360" customHeight="1">
+      <c r="B149" s="9" t="n">
+        <v>142</v>
+      </c>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-deflagration.maze-buff</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E149" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F149" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G149" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H149" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/MazeBuff.json; ID=633412; Lv=1; ParamList=0.5,1,1.5,2,2,2; StageAbility_633412</t>
+        </is>
+      </c>
+      <c r="I149" s="9" t="inlineStr">
+        <is>
+          <t>2fab98b723ee20d8798c68e200cc9c3704abc347b0983b2955cbd40b85bfeeac</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K149" s="9" t="inlineStr">
+        <is>
+          <t>Exact released joins, operands, curve values and named callbacks. Hidden postfix and Starclock timing/ownership parity are not inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="360" customHeight="1">
+      <c r="B150" s="9" t="n">
+        <v>143</v>
+      </c>
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-deflagration.text-en</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E150" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F150" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G150" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H150" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapEN.json; hash=8602529829111077351; Deflagration and one-through-four Fire clauses</t>
+        </is>
+      </c>
+      <c r="I150" s="9" t="inlineStr">
+        <is>
+          <t>afc6d0ff9eeb20d09042e61c311e60d4ed56e69757f1ac42466ca4840e6ed789</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K150" s="9" t="inlineStr">
+        <is>
+          <t>Exact released joins, operands, curve values and named callbacks. Hidden postfix and Starclock timing/ownership parity are not inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="360" customHeight="1">
+      <c r="B151" s="9" t="n">
+        <v>144</v>
+      </c>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-deflagration.text-zh</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E151" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F151" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G151" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H151" s="9" t="inlineStr">
+        <is>
+          <t>TextMap/TextMapCHS.json; hash=8602529829111077351; Deflagration and one-through-four Fire clauses</t>
+        </is>
+      </c>
+      <c r="I151" s="9" t="inlineStr">
+        <is>
+          <t>ec49e07932b4ed8aba9679e247d8e554ca69e831fea7931d94682551de567147</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K151" s="9" t="inlineStr">
+        <is>
+          <t>Exact released joins, operands, curve values and named callbacks. Hidden postfix and Starclock timing/ownership parity are not inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="360" customHeight="1">
+      <c r="B152" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-deflagration.program</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E152" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G152" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H152" s="9" t="inlineStr">
+        <is>
+          <t>Config/ConfigAbility/Level/Rogue_S7/Level_RogueBuff_Ability_HEX_S7.json; Name=StageAbility_633412; OnEnterBattle Fire count; SuperBurn OnPhase1 versus OnCustomEvent; HPRatio and fixed operand 100</t>
+        </is>
+      </c>
+      <c r="I152" s="9" t="inlineStr">
+        <is>
+          <t>5ad6c48751023184f5572e0069c5d02c841aef4de3cec092d0c2bc4913d17e47</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K152" s="9" t="inlineStr">
+        <is>
+          <t>Exact released joins, operands, curve values and named callbacks. Hidden postfix and Starclock timing/ownership parity are not inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="360" customHeight="1">
+      <c r="B153" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-deflagration.hard-level</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E153" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F153" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G153" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H153" s="9" t="inlineStr">
+        <is>
+          <t>ExcelOutput/HardLevelGroup.json; HardLevelGroup=1; Level=1..95; HPRatio.Value</t>
+        </is>
+      </c>
+      <c r="I153" s="9" t="inlineStr">
+        <is>
+          <t>d185c09b5388f4eeb368199276ee8a815b406fd9902744027b72a5011b962978</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="inlineStr">
+        <is>
+          <t>ExactStructured</t>
+        </is>
+      </c>
+      <c r="K153" s="9" t="inlineStr">
+        <is>
+          <t>Exact released joins, operands, curve values and named callbacks. Hidden postfix and Starclock timing/ownership parity are not inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="360" customHeight="1">
+      <c r="B154" s="9" t="n">
+        <v>147</v>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-deflagration.base-policy</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F154" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G154" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H154" s="9" t="inlineStr">
+        <is>
+          <t>docs/divergent-universe-weighted-curio-deflagration.md#base-damage-policy</t>
+        </is>
+      </c>
+      <c r="I154" s="9" t="inlineStr">
+        <is>
+          <t>ebafc6dc99fa33fa2239a8c9bca6c1002d9f1c2f8858fe3a108ef6405282b7fd</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="inlineStr">
+        <is>
+          <t>ProjectPolicy</t>
+        </is>
+      </c>
+      <c r="K154" s="9" t="inlineStr">
+        <is>
+          <t>Digest binds the corresponding base-policy note in WeightedCurioDeflagrations, not an upstream blob. Replace fields independently; native execution remains pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="360" customHeight="1">
+      <c r="B155" s="9" t="n">
+        <v>148</v>
+      </c>
+      <c r="C155" s="9" t="inlineStr">
+        <is>
+          <t>du.source.weighted-curio-deflagration.runtime-policy</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>https://gitlab.com/Dimbreath/turnbasedgamedata</t>
+        </is>
+      </c>
+      <c r="E155" s="9" t="inlineStr">
+        <is>
+          <t>fd978d6ef09f941fba644c731ab54abd6f7c3568</t>
+        </is>
+      </c>
+      <c r="F155" s="9" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="G155" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H155" s="9" t="inlineStr">
+        <is>
+          <t>docs/divergent-universe-weighted-curio-deflagration.md#execution-policy</t>
+        </is>
+      </c>
+      <c r="I155" s="9" t="inlineStr">
+        <is>
+          <t>0c5d34a4ec484ad2c04c93f34217f51ad8b673ff2d87e36813152ae5f57fc298</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="inlineStr">
+        <is>
+          <t>ProjectPolicy</t>
+        </is>
+      </c>
+      <c r="K155" s="9" t="inlineStr">
+        <is>
+          <t>Digest binds the corresponding runtime-policy note in WeightedCurioDeflagrations, not an upstream blob. Replace fields independently; native execution remains pending.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K147"/>
+  <autoFilter ref="A3:K155"/>
   <dataValidations count="2">
     <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
       <formula1>1</formula1>
@@ -45998,6 +46402,4406 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" style="5" min="9" max="9"/>
+    <col width="28" customWidth="1" style="5" min="10" max="10"/>
+    <col width="28" customWidth="1" style="5" min="11" max="11"/>
+    <col width="28" customWidth="1" style="5" min="12" max="12"/>
+    <col width="28" customWidth="1" style="5" min="13" max="13"/>
+    <col width="55" customWidth="1" style="5" min="14" max="15"/>
+    <col width="55" customWidth="1" min="15" max="15"/>
+    <col width="55" customWidth="1" style="5" min="16" max="16"/>
+    <col width="70" customWidth="1" style="5" min="17" max="17"/>
+    <col width="70" customWidth="1" style="5" min="18" max="18"/>
+    <col width="110" customWidth="1" style="5" min="19" max="19"/>
+    <col width="110" customWidth="1" style="5" min="20" max="20"/>
+    <col width="110" customWidth="1" style="5" min="21" max="21"/>
+    <col width="110" customWidth="1" style="5" min="22" max="22"/>
+    <col width="28" customWidth="1" style="5" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuWeightedCurioDeflagrations</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>172135f6409c36b8</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="n"/>
+      <c r="L1" s="9" t="n"/>
+      <c r="M1" s="9" t="n"/>
+      <c r="N1" s="9" t="n"/>
+      <c r="O1" s="9" t="n"/>
+      <c r="P1" s="9" t="n"/>
+      <c r="Q1" s="9" t="n"/>
+      <c r="R1" s="9" t="n"/>
+      <c r="S1" s="9" t="n"/>
+      <c r="T1" s="9" t="n"/>
+      <c r="U1" s="9" t="n"/>
+      <c r="V1" s="9" t="n"/>
+      <c r="W1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>elements</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>burn_fractions</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>damage_parameter</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>damage_multiplier</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>duration_parameter</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>duration_turns</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>base_fixed_damage</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>base_hard_level_group</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="O2" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>base_policy</t>
+        </is>
+      </c>
+      <c r="Q2" s="10" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="S2" s="10" t="inlineStr">
+        <is>
+          <t>runtime_policy_note</t>
+        </is>
+      </c>
+      <c r="T2" s="10" t="inlineStr">
+        <is>
+          <t>runtime_replacement_condition</t>
+        </is>
+      </c>
+      <c r="U2" s="10" t="inlineStr">
+        <is>
+          <t>base_policy_note</t>
+        </is>
+      </c>
+      <c r="V2" s="10" t="inlineStr">
+        <is>
+          <t>base_replacement_condition</t>
+        </is>
+      </c>
+      <c r="W2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>maze_buff_id</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>elements</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>burn_fractions</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>damage_parameter</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>damage_multiplier</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>duration_parameter</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>duration_turns</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>base_fixed_damage</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>base_hard_level_group</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t>base_policy</t>
+        </is>
+      </c>
+      <c r="Q3" s="12" t="inlineStr">
+        <is>
+          <t>summary_en</t>
+        </is>
+      </c>
+      <c r="R3" s="12" t="inlineStr">
+        <is>
+          <t>summary_zh_cn</t>
+        </is>
+      </c>
+      <c r="S3" s="12" t="inlineStr">
+        <is>
+          <t>runtime_policy_note</t>
+        </is>
+      </c>
+      <c r="T3" s="12" t="inlineStr">
+        <is>
+          <t>runtime_replacement_condition</t>
+        </is>
+      </c>
+      <c r="U3" s="12" t="inlineStr">
+        <is>
+          <t>base_policy_note</t>
+        </is>
+      </c>
+      <c r="V3" s="12" t="inlineStr">
+        <is>
+          <t>base_replacement_condition</t>
+        </is>
+      </c>
+      <c r="W3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;string&gt;</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuDeflagrationStatus&gt;</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuDeflagrationPolicy&gt;</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>enum&lt;DuDeflagrationBasePolicy&gt;</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="R4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="S4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="T4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="U4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="V4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="W4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="Q5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="S5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="T5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="U5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="V5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="W5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>range=5..5</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>range=6..6</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>range=2..2</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..1</t>
+        </is>
+      </c>
+      <c r="N6" s="12" t="n"/>
+      <c r="O6" s="12" t="n"/>
+      <c r="P6" s="12" t="n"/>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="S6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="T6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="U6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="V6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="W6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
+      <c r="W7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="330" customHeight="1">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.most-raucous</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>633412</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>0.5|1|1.5|2</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>AuthoredOperandsPendingNative</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>OriginalFireAfterActionNaturalTickBurns</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>TargetGroupOneHpRatioProtocolHpFloor</t>
+        </is>
+      </c>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t>Fire originals apply two-turn Deflagration, counted as Burn; natural ticks deal twice base damage and detonate other Burns at the original Fire-count fraction.</t>
+        </is>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>火属性原角色施加两回合爆燃（视为灼烧）；自然周期结算造成两倍基础伤害，并按入场火角色人数比例引爆其他灼烧。</t>
+        </is>
+      </c>
+      <c r="S8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: canonical Basic scaling-damage element proves each original entry-form Fire member; original party formations zero through three only, excluding owned linked units. At BattleStarted capture the alive/present original Fire count once, selecting the factual one/two/three/four-member Burn fractions; no recapture after defeat, revival, transformation or waves. Each eligible original Unit attack applies Deflagration once at complete ActionResolved AfterAction priority zero to distinct living/present opposing EventTargets, with Guaranteed application, no chance roll. Replace the prior target Deflagration across casters, capture twice the selected target's authored level/Protocol base, one dispellable Burn stack, SourceSnapshotTargetDynamic, TurnStart tick, TargetTurnEnd two-turn lifetime. Only own-source DotTick DamageApplied AfterEvent priority zero once per event detonates other classified Burns, including periodic Break Burns, in shared stable effect-instance order; exclude all Deflagration instances and preserve original other-Burn sources/lifetimes. DotDetonation never triggers other Burns. Timing, chance, cross-caster replacement, source snapshot, recipient presence, original-actor borrowing and count retention are independent low-confidence fields, not hidden callback parity.</t>
+        </is>
+      </c>
+      <c r="T8" s="9" t="inlineStr">
+        <is>
+          <t>Alternatives include hit-end application, source ReplaceByCaster coexistence, enemy-owned effects, resistible application, live Fire counts, inherited actors or other native reaction priorities. Complete-action application and single cross-caster effect use the existing bounded command/effect pipeline without introducing a second state machine. Replace each field independently with released typed semantics or reproducible current traces; retain the source-backed natural-tick versus custom-event distinction. Native tests must cover one through four originals, no-Fire admission, duplicate hits/targets, multi-caster replacement, two real turns, ordinary/Break Burns, external detonation nonrecursion, linked and transformed actors, rejection, fresh payloads/hashes and unequip in both families. Forge, equipment-command replay and complete-run release remain separate pending work.</t>
+        </is>
+      </c>
+      <c r="U8" s="9" t="inlineStr">
+        <is>
+          <t>VersionedProjectPolicy: use the selected enemy's own level to choose released Group 1 HPRatio, multiply fixed operand 100 by that ratio, then by one plus immutable Protocol maximum-HP increase, flooring each checked Scalar multiplication to six places. The hidden postfix, Group 1 selection, target-level correspondence, Protocol interpretation, operator order and rounding remain independently replaceable low-confidence fields, not decoded or observed parity. Preserve level/Protocol dependence rather than substituting owner ATK or a level-independent constant.</t>
+        </is>
+      </c>
+      <c r="V8" s="9" t="inlineStr">
+        <is>
+          <t>Alternatives include stage-level scaling, a different hard-level group, a separately decoded difficulty factor or different operation/rounding order. Group 1 is the existing deterministic source-backed curve policy, not source membership evidence for this mechanic. Replace each field independently when released typed postfix semantics or reproducible current numerical traces establish it. Data tests check exact-once 95 rows, canonical decimals, policy/source isolation and operand drift; native all-level and Protocol command consumers remain pending.</t>
+        </is>
+      </c>
+      <c r="W8" s="9" t="inlineStr">
+        <is>
+          <t>141|142|143|144|145|146|147|148</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:W8"/>
+  <dataValidations count="8">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="H8:H1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 5 to 5." promptTitle="Integer range" prompt="Enter an integer from 5 to 5." type="whole">
+      <formula1>5</formula1>
+      <formula2>5</formula2>
+    </dataValidation>
+    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 6 to 6." promptTitle="Integer range" prompt="Enter an integer from 6 to 6." type="whole">
+      <formula1>6</formula1>
+      <formula2>6</formula2>
+    </dataValidation>
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 2 to 2." promptTitle="Integer range" prompt="Enter an integer from 2 to 2." type="whole">
+      <formula1>2</formula1>
+      <formula2>2</formula2>
+    </dataValidation>
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 1." promptTitle="Integer range" prompt="Enter an integer from 1 to 1." type="whole">
+      <formula1>1</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AuthoredOperandsPendingNative" promptTitle="DuDeflagrationStatus enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AuthoredOperandsPendingNative"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O8:O1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: OriginalFireAfterActionNaturalTickBurns" promptTitle="DuDeflagrationPolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"OriginalFireAfterActionNaturalTickBurns"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P8:P1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: TargetGroupOneHpRatioProtocolHpFloor" promptTitle="DuDeflagrationBasePolicy enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"TargetGroupOneHpRatioProtocolHpFloor"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J102"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" style="5" min="2" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" style="5" min="4" max="4"/>
+    <col width="28" customWidth="1" style="5" min="5" max="5"/>
+    <col width="28" customWidth="1" style="5" min="6" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>DuWeightedCurioDeflagrationLevels</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>54d8a1dd8dde51ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>hard_level_group</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>unit_level</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>hp_ratio</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="n"/>
+      <c r="J2" s="9" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>weighted_curio_key</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>hard_level_group</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>unit_level</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>hp_ratio</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>source_ids</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="9" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>list&lt;ref&lt;DuDecisionSources.id&gt;&gt;</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="n"/>
+      <c r="J4" s="9" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..1</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>range=1..95</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>length=1..4000</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>parser=split;separator=|</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="n"/>
+      <c r="J6" s="9" t="n"/>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="9" t="n"/>
+      <c r="J7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.001</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.002</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="n"/>
+      <c r="J9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.003</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.004</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>1.362518</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.005</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>1.428762</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="n"/>
+      <c r="J12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.006</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>1.496191</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.007</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>1.564808</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="n"/>
+      <c r="J14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.008</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>1.634615</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="n"/>
+      <c r="J15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.009</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>1.705617</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.010</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>1.777814</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.011</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>1.902566</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.012</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>2.027318</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="n"/>
+      <c r="J19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.013</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>2.15207</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="n"/>
+      <c r="J20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.014</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>2.276821</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="n"/>
+      <c r="J21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.015</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>2.401573</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="n"/>
+      <c r="J22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.016</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>2.526325</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="n"/>
+      <c r="J23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.017</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>2.651077</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="n"/>
+      <c r="J24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.018</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>2.775828</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="n"/>
+      <c r="J25" s="9" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.019</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>2.90058</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="n"/>
+      <c r="J26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n"/>
+      <c r="B27" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.020</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>3.025332</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="n"/>
+      <c r="J27" s="9" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.021</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>3.24706</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="n"/>
+      <c r="J28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.022</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>3.468788</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="n"/>
+      <c r="J29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.023</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>3.690516</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="n"/>
+      <c r="J30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n"/>
+      <c r="B31" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.024</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>3.912244</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="n"/>
+      <c r="J31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n"/>
+      <c r="B32" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.025</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>4.133972</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="n"/>
+      <c r="J32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n"/>
+      <c r="B33" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.026</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>4.355701</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n"/>
+      <c r="B34" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.027</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>4.577429</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="n"/>
+      <c r="B35" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.028</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>4.799157</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n"/>
+      <c r="B36" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.029</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>5.020885</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="9" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n"/>
+      <c r="B37" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.030</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>5.242613</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n"/>
+      <c r="B38" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.031</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>5.67081</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="n"/>
+      <c r="J38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="n"/>
+      <c r="B39" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.032</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>6.099006</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="n"/>
+      <c r="J39" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n"/>
+      <c r="B40" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.033</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>6.527203</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="n"/>
+      <c r="J40" s="9" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="n"/>
+      <c r="B41" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.034</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>6.9554</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="n"/>
+      <c r="J41" s="9" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n"/>
+      <c r="B42" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.035</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>7.383597</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="n"/>
+      <c r="J42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="n"/>
+      <c r="B43" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.036</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>7.811794</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="n"/>
+      <c r="B44" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.037</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>8.23999</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="n"/>
+      <c r="J44" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="n"/>
+      <c r="B45" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.038</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>8.668187</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="n"/>
+      <c r="B46" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.039</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>9.096384</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="n"/>
+      <c r="J46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="n"/>
+      <c r="B47" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.040</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>9.524581</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="n"/>
+      <c r="J47" s="9" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="n"/>
+      <c r="B48" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.041</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>10.786134</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="n"/>
+      <c r="J48" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="n"/>
+      <c r="B49" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.042</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>12.047688</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="n"/>
+      <c r="J49" s="9" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="n"/>
+      <c r="B50" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.043</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>13.309242</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I50" s="9" t="n"/>
+      <c r="J50" s="9" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="n"/>
+      <c r="B51" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.044</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>14.570795</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="n"/>
+      <c r="J51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="n"/>
+      <c r="B52" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.045</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>15.832349</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I52" s="9" t="n"/>
+      <c r="J52" s="9" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="n"/>
+      <c r="B53" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.046</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>17.093903</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="n"/>
+      <c r="J53" s="9" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="n"/>
+      <c r="B54" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.047</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>18.355455</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="n"/>
+      <c r="J54" s="9" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="n"/>
+      <c r="B55" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.048</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>19.61701</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="n"/>
+      <c r="J55" s="9" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="n"/>
+      <c r="B56" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.049</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>20.878565</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="n"/>
+      <c r="J56" s="9" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="n"/>
+      <c r="B57" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.050</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>22.140118</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="n"/>
+      <c r="J57" s="9" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="n"/>
+      <c r="B58" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.051</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>25.19852</t>
+        </is>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="n"/>
+      <c r="J58" s="9" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="n"/>
+      <c r="B59" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.052</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>28.256924</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I59" s="9" t="n"/>
+      <c r="J59" s="9" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="n"/>
+      <c r="B60" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.053</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>31.315327</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I60" s="9" t="n"/>
+      <c r="J60" s="9" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.054</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>34.37373</t>
+        </is>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I61" s="9" t="n"/>
+      <c r="J61" s="9" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="n"/>
+      <c r="B62" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.055</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>37.432133</t>
+        </is>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I62" s="9" t="n"/>
+      <c r="J62" s="9" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="n"/>
+      <c r="B63" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.056</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>40.490536</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I63" s="9" t="n"/>
+      <c r="J63" s="9" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="n"/>
+      <c r="B64" s="9" t="n">
+        <v>57</v>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.057</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="9" t="n">
+        <v>57</v>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>43.54894</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I64" s="9" t="n"/>
+      <c r="J64" s="9" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="n"/>
+      <c r="B65" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.058</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>46.60734</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I65" s="9" t="n"/>
+      <c r="J65" s="9" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="n"/>
+      <c r="B66" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.059</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>49.665745</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I66" s="9" t="n"/>
+      <c r="J66" s="9" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="n"/>
+      <c r="B67" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.060</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>52.724148</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I67" s="9" t="n"/>
+      <c r="J67" s="9" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="n"/>
+      <c r="B68" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.061</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>56.95045</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I68" s="9" t="n"/>
+      <c r="J68" s="9" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="n"/>
+      <c r="B69" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.062</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>61.17675</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I69" s="9" t="n"/>
+      <c r="J69" s="9" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="n"/>
+      <c r="B70" s="9" t="n">
+        <v>63</v>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.063</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="9" t="n">
+        <v>63</v>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>65.40305</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I70" s="9" t="n"/>
+      <c r="J70" s="9" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="n"/>
+      <c r="B71" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.064</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>69.62936</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I71" s="9" t="n"/>
+      <c r="J71" s="9" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="n"/>
+      <c r="B72" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.065</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>73.85566</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I72" s="9" t="n"/>
+      <c r="J72" s="9" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="n"/>
+      <c r="B73" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.066</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>78.08196</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I73" s="9" t="n"/>
+      <c r="J73" s="9" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="n"/>
+      <c r="B74" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.067</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>82.30826</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I74" s="9" t="n"/>
+      <c r="J74" s="9" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="n"/>
+      <c r="B75" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.068</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>86.53456</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I75" s="9" t="n"/>
+      <c r="J75" s="9" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="n"/>
+      <c r="B76" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.069</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>90.760864</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I76" s="9" t="n"/>
+      <c r="J76" s="9" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="n"/>
+      <c r="B77" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.070</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>94.98717</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I77" s="9" t="n"/>
+      <c r="J77" s="9" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="n"/>
+      <c r="B78" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.071</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>100.28955</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I78" s="9" t="n"/>
+      <c r="J78" s="9" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="n"/>
+      <c r="B79" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.072</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>105.591934</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I79" s="9" t="n"/>
+      <c r="J79" s="9" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="n"/>
+      <c r="B80" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.073</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>110.894325</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I80" s="9" t="n"/>
+      <c r="J80" s="9" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n"/>
+      <c r="B81" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.074</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>116.19671</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I81" s="9" t="n"/>
+      <c r="J81" s="9" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="n"/>
+      <c r="B82" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.075</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>121.49909</t>
+        </is>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I82" s="9" t="n"/>
+      <c r="J82" s="9" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="n"/>
+      <c r="B83" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.076</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>126.80148</t>
+        </is>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I83" s="9" t="n"/>
+      <c r="J83" s="9" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="n"/>
+      <c r="B84" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.077</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>132.10387</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I84" s="9" t="n"/>
+      <c r="J84" s="9" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="n"/>
+      <c r="B85" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.078</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>137.40625</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I85" s="9" t="n"/>
+      <c r="J85" s="9" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="n"/>
+      <c r="B86" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.079</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t>142.70863</t>
+        </is>
+      </c>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I86" s="9" t="n"/>
+      <c r="J86" s="9" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="n"/>
+      <c r="B87" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.080</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>148.01102</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I87" s="9" t="n"/>
+      <c r="J87" s="9" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="n"/>
+      <c r="B88" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.081</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="G88" s="9" t="inlineStr">
+        <is>
+          <t>155.48743</t>
+        </is>
+      </c>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I88" s="9" t="n"/>
+      <c r="J88" s="9" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="n"/>
+      <c r="B89" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.082</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
+        <is>
+          <t>163.24046</t>
+        </is>
+      </c>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I89" s="9" t="n"/>
+      <c r="J89" s="9" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="n"/>
+      <c r="B90" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.083</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>171.28036</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I90" s="9" t="n"/>
+      <c r="J90" s="9" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="n"/>
+      <c r="B91" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.084</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="G91" s="9" t="inlineStr">
+        <is>
+          <t>179.61774</t>
+        </is>
+      </c>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I91" s="9" t="n"/>
+      <c r="J91" s="9" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="n"/>
+      <c r="B92" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.085</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="G92" s="9" t="inlineStr">
+        <is>
+          <t>188.2636</t>
+        </is>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I92" s="9" t="n"/>
+      <c r="J92" s="9" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="n"/>
+      <c r="B93" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.086</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="G93" s="9" t="inlineStr">
+        <is>
+          <t>197.22934</t>
+        </is>
+      </c>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I93" s="9" t="n"/>
+      <c r="J93" s="9" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="n"/>
+      <c r="B94" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.087</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>206.52684</t>
+        </is>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I94" s="9" t="n"/>
+      <c r="J94" s="9" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="n"/>
+      <c r="B95" s="9" t="n">
+        <v>88</v>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.088</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="9" t="n">
+        <v>88</v>
+      </c>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>216.16832</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I95" s="9" t="n"/>
+      <c r="J95" s="9" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="n"/>
+      <c r="B96" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.089</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="G96" s="9" t="inlineStr">
+        <is>
+          <t>226.16655</t>
+        </is>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I96" s="9" t="n"/>
+      <c r="J96" s="9" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="n"/>
+      <c r="B97" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.090</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="G97" s="9" t="inlineStr">
+        <is>
+          <t>236.53471</t>
+        </is>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I97" s="9" t="n"/>
+      <c r="J97" s="9" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="n"/>
+      <c r="B98" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.091</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="G98" s="9" t="inlineStr">
+        <is>
+          <t>247.2865</t>
+        </is>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I98" s="9" t="n"/>
+      <c r="J98" s="9" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="n"/>
+      <c r="B99" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.092</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="G99" s="9" t="inlineStr">
+        <is>
+          <t>258.4361</t>
+        </is>
+      </c>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I99" s="9" t="n"/>
+      <c r="J99" s="9" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="n"/>
+      <c r="B100" s="9" t="n">
+        <v>93</v>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.093</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="9" t="n">
+        <v>93</v>
+      </c>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>269.99823</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I100" s="9" t="n"/>
+      <c r="J100" s="9" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="n"/>
+      <c r="B101" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.094</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="G101" s="9" t="inlineStr">
+        <is>
+          <t>281.98816</t>
+        </is>
+      </c>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I101" s="9" t="n"/>
+      <c r="J101" s="9" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="n"/>
+      <c r="B102" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>du.weighted-curio-deflagration.level.095</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>divergent-universe.weighted-curio.1012</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="G102" s="9" t="inlineStr">
+        <is>
+          <t>294.42172</t>
+        </is>
+      </c>
+      <c r="H102" s="9" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I102" s="9" t="n"/>
+      <c r="J102" s="9" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J102"/>
+  <dataValidations count="3">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="E8:E1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 1." promptTitle="Integer range" prompt="Enter an integer from 1 to 1." type="whole">
+      <formula1>1</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="F8:F1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 95." promptTitle="Integer range" prompt="Enter an integer from 1 to 95." type="whole">
+      <formula1>1</formula1>
+      <formula2>95</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
+++ b/config/divergent-universe-decisions/data/DivergentUniverseDecisions.xlsx
@@ -8465,7 +8465,7 @@
       </c>
       <c r="K154" s="9" t="inlineStr">
         <is>
-          <t>Digest binds the corresponding base-policy note in WeightedCurioDeflagrations, not an upstream blob. Replace fields independently; native execution remains pending.</t>
+          <t>Digest binds the corresponding base-policy note in WeightedCurioDeflagrations, not an upstream blob. Replace fields independently; normal equipment executes the native policy, not observed parity.</t>
         </is>
       </c>
     </row>
@@ -8515,7 +8515,7 @@
       </c>
       <c r="K155" s="9" t="inlineStr">
         <is>
-          <t>Digest binds the corresponding runtime-policy note in WeightedCurioDeflagrations, not an upstream blob. Replace fields independently; native execution remains pending.</t>
+          <t>Digest binds the corresponding runtime-policy note in WeightedCurioDeflagrations, not an upstream blob. Replace fields independently; normal equipment executes the native policy, not observed parity.</t>
         </is>
       </c>
     </row>
@@ -47157,7 +47157,7 @@
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>AuthoredOperandsPendingNative</t>
+          <t>NativeProjectPolicy</t>
         </is>
       </c>
       <c r="O8" s="9" t="inlineStr">
@@ -47229,8 +47229,8 @@
       <formula1>1</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AuthoredOperandsPendingNative" promptTitle="DuDeflagrationStatus enum" prompt="Select a value from the dropdown." type="list">
-      <formula1>"AuthoredOperandsPendingNative"</formula1>
+    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: NativeProjectPolicy" promptTitle="DuDeflagrationStatus enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"NativeProjectPolicy"</formula1>
     </dataValidation>
     <dataValidation sqref="O8:O1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: OriginalFireAfterActionNaturalTickBurns" promptTitle="DuDeflagrationPolicy enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"OriginalFireAfterActionNaturalTickBurns"</formula1>
